--- a/outputs/VIC_historical_prices.xlsx
+++ b/outputs/VIC_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>70.67</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>89.73999999999999</v>
+        <v>88.06</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>72.31</v>
+        <v>70.97</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>92.03</v>
+        <v>90.06999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>76.89</v>
+        <v>74.05</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>91.41</v>
+        <v>88.37</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>79.84</v>
+        <v>76.67</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>94.95999999999999</v>
+        <v>91.56999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>69.23</v>
+        <v>67.5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>82.20999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>72.66</v>
+        <v>70.58</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>86.31999999999999</v>
+        <v>83.92</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>79.34</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>92.81999999999999</v>
+        <v>92.14</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>87.64</v>
+        <v>87.22</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>102.62</v>
+        <v>101.48</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>78.37</v>
+        <v>78.45</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>94.36</v>
+        <v>94.33</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>93.88</v>
+        <v>93.81</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>113.32</v>
+        <v>113.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Apr 2026</t>
+          <t>Data through: May 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F275"/>
+  <dimension ref="A1:F276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6253,6 +6253,26 @@
       </c>
       <c r="F275" s="7" t="inlineStr"/>
     </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B276" s="5" t="n">
+        <v>64.77</v>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="D276" s="5" t="n">
+        <v>64.77</v>
+      </c>
+      <c r="E276" s="5" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="F276" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6264,7 +6284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E275"/>
+  <dimension ref="A1:E276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11507,8 +11527,27 @@
         <v>37.67</v>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B276" s="5" t="n">
+        <v>64.77</v>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="D276" s="5" t="n">
+        <v>64.77</v>
+      </c>
+      <c r="E276" s="5" t="n">
+        <v>73.73999999999999</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B275">
+  <conditionalFormatting sqref="B2:B276">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11520,7 +11559,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C275">
+  <conditionalFormatting sqref="C2:C276">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11532,7 +11571,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D275">
+  <conditionalFormatting sqref="D2:D276">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11544,7 +11583,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E275">
+  <conditionalFormatting sqref="E2:E276">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/VIC_historical_prices.xlsx
+++ b/outputs/VIC_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>69.56999999999999</v>
+        <v>53.08</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>88.06</v>
+        <v>55.96</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>70.97</v>
+        <v>53.75</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>90.06999999999999</v>
+        <v>56.69</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>74.05</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>88.37</v>
+        <v>83.34</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>76.67</v>
+        <v>72.23</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>91.56999999999999</v>
+        <v>86.08</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>67.5</v>
+        <v>67.84</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>80.2</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>70.58</v>
+        <v>70.78</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>83.92</v>
+        <v>83.48</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>79.20999999999999</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>92.14</v>
+        <v>91.64</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>87.22</v>
+        <v>86.53</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>101.48</v>
+        <v>100.56</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>78.45</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>94.33</v>
+        <v>94</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>93.81</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>113.08</v>
+        <v>112.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: May 2026</t>
+          <t>Data through: Jun 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F276"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6273,6 +6273,26 @@
       </c>
       <c r="F276" s="7" t="inlineStr"/>
     </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="n">
+        <v>66.81</v>
+      </c>
+      <c r="C277" s="5" t="n">
+        <v>78.04000000000001</v>
+      </c>
+      <c r="D277" s="5" t="n">
+        <v>66.81</v>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>78.04000000000001</v>
+      </c>
+      <c r="F277" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6284,7 +6304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E276"/>
+  <dimension ref="A1:E277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11546,8 +11566,27 @@
         <v>73.73999999999999</v>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="n">
+        <v>66.81</v>
+      </c>
+      <c r="C277" s="5" t="n">
+        <v>78.04000000000001</v>
+      </c>
+      <c r="D277" s="5" t="n">
+        <v>66.81</v>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>78.04000000000001</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B276">
+  <conditionalFormatting sqref="B2:B277">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11559,7 +11598,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C276">
+  <conditionalFormatting sqref="C2:C277">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11571,7 +11610,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D276">
+  <conditionalFormatting sqref="D2:D277">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11583,7 +11622,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E276">
+  <conditionalFormatting sqref="E2:E277">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/VIC_historical_prices.xlsx
+++ b/outputs/VIC_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>53.08</v>
+        <v>52.1</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>55.96</v>
+        <v>54.53</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>53.75</v>
+        <v>52.8</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>56.69</v>
+        <v>55.21</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>69.98999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>83.34</v>
+        <v>79.13</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>72.23</v>
+        <v>68.98</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>86.08</v>
+        <v>81.87</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>67.84</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>79.98999999999999</v>
+        <v>80.39</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>70.78</v>
+        <v>71.45</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>83.48</v>
+        <v>84.15000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>78.84999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>91.64</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>86.53</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>100.56</v>
+        <v>100.05</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>78.23999999999999</v>
+        <v>78.28</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>94</v>
+        <v>94.03</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>93.31999999999999</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>112.4</v>
+        <v>112.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Jun 2026</t>
+          <t>Data through: Jul 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F277"/>
+  <dimension ref="A1:F278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -690,10 +690,10 @@
         <v>32.99</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>47.61</v>
+        <v>47.9</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>61.31</v>
+        <v>61.68</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
     </row>
@@ -710,10 +710,10 @@
         <v>23.45</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>37.38</v>
+        <v>37.6</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>43.5</v>
+        <v>43.76</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
     </row>
@@ -730,10 +730,10 @@
         <v>25.19</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>38.38</v>
+        <v>38.61</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>46.64</v>
+        <v>46.92</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
     </row>
@@ -750,10 +750,10 @@
         <v>25.19</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>38.33</v>
+        <v>38.56</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>46.56</v>
+        <v>46.84</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
     </row>
@@ -770,10 +770,10 @@
         <v>26.23</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>39.08</v>
+        <v>39.31</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>48.39</v>
+        <v>48.68</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
     </row>
@@ -790,10 +790,10 @@
         <v>34.01</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>45.99</v>
+        <v>46.26</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>62.64</v>
+        <v>63.01</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
     </row>
@@ -810,10 +810,10 @@
         <v>30.37</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>41.35</v>
+        <v>41.6</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>55.77</v>
+        <v>56.1</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
@@ -830,10 +830,10 @@
         <v>48.76</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>70.70999999999999</v>
+        <v>71.13</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>89.27</v>
+        <v>89.81</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
     </row>
@@ -850,10 +850,10 @@
         <v>28.54</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>39.21</v>
+        <v>39.45</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>52.1</v>
+        <v>52.41</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
     </row>
@@ -870,10 +870,10 @@
         <v>36.99</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>53.7</v>
+        <v>54.02</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>67.42</v>
+        <v>67.83</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
     </row>
@@ -890,10 +890,10 @@
         <v>39.67</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>56.94</v>
+        <v>57.29</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>72.19</v>
+        <v>72.63</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -910,10 +910,10 @@
         <v>34.73</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>52.02</v>
+        <v>52.33</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>63.11</v>
+        <v>63.48</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
@@ -930,10 +930,10 @@
         <v>43.7</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>56.92</v>
+        <v>57.26</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>79.3</v>
+        <v>79.77</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -950,10 +950,10 @@
         <v>27.37</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>40.86</v>
+        <v>41.11</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>49.6</v>
+        <v>49.89</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -970,10 +970,10 @@
         <v>31.48</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>49.22</v>
+        <v>49.52</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>56.97</v>
+        <v>57.31</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -990,10 +990,10 @@
         <v>70.45</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>81.01000000000001</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>127.16</v>
+        <v>127.93</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -1010,10 +1010,10 @@
         <v>44.55</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>64.2</v>
+        <v>64.59</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>80.20999999999999</v>
+        <v>80.69</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
     </row>
@@ -1030,10 +1030,10 @@
         <v>33</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>49.13</v>
+        <v>49.43</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>59.26</v>
+        <v>59.62</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -1050,10 +1050,10 @@
         <v>29.72</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>40.93</v>
+        <v>41.17</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>53.25</v>
+        <v>53.57</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
     </row>
@@ -1070,10 +1070,10 @@
         <v>27.43</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>39.03</v>
+        <v>39.26</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>49.04</v>
+        <v>49.34</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
     </row>
@@ -1090,10 +1090,10 @@
         <v>21.15</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>33.36</v>
+        <v>33.56</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>37.73</v>
+        <v>37.96</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
     </row>
@@ -1110,10 +1110,10 @@
         <v>37.8</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>54.53</v>
+        <v>54.86</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>67.3</v>
+        <v>67.7</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
     </row>
@@ -1130,10 +1130,10 @@
         <v>29.2</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>43.64</v>
+        <v>43.9</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>51.88</v>
+        <v>52.19</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
     </row>
@@ -1150,10 +1150,10 @@
         <v>27.29</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>41.74</v>
+        <v>41.99</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>48.39</v>
+        <v>48.68</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
     </row>
@@ -1170,10 +1170,10 @@
         <v>32.37</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>46.86</v>
+        <v>47.14</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>57.21</v>
+        <v>57.56</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
     </row>
@@ -1190,10 +1190,10 @@
         <v>40.25</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>52.85</v>
+        <v>53.17</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>70.91</v>
+        <v>71.33</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
     </row>
@@ -1210,10 +1210,10 @@
         <v>37.44</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>51.17</v>
+        <v>51.47</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>65.73999999999999</v>
+        <v>66.13</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
     </row>
@@ -1230,10 +1230,10 @@
         <v>28.49</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>39.68</v>
+        <v>39.92</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>49.94</v>
+        <v>50.24</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
     </row>
@@ -1250,10 +1250,10 @@
         <v>46.39</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>53.72</v>
+        <v>54.04</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>81.17</v>
+        <v>81.66</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
     </row>
@@ -1270,10 +1270,10 @@
         <v>49.23</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>59.81</v>
+        <v>60.17</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>86</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
     </row>
@@ -1290,10 +1290,10 @@
         <v>88.63</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>93.08</v>
+        <v>93.64</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>154.38</v>
+        <v>155.3</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
     </row>
@@ -1310,10 +1310,10 @@
         <v>105.51</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>97.27</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>183.26</v>
+        <v>184.36</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
     </row>
@@ -1330,10 +1330,10 @@
         <v>29.33</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>40.46</v>
+        <v>40.7</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>50.8</v>
+        <v>51.1</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
     </row>
@@ -1350,10 +1350,10 @@
         <v>27.86</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>38.92</v>
+        <v>39.15</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>48</v>
+        <v>48.29</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
     </row>
@@ -1370,10 +1370,10 @@
         <v>37.94</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>48.42</v>
+        <v>48.71</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>65.02</v>
+        <v>65.41</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
     </row>
@@ -1390,10 +1390,10 @@
         <v>42.49</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>59.01</v>
+        <v>59.36</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>72.44</v>
+        <v>72.88</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
     </row>
@@ -1410,10 +1410,10 @@
         <v>71.86</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>80.23999999999999</v>
+        <v>80.72</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>122.16</v>
+        <v>122.89</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
     </row>
@@ -1430,10 +1430,10 @@
         <v>39.11</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>54.59</v>
+        <v>54.92</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>66.29000000000001</v>
+        <v>66.69</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
     </row>
@@ -1450,10 +1450,10 @@
         <v>38.91</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>52.05</v>
+        <v>52.36</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>65.76000000000001</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
     </row>
@@ -1470,10 +1470,10 @@
         <v>34.69</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>46.76</v>
+        <v>47.04</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>58.65</v>
+        <v>59</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
     </row>
@@ -1490,10 +1490,10 @@
         <v>42.78</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>55.32</v>
+        <v>55.65</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>72.34999999999999</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
     </row>
@@ -1510,10 +1510,10 @@
         <v>28.32</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>37.7</v>
+        <v>37.92</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>47.91</v>
+        <v>48.2</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
     </row>
@@ -1530,10 +1530,10 @@
         <v>165.37</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>154.7</v>
+        <v>155.63</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>279.71</v>
+        <v>281.39</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
     </row>
@@ -1550,10 +1550,10 @@
         <v>69.13</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>80.22</v>
+        <v>80.7</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>116.9</v>
+        <v>117.6</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
     </row>
@@ -1570,10 +1570,10 @@
         <v>74.84999999999999</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>90.06999999999999</v>
+        <v>90.61</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>126.53</v>
+        <v>127.29</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
     </row>
@@ -1590,10 +1590,10 @@
         <v>81.62</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>114.08</v>
+        <v>114.76</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>137.41</v>
+        <v>138.24</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
     </row>
@@ -1610,10 +1610,10 @@
         <v>75.48999999999999</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>105.03</v>
+        <v>105.66</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>126.58</v>
+        <v>127.34</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
     </row>
@@ -1630,10 +1630,10 @@
         <v>218.05</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>239.27</v>
+        <v>240.71</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>364.13</v>
+        <v>366.32</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
     </row>
@@ -1650,10 +1650,10 @@
         <v>115.22</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>142.54</v>
+        <v>143.39</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>191.97</v>
+        <v>193.12</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
     </row>
@@ -1670,10 +1670,10 @@
         <v>50.83</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>69.37</v>
+        <v>69.78</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>84.5</v>
+        <v>85</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
     </row>
@@ -1690,10 +1690,10 @@
         <v>55.04</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>73.94</v>
+        <v>74.38</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>91.28</v>
+        <v>91.83</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
     </row>
@@ -1710,10 +1710,10 @@
         <v>45.32</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>58.71</v>
+        <v>59.06</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>74.93000000000001</v>
+        <v>75.38</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
     </row>
@@ -1730,10 +1730,10 @@
         <v>54.55</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>70.43000000000001</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>89.91</v>
+        <v>90.45</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
     </row>
@@ -1750,10 +1750,10 @@
         <v>62.08</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>73.59999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>102.01</v>
+        <v>102.62</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
     </row>
@@ -1770,10 +1770,10 @@
         <v>55.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>66.04000000000001</v>
+        <v>66.44</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>90.16</v>
+        <v>90.7</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
     </row>
@@ -1790,10 +1790,10 @@
         <v>52.11</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>60.07</v>
+        <v>60.43</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>84.87</v>
+        <v>85.38</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
     </row>
@@ -1810,10 +1810,10 @@
         <v>84.56999999999999</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>84.54000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>137.13</v>
+        <v>137.95</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
     </row>
@@ -1830,10 +1830,10 @@
         <v>50.14</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>64.31999999999999</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>80.91</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
@@ -1850,10 +1850,10 @@
         <v>64.59</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>86.77</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>103.73</v>
+        <v>104.35</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
     </row>
@@ -1870,10 +1870,10 @@
         <v>52.09</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>67.19</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>83.26000000000001</v>
+        <v>83.75</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
@@ -1890,10 +1890,10 @@
         <v>60.12</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>68.53</v>
+        <v>68.94</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>95.72</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
     </row>
@@ -1910,10 +1910,10 @@
         <v>50.92</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>64.88</v>
+        <v>65.27</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>80.76000000000001</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
     </row>
@@ -1930,10 +1930,10 @@
         <v>47.77</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>57.86</v>
+        <v>58.2</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>75.47</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
     </row>
@@ -1950,10 +1950,10 @@
         <v>51.76</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>62.27</v>
+        <v>62.64</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>81.87</v>
+        <v>82.36</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
     </row>
@@ -1970,10 +1970,10 @@
         <v>45.33</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>54.72</v>
+        <v>55.05</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>71.77</v>
+        <v>72.2</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
     </row>
@@ -1990,10 +1990,10 @@
         <v>27.82</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>35.65</v>
+        <v>35.86</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>44.1</v>
+        <v>44.36</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
     </row>
@@ -2010,10 +2010,10 @@
         <v>248.2</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>198.92</v>
+        <v>200.11</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>393.28</v>
+        <v>395.64</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
     </row>
@@ -2030,10 +2030,10 @@
         <v>44.74</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>52.9</v>
+        <v>53.22</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>70.87</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
     </row>
@@ -2050,10 +2050,10 @@
         <v>32.56</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>40.01</v>
+        <v>40.25</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>51.55</v>
+        <v>51.86</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
     </row>
@@ -2070,10 +2070,10 @@
         <v>49.27</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>58.96</v>
+        <v>59.32</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>77.88</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
     </row>
@@ -2090,10 +2090,10 @@
         <v>37.87</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>49.63</v>
+        <v>49.93</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>59.76</v>
+        <v>60.12</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
     </row>
@@ -2110,10 +2110,10 @@
         <v>37.13</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>47.38</v>
+        <v>47.66</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>58.5</v>
+        <v>58.85</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
     </row>
@@ -2130,10 +2130,10 @@
         <v>32.55</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>42.15</v>
+        <v>42.41</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>51.12</v>
+        <v>51.43</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
     </row>
@@ -2150,10 +2150,10 @@
         <v>28.02</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>35.13</v>
+        <v>35.34</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>43.87</v>
+        <v>44.13</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
     </row>
@@ -2170,10 +2170,10 @@
         <v>27.43</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>35.8</v>
+        <v>36.02</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>42.81</v>
+        <v>43.07</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
     </row>
@@ -2190,10 +2190,10 @@
         <v>31.55</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>39.82</v>
+        <v>40.06</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>49.15</v>
+        <v>49.45</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
     </row>
@@ -2210,10 +2210,10 @@
         <v>44.98</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>50.44</v>
+        <v>50.74</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>69.95</v>
+        <v>70.37</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
     </row>
@@ -2230,10 +2230,10 @@
         <v>29.49</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>36.5</v>
+        <v>36.72</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>45.78</v>
+        <v>46.06</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
     </row>
@@ -2250,10 +2250,10 @@
         <v>114.74</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>94.33</v>
+        <v>94.89</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>177.58</v>
+        <v>178.64</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
     </row>
@@ -2270,10 +2270,10 @@
         <v>124.09</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>104.78</v>
+        <v>105.4</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>191.45</v>
+        <v>192.6</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
     </row>
@@ -2290,10 +2290,10 @@
         <v>27.11</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>35.16</v>
+        <v>35.37</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>41.7</v>
+        <v>41.95</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
     </row>
@@ -2310,10 +2310,10 @@
         <v>131.25</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>109.85</v>
+        <v>110.5</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>201.47</v>
+        <v>202.68</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>34.97</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>46.71</v>
+        <v>46.99</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>53.57</v>
+        <v>53.89</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
     </row>
@@ -2350,10 +2350,10 @@
         <v>36.19</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>48.01</v>
+        <v>48.29</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>55.33</v>
+        <v>55.66</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
     </row>
@@ -2370,10 +2370,10 @@
         <v>30.36</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>40.65</v>
+        <v>40.89</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>46.3</v>
+        <v>46.58</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
     </row>
@@ -2390,10 +2390,10 @@
         <v>30.73</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>41.16</v>
+        <v>41.4</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>46.76</v>
+        <v>47.04</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
     </row>
@@ -2410,10 +2410,10 @@
         <v>24.89</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>33.58</v>
+        <v>33.78</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>37.78</v>
+        <v>38.01</v>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
     </row>
@@ -2430,10 +2430,10 @@
         <v>24.65</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>31.56</v>
+        <v>31.75</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>37.37</v>
+        <v>37.59</v>
       </c>
       <c r="F89" s="7" t="inlineStr"/>
     </row>
@@ -2450,10 +2450,10 @@
         <v>21.04</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>27.89</v>
+        <v>28.06</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
     </row>
@@ -2470,10 +2470,10 @@
         <v>18.96</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>24.98</v>
+        <v>25.13</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>28.67</v>
+        <v>28.84</v>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
     </row>
@@ -2490,10 +2490,10 @@
         <v>66.16</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>61.78</v>
+        <v>62.15</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>99.52</v>
+        <v>100.12</v>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
     </row>
@@ -2510,10 +2510,10 @@
         <v>59.69</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>60.55</v>
+        <v>60.92</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>89.33</v>
+        <v>89.87</v>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
     </row>
@@ -2530,10 +2530,10 @@
         <v>28.62</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>37.17</v>
+        <v>37.39</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>42.62</v>
+        <v>42.87</v>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
     </row>
@@ -2550,10 +2550,10 @@
         <v>28.26</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>38</v>
+        <v>38.23</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>41.95</v>
+        <v>42.2</v>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
     </row>
@@ -2570,10 +2570,10 @@
         <v>40.58</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>50.84</v>
+        <v>51.14</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>60.06</v>
+        <v>60.42</v>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
     </row>
@@ -2590,10 +2590,10 @@
         <v>33.89</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>41.19</v>
+        <v>41.44</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
     </row>
@@ -2610,10 +2610,10 @@
         <v>37.84</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>43.42</v>
+        <v>43.68</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>55.72</v>
+        <v>56.05</v>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
     </row>
@@ -2630,10 +2630,10 @@
         <v>35.44</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>44.01</v>
+        <v>44.28</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>52.08</v>
+        <v>52.39</v>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
     </row>
@@ -2650,10 +2650,10 @@
         <v>31.61</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>39.57</v>
+        <v>39.81</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>46.36</v>
+        <v>46.64</v>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
     </row>
@@ -2670,10 +2670,10 @@
         <v>29</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>34.63</v>
+        <v>34.84</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>42.53</v>
+        <v>42.79</v>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
     </row>
@@ -2690,10 +2690,10 @@
         <v>30.77</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>38.98</v>
+        <v>39.22</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>45.13</v>
+        <v>45.4</v>
       </c>
       <c r="F102" s="7" t="inlineStr"/>
     </row>
@@ -2710,10 +2710,10 @@
         <v>25.62</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>32.53</v>
+        <v>32.73</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>37.58</v>
+        <v>37.8</v>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
     </row>
@@ -2730,10 +2730,10 @@
         <v>29.13</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>35.24</v>
+        <v>35.45</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>42.72</v>
+        <v>42.97</v>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
     </row>
@@ -2750,10 +2750,10 @@
         <v>30.01</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>37.9</v>
+        <v>38.13</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>44</v>
+        <v>44.26</v>
       </c>
       <c r="F105" s="7" t="inlineStr"/>
     </row>
@@ -2770,10 +2770,10 @@
         <v>27.89</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>34.74</v>
+        <v>34.95</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>40.88</v>
+        <v>41.13</v>
       </c>
       <c r="F106" s="7" t="inlineStr"/>
     </row>
@@ -2790,10 +2790,10 @@
         <v>36.3</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>46.84</v>
+        <v>47.12</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>53.12</v>
+        <v>53.44</v>
       </c>
       <c r="F107" s="7" t="inlineStr"/>
     </row>
@@ -2810,10 +2810,10 @@
         <v>30.09</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>38.83</v>
+        <v>39.06</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>43.96</v>
+        <v>44.22</v>
       </c>
       <c r="F108" s="7" t="inlineStr"/>
     </row>
@@ -2830,10 +2830,10 @@
         <v>42.66</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>53.59</v>
+        <v>53.91</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>62.21</v>
+        <v>62.58</v>
       </c>
       <c r="F109" s="7" t="inlineStr"/>
     </row>
@@ -2850,10 +2850,10 @@
         <v>90.05</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>106.64</v>
+        <v>107.28</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>130.72</v>
+        <v>131.51</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -2874,10 +2874,10 @@
         <v>58.79</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>80.58</v>
+        <v>81.06</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>84.95999999999999</v>
+        <v>85.47</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -2898,10 +2898,10 @@
         <v>60.96</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>76.94</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>87.7</v>
+        <v>88.23</v>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
         <v>55</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>73.7</v>
+        <v>74.14</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>79.06</v>
+        <v>79.53</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         <v>108.73</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>110.85</v>
+        <v>111.51</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>156.16</v>
+        <v>157.1</v>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
@@ -2970,10 +2970,10 @@
         <v>58.92</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>74.88</v>
+        <v>75.33</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>84.55</v>
+        <v>85.06</v>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         <v>65.31</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>77.79000000000001</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>93.62</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
@@ -3018,10 +3018,10 @@
         <v>59.78</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>76.73</v>
+        <v>77.19</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>85.59</v>
+        <v>86.11</v>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
@@ -3042,10 +3042,10 @@
         <v>60.03</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>74.81</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="E118" s="9" t="n">
-        <v>85.84999999999999</v>
+        <v>86.37</v>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
         <v>53.46</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>71.45</v>
+        <v>71.88</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>76.36</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
@@ -3090,10 +3090,10 @@
         <v>61.01</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>78.25</v>
+        <v>78.72</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>87.03</v>
+        <v>87.56</v>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
         <v>70.51000000000001</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>86.77</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="E121" s="9" t="n">
-        <v>100.46</v>
+        <v>101.06</v>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
@@ -3138,10 +3138,10 @@
         <v>62.4</v>
       </c>
       <c r="D122" s="9" t="n">
-        <v>82.8</v>
+        <v>83.3</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>88.55</v>
+        <v>89.08</v>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
@@ -3162,10 +3162,10 @@
         <v>57.79</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>76.48999999999999</v>
+        <v>76.95</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>81.67</v>
+        <v>82.16</v>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         <v>52.11</v>
       </c>
       <c r="D124" s="9" t="n">
-        <v>69.31999999999999</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>73.34999999999999</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         <v>51.91</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>69.47</v>
+        <v>69.88</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>72.89</v>
+        <v>73.33</v>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
@@ -3234,10 +3234,10 @@
         <v>49.47</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>65.51000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>69.3</v>
+        <v>69.72</v>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
@@ -3258,10 +3258,10 @@
         <v>57.51</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>70.34</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>80.37</v>
+        <v>80.86</v>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
@@ -3282,10 +3282,10 @@
         <v>105.62</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>101.03</v>
+        <v>101.63</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>147.32</v>
+        <v>148.2</v>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         <v>51.64</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>68.56</v>
+        <v>68.97</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>71.89</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
@@ -3330,10 +3330,10 @@
         <v>50.99</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>63.85</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>70.84</v>
+        <v>71.27</v>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
         <v>46.48</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>60.74</v>
+        <v>61.1</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>64.47</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
@@ -3378,10 +3378,10 @@
         <v>53.42</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>66.73999999999999</v>
+        <v>67.14</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>73.97</v>
+        <v>74.41</v>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
@@ -3402,10 +3402,10 @@
         <v>53.9</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>67.97</v>
+        <v>68.38</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>74.51000000000001</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
@@ -3426,10 +3426,10 @@
         <v>43.69</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>53.27</v>
+        <v>53.59</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>60.31</v>
+        <v>60.67</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
     </row>
@@ -3446,10 +3446,10 @@
         <v>40.67</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>47.57</v>
+        <v>47.86</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>56.06</v>
+        <v>56.4</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
     </row>
@@ -3466,10 +3466,10 @@
         <v>42.07</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>49.91</v>
+        <v>50.21</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>57.91</v>
+        <v>58.26</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
     </row>
@@ -3486,10 +3486,10 @@
         <v>30.63</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>36.58</v>
+        <v>36.8</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>42.14</v>
+        <v>42.39</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
     </row>
@@ -3506,10 +3506,10 @@
         <v>34.46</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>39.26</v>
+        <v>39.5</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>47.38</v>
+        <v>47.66</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
     </row>
@@ -3526,10 +3526,10 @@
         <v>31.31</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>36.46</v>
+        <v>36.68</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>43.02</v>
+        <v>43.28</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
     </row>
@@ -3546,10 +3546,10 @@
         <v>33.61</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>35.84</v>
+        <v>36.05</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>46.15</v>
+        <v>46.43</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
     </row>
@@ -3566,10 +3566,10 @@
         <v>35.21</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>38.46</v>
+        <v>38.69</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>48.32</v>
+        <v>48.61</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
     </row>
@@ -3586,10 +3586,10 @@
         <v>31.79</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>35.39</v>
+        <v>35.61</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>43.6</v>
+        <v>43.86</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
     </row>
@@ -3606,10 +3606,10 @@
         <v>35.26</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>39.55</v>
+        <v>39.79</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>48.24</v>
+        <v>48.53</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
     </row>
@@ -3626,10 +3626,10 @@
         <v>38.41</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>40.74</v>
+        <v>40.99</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>52.42</v>
+        <v>52.74</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
     </row>
@@ -3646,10 +3646,10 @@
         <v>41.52</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>46.85</v>
+        <v>47.13</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>56.53</v>
+        <v>56.87</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
     </row>
@@ -3666,10 +3666,10 @@
         <v>42.82</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>47.26</v>
+        <v>47.54</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>58.23</v>
+        <v>58.58</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
     </row>
@@ -3686,10 +3686,10 @@
         <v>42.1</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>47.59</v>
+        <v>47.87</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>57.18</v>
+        <v>57.52</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
     </row>
@@ -3706,10 +3706,10 @@
         <v>50.84</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>60.43</v>
+        <v>60.79</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>68.95999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
     </row>
@@ -3726,10 +3726,10 @@
         <v>45.47</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>48.26</v>
+        <v>48.55</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>61.59</v>
+        <v>61.96</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
     </row>
@@ -3746,10 +3746,10 @@
         <v>45.23</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>47.24</v>
+        <v>47.53</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>61.19</v>
+        <v>61.56</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
     </row>
@@ -3766,10 +3766,10 @@
         <v>62.67</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>64.87</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>84.68000000000001</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
     </row>
@@ -3786,10 +3786,10 @@
         <v>72.90000000000001</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>63.48</v>
+        <v>63.86</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>98.56</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
     </row>
@@ -3806,10 +3806,10 @@
         <v>44.52</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>47.92</v>
+        <v>48.21</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>60.23</v>
+        <v>60.59</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
     </row>
@@ -3826,10 +3826,10 @@
         <v>59.65</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>62.13</v>
+        <v>62.5</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>80.76000000000001</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
     </row>
@@ -3846,10 +3846,10 @@
         <v>61.49</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>62.02</v>
+        <v>62.4</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>83.13</v>
+        <v>83.62</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
     </row>
@@ -3866,10 +3866,10 @@
         <v>76.45999999999999</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>73.22</v>
+        <v>73.66</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>103.21</v>
+        <v>103.83</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
     </row>
@@ -3886,10 +3886,10 @@
         <v>118.54</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>125.05</v>
+        <v>125.8</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>159.78</v>
+        <v>160.74</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
     </row>
@@ -3906,10 +3906,10 @@
         <v>86.77</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>86.93000000000001</v>
+        <v>87.45</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>116.69</v>
+        <v>117.39</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
     </row>
@@ -3926,10 +3926,10 @@
         <v>55.76</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>58.01</v>
+        <v>58.36</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>74.81</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
     </row>
@@ -3946,10 +3946,10 @@
         <v>48.5</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>54.91</v>
+        <v>55.24</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>64.92</v>
+        <v>65.31</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
     </row>
@@ -3966,10 +3966,10 @@
         <v>41.02</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>44.33</v>
+        <v>44.6</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>54.81</v>
+        <v>55.14</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
     </row>
@@ -3986,10 +3986,10 @@
         <v>46.93</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>48.11</v>
+        <v>48.4</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>62.6</v>
+        <v>62.97</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
     </row>
@@ -4006,10 +4006,10 @@
         <v>37.59</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>39.81</v>
+        <v>40.05</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>50.05</v>
+        <v>50.35</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
     </row>
@@ -4026,10 +4026,10 @@
         <v>81.03</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>82.48</v>
+        <v>82.98</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>107.73</v>
+        <v>108.37</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
     </row>
@@ -4046,10 +4046,10 @@
         <v>114.18</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>114.23</v>
+        <v>114.91</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>151.57</v>
+        <v>152.48</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
     </row>
@@ -4066,10 +4066,10 @@
         <v>112.64</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>120.12</v>
+        <v>120.84</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>149.3</v>
+        <v>150.19</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
     </row>
@@ -4086,10 +4086,10 @@
         <v>123.35</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>143.32</v>
+        <v>144.18</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>163.38</v>
+        <v>164.36</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
     </row>
@@ -4106,10 +4106,10 @@
         <v>123.09</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>142.89</v>
+        <v>143.75</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>162.93</v>
+        <v>163.91</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
     </row>
@@ -4126,10 +4126,10 @@
         <v>105</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>130.3</v>
+        <v>131.08</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>138.9</v>
+        <v>139.73</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
     </row>
@@ -4146,10 +4146,10 @@
         <v>131.48</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>154.96</v>
+        <v>155.89</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>173.57</v>
+        <v>174.61</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
     </row>
@@ -4166,10 +4166,10 @@
         <v>119.74</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>135.13</v>
+        <v>135.94</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>157.75</v>
+        <v>158.7</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
     </row>
@@ -4186,10 +4186,10 @@
         <v>89.62</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>104.43</v>
+        <v>105.06</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>117.83</v>
+        <v>118.54</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
     </row>
@@ -4206,10 +4206,10 @@
         <v>82.48</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>96.17</v>
+        <v>96.75</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>108.2</v>
+        <v>108.85</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
     </row>
@@ -4226,10 +4226,10 @@
         <v>112.43</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>125.06</v>
+        <v>125.81</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>147.16</v>
+        <v>148.05</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
     </row>
@@ -4246,10 +4246,10 @@
         <v>97.75</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>110.82</v>
+        <v>111.48</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>127.66</v>
+        <v>128.43</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
     </row>
@@ -4266,10 +4266,10 @@
         <v>183</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>174.07</v>
+        <v>175.12</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>238.65</v>
+        <v>240.09</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
     </row>
@@ -4286,10 +4286,10 @@
         <v>124.33</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>126.88</v>
+        <v>127.64</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>161.91</v>
+        <v>162.88</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
     </row>
@@ -4306,10 +4306,10 @@
         <v>82.25</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>98.84</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>106.95</v>
+        <v>107.59</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
     </row>
@@ -4326,10 +4326,10 @@
         <v>87.09</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>96.16</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>113.11</v>
+        <v>113.79</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
     </row>
@@ -4346,10 +4346,10 @@
         <v>95.98</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>103.51</v>
+        <v>104.13</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>124.51</v>
+        <v>125.26</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
     </row>
@@ -4366,10 +4366,10 @@
         <v>112.11</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>121.43</v>
+        <v>122.16</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>145.26</v>
+        <v>146.13</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
     </row>
@@ -4386,10 +4386,10 @@
         <v>88.33</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>90.7</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>114.28</v>
+        <v>114.97</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
     </row>
@@ -4406,10 +4406,10 @@
         <v>102.2</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>102.29</v>
+        <v>102.9</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>132.04</v>
+        <v>132.83</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
     </row>
@@ -4426,10 +4426,10 @@
         <v>108.02</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>119.79</v>
+        <v>120.51</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>139.36</v>
+        <v>140.19</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>109.7</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>128.57</v>
+        <v>129.34</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>141.28</v>
+        <v>142.13</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
     </row>
@@ -4466,10 +4466,10 @@
         <v>105.48</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>125.79</v>
+        <v>126.54</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>135.61</v>
+        <v>136.42</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
     </row>
@@ -4486,10 +4486,10 @@
         <v>113.92</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>117.81</v>
+        <v>118.51</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>146.21</v>
+        <v>147.09</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
     </row>
@@ -4506,10 +4506,10 @@
         <v>423.33</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>321.3</v>
+        <v>323.22</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>543.34</v>
+        <v>546.6</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
     </row>
@@ -4526,10 +4526,10 @@
         <v>120.86</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>142.68</v>
+        <v>143.54</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>155.13</v>
+        <v>156.06</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
     </row>
@@ -4546,10 +4546,10 @@
         <v>177.81</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>168.29</v>
+        <v>169.3</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>228.24</v>
+        <v>229.61</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
     </row>
@@ -4566,10 +4566,10 @@
         <v>106.79</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>126.11</v>
+        <v>126.87</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>136.81</v>
+        <v>137.63</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
     </row>
@@ -4586,10 +4586,10 @@
         <v>104.25</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>117.5</v>
+        <v>118.2</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>133.29</v>
+        <v>134.09</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
     </row>
@@ -4606,10 +4606,10 @@
         <v>122.01</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>129.91</v>
+        <v>130.69</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>155.69</v>
+        <v>156.62</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
     </row>
@@ -4626,10 +4626,10 @@
         <v>105.02</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>109.43</v>
+        <v>110.09</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>133.76</v>
+        <v>134.56</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
     </row>
@@ -4646,10 +4646,10 @@
         <v>130.29</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>133.42</v>
+        <v>134.22</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>165.63</v>
+        <v>166.62</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
     </row>
@@ -4666,10 +4666,10 @@
         <v>121.93</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>132.93</v>
+        <v>133.72</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>154.71</v>
+        <v>155.64</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
     </row>
@@ -4686,10 +4686,10 @@
         <v>113.03</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>127.48</v>
+        <v>128.25</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>143.09</v>
+        <v>143.95</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
     </row>
@@ -4706,10 +4706,10 @@
         <v>69.79000000000001</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>85.87</v>
+        <v>86.38</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>88.15000000000001</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
     </row>
@@ -4726,10 +4726,10 @@
         <v>77.45999999999999</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>77.37</v>
+        <v>77.83</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>97.62</v>
+        <v>98.2</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
     </row>
@@ -4746,10 +4746,10 @@
         <v>255.88</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>179.93</v>
+        <v>181.01</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>322.07</v>
+        <v>324</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
     </row>
@@ -4766,10 +4766,10 @@
         <v>55.83</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>60.73</v>
+        <v>61.1</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>70.18000000000001</v>
+        <v>70.61</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
     </row>
@@ -4786,10 +4786,10 @@
         <v>50.47</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>54.37</v>
+        <v>54.69</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>63.37</v>
+        <v>63.75</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
     </row>
@@ -4806,10 +4806,10 @@
         <v>41.9</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>44.01</v>
+        <v>44.28</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>52.95</v>
+        <v>53.27</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
     </row>
@@ -4826,10 +4826,10 @@
         <v>47.04</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>48.7</v>
+        <v>48.99</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>59.83</v>
+        <v>60.19</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
     </row>
@@ -4846,10 +4846,10 @@
         <v>62.91</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>62.3</v>
+        <v>62.67</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>80.54000000000001</v>
+        <v>81.02</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>81</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>95.54000000000001</v>
+        <v>96.11</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
     </row>
@@ -4886,10 +4886,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>68.04000000000001</v>
+        <v>68.45</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>84.14</v>
+        <v>84.64</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
     </row>
@@ -4906,10 +4906,10 @@
         <v>39.08</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>43.68</v>
+        <v>43.94</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>49.27</v>
+        <v>49.56</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
     </row>
@@ -4926,10 +4926,10 @@
         <v>55.4</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>56.3</v>
+        <v>56.63</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>69.63</v>
+        <v>70.05</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
     </row>
@@ -4946,10 +4946,10 @@
         <v>49.88</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>55.23</v>
+        <v>55.56</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>62.51</v>
+        <v>62.88</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
     </row>
@@ -4966,10 +4966,10 @@
         <v>23.5</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>29.72</v>
+        <v>29.9</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>29.36</v>
+        <v>29.54</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
     </row>
@@ -4986,10 +4986,10 @@
         <v>20.68</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>28.46</v>
+        <v>28.63</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>25.79</v>
+        <v>25.94</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
     </row>
@@ -5006,10 +5006,10 @@
         <v>24.89</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>27.19</v>
+        <v>27.36</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>30.98</v>
+        <v>31.16</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
     </row>
@@ -5026,10 +5026,10 @@
         <v>32.84</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>37.71</v>
+        <v>37.94</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>40.79</v>
+        <v>41.04</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
     </row>
@@ -5046,10 +5046,10 @@
         <v>62.46</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>61.3</v>
+        <v>61.67</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.86</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
     </row>
@@ -5066,10 +5066,10 @@
         <v>114.98</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>90.04000000000001</v>
+        <v>90.58</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>142.14</v>
+        <v>142.99</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
     </row>
@@ -5086,10 +5086,10 @@
         <v>107.95</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>108.42</v>
+        <v>109.07</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>133.12</v>
+        <v>133.92</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
     </row>
@@ -5106,10 +5106,10 @@
         <v>126.87</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>112.79</v>
+        <v>113.46</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>156.01</v>
+        <v>156.95</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
     </row>
@@ -5126,10 +5126,10 @@
         <v>55.18</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>57.63</v>
+        <v>57.98</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>67.66</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
     </row>
@@ -5146,10 +5146,10 @@
         <v>33.73</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>41.24</v>
+        <v>41.49</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
     </row>
@@ -5166,10 +5166,10 @@
         <v>15.09</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>22.48</v>
+        <v>22.61</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>18.37</v>
+        <v>18.48</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
     </row>
@@ -5186,10 +5186,10 @@
         <v>40.78</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>42.46</v>
+        <v>42.72</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>49.45</v>
+        <v>49.74</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
     </row>
@@ -5206,10 +5206,10 @@
         <v>30.8</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>38.91</v>
+        <v>39.15</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>37.19</v>
+        <v>37.41</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
     </row>
@@ -5226,10 +5226,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>72.91</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>89.92</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
     </row>
@@ -5246,10 +5246,10 @@
         <v>48.54</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>64.48</v>
+        <v>64.86</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>57.78</v>
+        <v>58.12</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
     </row>
@@ -5266,10 +5266,10 @@
         <v>56.47</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>64.73999999999999</v>
+        <v>65.13</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>66.73999999999999</v>
+        <v>67.14</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
     </row>
@@ -5286,10 +5286,10 @@
         <v>168.15</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>166.25</v>
+        <v>167.25</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>197.55</v>
+        <v>198.74</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
     </row>
@@ -5306,10 +5306,10 @@
         <v>264.24</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>272.88</v>
+        <v>274.51</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>308.62</v>
+        <v>310.47</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
     </row>
@@ -5326,10 +5326,10 @@
         <v>375.96</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>344.25</v>
+        <v>346.32</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>436.52</v>
+        <v>439.14</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
     </row>
@@ -5346,10 +5346,10 @@
         <v>432</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>392.76</v>
+        <v>395.12</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>498.54</v>
+        <v>501.53</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
     </row>
@@ -5366,10 +5366,10 @@
         <v>137.33</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>138.8</v>
+        <v>139.64</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>157.52</v>
+        <v>158.47</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
     </row>
@@ -5386,10 +5386,10 @@
         <v>130.9</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>127.43</v>
+        <v>128.2</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>149.24</v>
+        <v>150.14</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
     </row>
@@ -5406,10 +5406,10 @@
         <v>97.36</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>112.07</v>
+        <v>112.74</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>110.32</v>
+        <v>110.98</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
     </row>
@@ -5426,10 +5426,10 @@
         <v>58.3</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>66.03</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>65.66</v>
+        <v>66.05</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
     </row>
@@ -5446,10 +5446,10 @@
         <v>11.57</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>35.02</v>
+        <v>35.23</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>12.95</v>
+        <v>13.03</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
     </row>
@@ -5466,10 +5466,10 @@
         <v>32.05</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>53.59</v>
+        <v>53.91</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>35.72</v>
+        <v>35.93</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
     </row>
@@ -5486,10 +5486,10 @@
         <v>55.29</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>64.36</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>61.34</v>
+        <v>61.71</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
     </row>
@@ -5506,10 +5506,10 @@
         <v>54.59</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>68.5</v>
+        <v>68.91</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>60.29</v>
+        <v>60.65</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
     </row>
@@ -5526,10 +5526,10 @@
         <v>86.78</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>92.09</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>95.56999999999999</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
     </row>
@@ -5546,10 +5546,10 @@
         <v>145.97</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>139.64</v>
+        <v>140.47</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>160.3</v>
+        <v>161.26</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
     </row>
@@ -5566,10 +5566,10 @@
         <v>85.79000000000001</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>59.71</v>
+        <v>60.07</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>93.95</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
     </row>
@@ -5586,10 +5586,10 @@
         <v>76.38</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>60.23</v>
+        <v>60.59</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>83.31999999999999</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
     </row>
@@ -5606,10 +5606,10 @@
         <v>80.04000000000001</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>70.27</v>
+        <v>70.69</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>86.98</v>
+        <v>87.5</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
     </row>
@@ -5626,10 +5626,10 @@
         <v>28.16</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>28.48</v>
+        <v>28.65</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>30.49</v>
+        <v>30.67</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
     </row>
@@ -5646,10 +5646,10 @@
         <v>15.14</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>18.57</v>
+        <v>18.68</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>16.36</v>
+        <v>16.45</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
     </row>
@@ -5666,10 +5666,10 @@
         <v>31.79</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>37.67</v>
+        <v>37.89</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>34.27</v>
+        <v>34.48</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
     </row>
@@ -5686,10 +5686,10 @@
         <v>25.23</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>27.21</v>
+        <v>27.37</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>27.14</v>
+        <v>27.31</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
     </row>
@@ -5706,10 +5706,10 @@
         <v>17.65</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>23.7</v>
+        <v>23.84</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>18.93</v>
+        <v>19.04</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
     </row>
@@ -5726,10 +5726,10 @@
         <v>133.13</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>88.68000000000001</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>142.34</v>
+        <v>143.2</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
     </row>
@@ -5746,10 +5746,10 @@
         <v>46.25</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>55.42</v>
+        <v>55.75</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>49.3</v>
+        <v>49.59</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
     </row>
@@ -5766,10 +5766,10 @@
         <v>80.23</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>90.08</v>
+        <v>90.62</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>85.22</v>
+        <v>85.73</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
     </row>
@@ -5786,10 +5786,10 @@
         <v>146.58</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>140.75</v>
+        <v>141.6</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>155.16</v>
+        <v>156.09</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
     </row>
@@ -5806,10 +5806,10 @@
         <v>198.82</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>173.24</v>
+        <v>174.28</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>209.73</v>
+        <v>210.99</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
     </row>
@@ -5826,10 +5826,10 @@
         <v>191.83</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>157.21</v>
+        <v>158.15</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>202.21</v>
+        <v>203.42</v>
       </c>
       <c r="F254" s="7" t="inlineStr"/>
     </row>
@@ -5846,10 +5846,10 @@
         <v>216.14</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>151.05</v>
+        <v>151.95</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>227.67</v>
+        <v>229.03</v>
       </c>
       <c r="F255" s="7" t="inlineStr"/>
     </row>
@@ -5866,10 +5866,10 @@
         <v>26.5</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>18.3</v>
+        <v>18.41</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>27.89</v>
+        <v>28.06</v>
       </c>
       <c r="F256" s="7" t="inlineStr"/>
     </row>
@@ -5886,10 +5886,10 @@
         <v>10.18</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>21.42</v>
+        <v>21.54</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>10.71</v>
+        <v>10.77</v>
       </c>
       <c r="F257" s="7" t="inlineStr"/>
     </row>
@@ -5906,10 +5906,10 @@
         <v>52.94</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>67.36</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>55.65</v>
+        <v>55.98</v>
       </c>
       <c r="F258" s="7" t="inlineStr"/>
     </row>
@@ -5926,10 +5926,10 @@
         <v>39.93</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>54.89</v>
+        <v>55.22</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>41.95</v>
+        <v>42.2</v>
       </c>
       <c r="F259" s="7" t="inlineStr"/>
     </row>
@@ -5946,10 +5946,10 @@
         <v>23.72</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>50.64</v>
+        <v>50.94</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>24.84</v>
+        <v>24.99</v>
       </c>
       <c r="F260" s="7" t="inlineStr"/>
     </row>
@@ -5966,10 +5966,10 @@
         <v>76.73</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>71.56999999999999</v>
+        <v>72</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>80.11</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F261" s="7" t="inlineStr"/>
     </row>
@@ -5986,10 +5986,10 @@
         <v>62.93</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>64.28</v>
+        <v>64.66</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>65.51000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F262" s="7" t="inlineStr"/>
     </row>
@@ -6006,10 +6006,10 @@
         <v>70.56</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>77.63</v>
+        <v>78.09</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>73.27</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="F263" s="7" t="inlineStr"/>
     </row>
@@ -6026,10 +6026,10 @@
         <v>93.92</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>80.84</v>
+        <v>81.33</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>97.28</v>
+        <v>97.86</v>
       </c>
       <c r="F264" s="7" t="inlineStr"/>
     </row>
@@ -6046,10 +6046,10 @@
         <v>463.18</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>273.39</v>
+        <v>275.03</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>478.57</v>
+        <v>481.44</v>
       </c>
       <c r="F265" s="7" t="inlineStr"/>
     </row>
@@ -6066,10 +6066,10 @@
         <v>107.96</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>84.48999999999999</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>111.06</v>
+        <v>111.72</v>
       </c>
       <c r="F266" s="7" t="inlineStr"/>
     </row>
@@ -6086,10 +6086,10 @@
         <v>107.79</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>95.45</v>
+        <v>96.02</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>110.4</v>
+        <v>111.06</v>
       </c>
       <c r="F267" s="7" t="inlineStr"/>
     </row>
@@ -6106,10 +6106,10 @@
         <v>61.8</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>56.36</v>
+        <v>56.7</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>63.02</v>
+        <v>63.4</v>
       </c>
       <c r="F268" s="7" t="inlineStr"/>
     </row>
@@ -6126,10 +6126,10 @@
         <v>45.13</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>52.28</v>
+        <v>52.6</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>45.93</v>
+        <v>46.21</v>
       </c>
       <c r="F269" s="7" t="inlineStr"/>
     </row>
@@ -6146,10 +6146,10 @@
         <v>13.79</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>32.42</v>
+        <v>32.62</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>14.01</v>
+        <v>14.09</v>
       </c>
       <c r="F270" s="7" t="inlineStr"/>
     </row>
@@ -6166,10 +6166,10 @@
         <v>16.99</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>27.89</v>
+        <v>28.06</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>17.22</v>
+        <v>17.33</v>
       </c>
       <c r="F271" s="7" t="inlineStr"/>
     </row>
@@ -6186,10 +6186,10 @@
         <v>43.74</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>38.9</v>
+        <v>39.14</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>44.14</v>
+        <v>44.4</v>
       </c>
       <c r="F272" s="7" t="inlineStr"/>
     </row>
@@ -6206,10 +6206,10 @@
         <v>40.2</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>45.26</v>
+        <v>45.54</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>40.38</v>
+        <v>40.62</v>
       </c>
       <c r="F273" s="7" t="inlineStr"/>
     </row>
@@ -6226,10 +6226,10 @@
         <v>44.69</v>
       </c>
       <c r="D274" s="5" t="n">
-        <v>44.74</v>
+        <v>45.01</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>44.69</v>
+        <v>44.96</v>
       </c>
       <c r="F274" s="7" t="inlineStr"/>
     </row>
@@ -6246,10 +6246,10 @@
         <v>37.67</v>
       </c>
       <c r="D275" s="5" t="n">
-        <v>35.68</v>
+        <v>35.82</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>37.67</v>
+        <v>37.82</v>
       </c>
       <c r="F275" s="7" t="inlineStr"/>
     </row>
@@ -6266,10 +6266,10 @@
         <v>73.73999999999999</v>
       </c>
       <c r="D276" s="5" t="n">
-        <v>64.77</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>73.73999999999999</v>
+        <v>73.89</v>
       </c>
       <c r="F276" s="7" t="inlineStr"/>
     </row>
@@ -6292,6 +6292,26 @@
         <v>78.04000000000001</v>
       </c>
       <c r="F277" s="7" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B278" s="5" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="D278" s="5" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="F278" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6304,7 +6324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E277"/>
+  <dimension ref="A1:E278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6354,10 +6374,10 @@
         <v>32.99</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>47.61</v>
+        <v>47.9</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>61.31</v>
+        <v>61.68</v>
       </c>
     </row>
     <row r="3">
@@ -6373,10 +6393,10 @@
         <v>23.45</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>37.38</v>
+        <v>37.6</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>43.5</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="4">
@@ -6392,10 +6412,10 @@
         <v>25.19</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>38.38</v>
+        <v>38.61</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>46.64</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="5">
@@ -6411,10 +6431,10 @@
         <v>25.19</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>38.33</v>
+        <v>38.56</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>46.56</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="6">
@@ -6430,10 +6450,10 @@
         <v>26.23</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>39.08</v>
+        <v>39.31</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>48.39</v>
+        <v>48.68</v>
       </c>
     </row>
     <row r="7">
@@ -6449,10 +6469,10 @@
         <v>34.01</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>45.99</v>
+        <v>46.26</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>62.64</v>
+        <v>63.01</v>
       </c>
     </row>
     <row r="8">
@@ -6468,10 +6488,10 @@
         <v>30.37</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>41.35</v>
+        <v>41.6</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>55.77</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="9">
@@ -6487,10 +6507,10 @@
         <v>48.76</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>70.70999999999999</v>
+        <v>71.13</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>89.27</v>
+        <v>89.81</v>
       </c>
     </row>
     <row r="10">
@@ -6506,10 +6526,10 @@
         <v>28.54</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>39.21</v>
+        <v>39.45</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>52.1</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="11">
@@ -6525,10 +6545,10 @@
         <v>36.99</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>53.7</v>
+        <v>54.02</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>67.42</v>
+        <v>67.83</v>
       </c>
     </row>
     <row r="12">
@@ -6544,10 +6564,10 @@
         <v>39.67</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>56.94</v>
+        <v>57.29</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>72.19</v>
+        <v>72.63</v>
       </c>
     </row>
     <row r="13">
@@ -6563,10 +6583,10 @@
         <v>34.73</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>52.02</v>
+        <v>52.33</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>63.11</v>
+        <v>63.48</v>
       </c>
     </row>
     <row r="14">
@@ -6582,10 +6602,10 @@
         <v>43.7</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>56.92</v>
+        <v>57.26</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>79.3</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="15">
@@ -6601,10 +6621,10 @@
         <v>27.37</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>40.86</v>
+        <v>41.11</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>49.6</v>
+        <v>49.89</v>
       </c>
     </row>
     <row r="16">
@@ -6620,10 +6640,10 @@
         <v>31.48</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>49.22</v>
+        <v>49.52</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>56.97</v>
+        <v>57.31</v>
       </c>
     </row>
     <row r="17">
@@ -6639,10 +6659,10 @@
         <v>70.45</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>81.01000000000001</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>127.16</v>
+        <v>127.93</v>
       </c>
     </row>
     <row r="18">
@@ -6658,10 +6678,10 @@
         <v>44.55</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>64.2</v>
+        <v>64.59</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>80.20999999999999</v>
+        <v>80.69</v>
       </c>
     </row>
     <row r="19">
@@ -6677,10 +6697,10 @@
         <v>33</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>49.13</v>
+        <v>49.43</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>59.26</v>
+        <v>59.62</v>
       </c>
     </row>
     <row r="20">
@@ -6696,10 +6716,10 @@
         <v>29.72</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>40.93</v>
+        <v>41.17</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>53.25</v>
+        <v>53.57</v>
       </c>
     </row>
     <row r="21">
@@ -6715,10 +6735,10 @@
         <v>27.43</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>39.03</v>
+        <v>39.26</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>49.04</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="22">
@@ -6734,10 +6754,10 @@
         <v>21.15</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>33.36</v>
+        <v>33.56</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>37.73</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="23">
@@ -6753,10 +6773,10 @@
         <v>37.8</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>54.53</v>
+        <v>54.86</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>67.3</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="24">
@@ -6772,10 +6792,10 @@
         <v>29.2</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>43.64</v>
+        <v>43.9</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>51.88</v>
+        <v>52.19</v>
       </c>
     </row>
     <row r="25">
@@ -6791,10 +6811,10 @@
         <v>27.29</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>41.74</v>
+        <v>41.99</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>48.39</v>
+        <v>48.68</v>
       </c>
     </row>
     <row r="26">
@@ -6810,10 +6830,10 @@
         <v>32.37</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>46.86</v>
+        <v>47.14</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>57.21</v>
+        <v>57.56</v>
       </c>
     </row>
     <row r="27">
@@ -6829,10 +6849,10 @@
         <v>40.25</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>52.85</v>
+        <v>53.17</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>70.91</v>
+        <v>71.33</v>
       </c>
     </row>
     <row r="28">
@@ -6848,10 +6868,10 @@
         <v>37.44</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>51.17</v>
+        <v>51.47</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>65.73999999999999</v>
+        <v>66.13</v>
       </c>
     </row>
     <row r="29">
@@ -6867,10 +6887,10 @@
         <v>28.49</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>39.68</v>
+        <v>39.92</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>49.94</v>
+        <v>50.24</v>
       </c>
     </row>
     <row r="30">
@@ -6886,10 +6906,10 @@
         <v>46.39</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>53.72</v>
+        <v>54.04</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>81.17</v>
+        <v>81.66</v>
       </c>
     </row>
     <row r="31">
@@ -6905,10 +6925,10 @@
         <v>49.23</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>59.81</v>
+        <v>60.17</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>86</v>
+        <v>86.51000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -6924,10 +6944,10 @@
         <v>88.63</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>93.08</v>
+        <v>93.64</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>154.38</v>
+        <v>155.3</v>
       </c>
     </row>
     <row r="33">
@@ -6943,10 +6963,10 @@
         <v>105.51</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>97.27</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>183.26</v>
+        <v>184.36</v>
       </c>
     </row>
     <row r="34">
@@ -6962,10 +6982,10 @@
         <v>29.33</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>40.46</v>
+        <v>40.7</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>50.8</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="35">
@@ -6981,10 +7001,10 @@
         <v>27.86</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>38.92</v>
+        <v>39.15</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>48</v>
+        <v>48.29</v>
       </c>
     </row>
     <row r="36">
@@ -7000,10 +7020,10 @@
         <v>37.94</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>48.42</v>
+        <v>48.71</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>65.02</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="37">
@@ -7019,10 +7039,10 @@
         <v>42.49</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>59.01</v>
+        <v>59.36</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>72.44</v>
+        <v>72.88</v>
       </c>
     </row>
     <row r="38">
@@ -7038,10 +7058,10 @@
         <v>71.86</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>80.23999999999999</v>
+        <v>80.72</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>122.16</v>
+        <v>122.89</v>
       </c>
     </row>
     <row r="39">
@@ -7057,10 +7077,10 @@
         <v>39.11</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>54.59</v>
+        <v>54.92</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>66.29000000000001</v>
+        <v>66.69</v>
       </c>
     </row>
     <row r="40">
@@ -7076,10 +7096,10 @@
         <v>38.91</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>52.05</v>
+        <v>52.36</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>65.76000000000001</v>
+        <v>66.15000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -7095,10 +7115,10 @@
         <v>34.69</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>46.76</v>
+        <v>47.04</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>58.65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42">
@@ -7114,10 +7134,10 @@
         <v>42.78</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>55.32</v>
+        <v>55.65</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>72.34999999999999</v>
+        <v>72.79000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -7133,10 +7153,10 @@
         <v>28.32</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>37.7</v>
+        <v>37.92</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>47.91</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="44">
@@ -7152,10 +7172,10 @@
         <v>165.37</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>154.7</v>
+        <v>155.63</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>279.71</v>
+        <v>281.39</v>
       </c>
     </row>
     <row r="45">
@@ -7171,10 +7191,10 @@
         <v>69.13</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>80.22</v>
+        <v>80.7</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>116.9</v>
+        <v>117.6</v>
       </c>
     </row>
     <row r="46">
@@ -7190,10 +7210,10 @@
         <v>74.84999999999999</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>90.06999999999999</v>
+        <v>90.61</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>126.53</v>
+        <v>127.29</v>
       </c>
     </row>
     <row r="47">
@@ -7209,10 +7229,10 @@
         <v>81.62</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>114.08</v>
+        <v>114.76</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>137.41</v>
+        <v>138.24</v>
       </c>
     </row>
     <row r="48">
@@ -7228,10 +7248,10 @@
         <v>75.48999999999999</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>105.03</v>
+        <v>105.66</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>126.58</v>
+        <v>127.34</v>
       </c>
     </row>
     <row r="49">
@@ -7247,10 +7267,10 @@
         <v>218.05</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>239.27</v>
+        <v>240.71</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>364.13</v>
+        <v>366.32</v>
       </c>
     </row>
     <row r="50">
@@ -7266,10 +7286,10 @@
         <v>115.22</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>142.54</v>
+        <v>143.39</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>191.97</v>
+        <v>193.12</v>
       </c>
     </row>
     <row r="51">
@@ -7285,10 +7305,10 @@
         <v>50.83</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>69.37</v>
+        <v>69.78</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>84.5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52">
@@ -7304,10 +7324,10 @@
         <v>55.04</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>73.94</v>
+        <v>74.38</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>91.28</v>
+        <v>91.83</v>
       </c>
     </row>
     <row r="53">
@@ -7323,10 +7343,10 @@
         <v>45.32</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>58.71</v>
+        <v>59.06</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>74.93000000000001</v>
+        <v>75.38</v>
       </c>
     </row>
     <row r="54">
@@ -7342,10 +7362,10 @@
         <v>54.55</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>70.43000000000001</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>89.91</v>
+        <v>90.45</v>
       </c>
     </row>
     <row r="55">
@@ -7361,10 +7381,10 @@
         <v>62.08</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>73.59999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>102.01</v>
+        <v>102.62</v>
       </c>
     </row>
     <row r="56">
@@ -7380,10 +7400,10 @@
         <v>55.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>66.04000000000001</v>
+        <v>66.44</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>90.16</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="57">
@@ -7399,10 +7419,10 @@
         <v>52.11</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>60.07</v>
+        <v>60.43</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>84.87</v>
+        <v>85.38</v>
       </c>
     </row>
     <row r="58">
@@ -7418,10 +7438,10 @@
         <v>84.56999999999999</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>84.54000000000001</v>
+        <v>85.05</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>137.13</v>
+        <v>137.95</v>
       </c>
     </row>
     <row r="59">
@@ -7437,10 +7457,10 @@
         <v>50.14</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>64.31999999999999</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>80.91</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -7456,10 +7476,10 @@
         <v>64.59</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>86.77</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>103.73</v>
+        <v>104.35</v>
       </c>
     </row>
     <row r="61">
@@ -7475,10 +7495,10 @@
         <v>52.09</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>67.19</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>83.26000000000001</v>
+        <v>83.75</v>
       </c>
     </row>
     <row r="62">
@@ -7494,10 +7514,10 @@
         <v>60.12</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>68.53</v>
+        <v>68.94</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>95.72</v>
+        <v>96.29000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -7513,10 +7533,10 @@
         <v>50.92</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>64.88</v>
+        <v>65.27</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>80.76000000000001</v>
+        <v>81.23999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -7532,10 +7552,10 @@
         <v>47.77</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>57.86</v>
+        <v>58.2</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>75.47</v>
+        <v>75.93000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -7551,10 +7571,10 @@
         <v>51.76</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>62.27</v>
+        <v>62.64</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>81.87</v>
+        <v>82.36</v>
       </c>
     </row>
     <row r="66">
@@ -7570,10 +7590,10 @@
         <v>45.33</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>54.72</v>
+        <v>55.05</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>71.77</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="67">
@@ -7589,10 +7609,10 @@
         <v>27.82</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>35.65</v>
+        <v>35.86</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>44.1</v>
+        <v>44.36</v>
       </c>
     </row>
     <row r="68">
@@ -7608,10 +7628,10 @@
         <v>248.2</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>198.92</v>
+        <v>200.11</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>393.28</v>
+        <v>395.64</v>
       </c>
     </row>
     <row r="69">
@@ -7627,10 +7647,10 @@
         <v>44.74</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>52.9</v>
+        <v>53.22</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>70.87</v>
+        <v>71.29000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -7646,10 +7666,10 @@
         <v>32.56</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>40.01</v>
+        <v>40.25</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>51.55</v>
+        <v>51.86</v>
       </c>
     </row>
     <row r="71">
@@ -7665,10 +7685,10 @@
         <v>49.27</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>58.96</v>
+        <v>59.32</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>77.88</v>
+        <v>78.34999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -7684,10 +7704,10 @@
         <v>37.87</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>49.63</v>
+        <v>49.93</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>59.76</v>
+        <v>60.12</v>
       </c>
     </row>
     <row r="73">
@@ -7703,10 +7723,10 @@
         <v>37.13</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>47.38</v>
+        <v>47.66</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>58.5</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="74">
@@ -7722,10 +7742,10 @@
         <v>32.55</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>42.15</v>
+        <v>42.41</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>51.12</v>
+        <v>51.43</v>
       </c>
     </row>
     <row r="75">
@@ -7741,10 +7761,10 @@
         <v>28.02</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>35.13</v>
+        <v>35.34</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>43.87</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="76">
@@ -7760,10 +7780,10 @@
         <v>27.43</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>35.8</v>
+        <v>36.02</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>42.81</v>
+        <v>43.07</v>
       </c>
     </row>
     <row r="77">
@@ -7779,10 +7799,10 @@
         <v>31.55</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>39.82</v>
+        <v>40.06</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>49.15</v>
+        <v>49.45</v>
       </c>
     </row>
     <row r="78">
@@ -7798,10 +7818,10 @@
         <v>44.98</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>50.44</v>
+        <v>50.74</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>69.95</v>
+        <v>70.37</v>
       </c>
     </row>
     <row r="79">
@@ -7817,10 +7837,10 @@
         <v>29.49</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>36.5</v>
+        <v>36.72</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>45.78</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="80">
@@ -7836,10 +7856,10 @@
         <v>114.74</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>94.33</v>
+        <v>94.89</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>177.58</v>
+        <v>178.64</v>
       </c>
     </row>
     <row r="81">
@@ -7855,10 +7875,10 @@
         <v>124.09</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>104.78</v>
+        <v>105.4</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>191.45</v>
+        <v>192.6</v>
       </c>
     </row>
     <row r="82">
@@ -7874,10 +7894,10 @@
         <v>27.11</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>35.16</v>
+        <v>35.37</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>41.7</v>
+        <v>41.95</v>
       </c>
     </row>
     <row r="83">
@@ -7893,10 +7913,10 @@
         <v>131.25</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>109.85</v>
+        <v>110.5</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>201.47</v>
+        <v>202.68</v>
       </c>
     </row>
     <row r="84">
@@ -7912,10 +7932,10 @@
         <v>34.97</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>46.71</v>
+        <v>46.99</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>53.57</v>
+        <v>53.89</v>
       </c>
     </row>
     <row r="85">
@@ -7931,10 +7951,10 @@
         <v>36.19</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>48.01</v>
+        <v>48.29</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>55.33</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="86">
@@ -7950,10 +7970,10 @@
         <v>30.36</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>40.65</v>
+        <v>40.89</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>46.3</v>
+        <v>46.58</v>
       </c>
     </row>
     <row r="87">
@@ -7969,10 +7989,10 @@
         <v>30.73</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>41.16</v>
+        <v>41.4</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>46.76</v>
+        <v>47.04</v>
       </c>
     </row>
     <row r="88">
@@ -7988,10 +8008,10 @@
         <v>24.89</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>33.58</v>
+        <v>33.78</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>37.78</v>
+        <v>38.01</v>
       </c>
     </row>
     <row r="89">
@@ -8007,10 +8027,10 @@
         <v>24.65</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>31.56</v>
+        <v>31.75</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>37.37</v>
+        <v>37.59</v>
       </c>
     </row>
     <row r="90">
@@ -8026,10 +8046,10 @@
         <v>21.04</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>27.89</v>
+        <v>28.06</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>31.85</v>
+        <v>32.05</v>
       </c>
     </row>
     <row r="91">
@@ -8045,10 +8065,10 @@
         <v>18.96</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>24.98</v>
+        <v>25.13</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>28.67</v>
+        <v>28.84</v>
       </c>
     </row>
     <row r="92">
@@ -8064,10 +8084,10 @@
         <v>66.16</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>61.78</v>
+        <v>62.15</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>99.52</v>
+        <v>100.12</v>
       </c>
     </row>
     <row r="93">
@@ -8083,10 +8103,10 @@
         <v>59.69</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>60.55</v>
+        <v>60.92</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>89.33</v>
+        <v>89.87</v>
       </c>
     </row>
     <row r="94">
@@ -8102,10 +8122,10 @@
         <v>28.62</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>37.17</v>
+        <v>37.39</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>42.62</v>
+        <v>42.87</v>
       </c>
     </row>
     <row r="95">
@@ -8121,10 +8141,10 @@
         <v>28.26</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>38</v>
+        <v>38.23</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>41.95</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="96">
@@ -8140,10 +8160,10 @@
         <v>40.58</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>50.84</v>
+        <v>51.14</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>60.06</v>
+        <v>60.42</v>
       </c>
     </row>
     <row r="97">
@@ -8159,10 +8179,10 @@
         <v>33.89</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>41.19</v>
+        <v>41.44</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="98">
@@ -8178,10 +8198,10 @@
         <v>37.84</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>43.42</v>
+        <v>43.68</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>55.72</v>
+        <v>56.05</v>
       </c>
     </row>
     <row r="99">
@@ -8197,10 +8217,10 @@
         <v>35.44</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>44.01</v>
+        <v>44.28</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>52.08</v>
+        <v>52.39</v>
       </c>
     </row>
     <row r="100">
@@ -8216,10 +8236,10 @@
         <v>31.61</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>39.57</v>
+        <v>39.81</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>46.36</v>
+        <v>46.64</v>
       </c>
     </row>
     <row r="101">
@@ -8235,10 +8255,10 @@
         <v>29</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>34.63</v>
+        <v>34.84</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>42.53</v>
+        <v>42.79</v>
       </c>
     </row>
     <row r="102">
@@ -8254,10 +8274,10 @@
         <v>30.77</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>38.98</v>
+        <v>39.22</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>45.13</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="103">
@@ -8273,10 +8293,10 @@
         <v>25.62</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>32.53</v>
+        <v>32.73</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>37.58</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="104">
@@ -8292,10 +8312,10 @@
         <v>29.13</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>35.24</v>
+        <v>35.45</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>42.72</v>
+        <v>42.97</v>
       </c>
     </row>
     <row r="105">
@@ -8311,10 +8331,10 @@
         <v>30.01</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>37.9</v>
+        <v>38.13</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>44</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="106">
@@ -8330,10 +8350,10 @@
         <v>27.89</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>34.74</v>
+        <v>34.95</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>40.88</v>
+        <v>41.13</v>
       </c>
     </row>
     <row r="107">
@@ -8349,10 +8369,10 @@
         <v>36.3</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>46.84</v>
+        <v>47.12</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>53.12</v>
+        <v>53.44</v>
       </c>
     </row>
     <row r="108">
@@ -8368,10 +8388,10 @@
         <v>30.09</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>38.83</v>
+        <v>39.06</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>43.96</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="109">
@@ -8387,10 +8407,10 @@
         <v>42.66</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>53.59</v>
+        <v>53.91</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>62.21</v>
+        <v>62.58</v>
       </c>
     </row>
     <row r="110">
@@ -8406,10 +8426,10 @@
         <v>90.05</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>106.64</v>
+        <v>107.28</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>130.72</v>
+        <v>131.51</v>
       </c>
     </row>
     <row r="111">
@@ -8425,10 +8445,10 @@
         <v>58.79</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>80.58</v>
+        <v>81.06</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>84.95999999999999</v>
+        <v>85.47</v>
       </c>
     </row>
     <row r="112">
@@ -8444,10 +8464,10 @@
         <v>60.96</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>76.94</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>87.7</v>
+        <v>88.23</v>
       </c>
     </row>
     <row r="113">
@@ -8463,10 +8483,10 @@
         <v>55</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>73.7</v>
+        <v>74.14</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>79.06</v>
+        <v>79.53</v>
       </c>
     </row>
     <row r="114">
@@ -8482,10 +8502,10 @@
         <v>108.73</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>110.85</v>
+        <v>111.51</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>156.16</v>
+        <v>157.1</v>
       </c>
     </row>
     <row r="115">
@@ -8501,10 +8521,10 @@
         <v>58.92</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>74.88</v>
+        <v>75.33</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>84.55</v>
+        <v>85.06</v>
       </c>
     </row>
     <row r="116">
@@ -8520,10 +8540,10 @@
         <v>65.31</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>77.79000000000001</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>93.62</v>
+        <v>94.18000000000001</v>
       </c>
     </row>
     <row r="117">
@@ -8539,10 +8559,10 @@
         <v>59.78</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>76.73</v>
+        <v>77.19</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>85.59</v>
+        <v>86.11</v>
       </c>
     </row>
     <row r="118">
@@ -8558,10 +8578,10 @@
         <v>60.03</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>74.81</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>85.84999999999999</v>
+        <v>86.37</v>
       </c>
     </row>
     <row r="119">
@@ -8577,10 +8597,10 @@
         <v>53.46</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>71.45</v>
+        <v>71.88</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>76.36</v>
+        <v>76.81999999999999</v>
       </c>
     </row>
     <row r="120">
@@ -8596,10 +8616,10 @@
         <v>61.01</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>78.25</v>
+        <v>78.72</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>87.03</v>
+        <v>87.56</v>
       </c>
     </row>
     <row r="121">
@@ -8615,10 +8635,10 @@
         <v>70.51000000000001</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>86.77</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>100.46</v>
+        <v>101.06</v>
       </c>
     </row>
     <row r="122">
@@ -8634,10 +8654,10 @@
         <v>62.4</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>82.8</v>
+        <v>83.3</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>88.55</v>
+        <v>89.08</v>
       </c>
     </row>
     <row r="123">
@@ -8653,10 +8673,10 @@
         <v>57.79</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>76.48999999999999</v>
+        <v>76.95</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>81.67</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="124">
@@ -8672,10 +8692,10 @@
         <v>52.11</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>69.31999999999999</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>73.34999999999999</v>
+        <v>73.79000000000001</v>
       </c>
     </row>
     <row r="125">
@@ -8691,10 +8711,10 @@
         <v>51.91</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>69.47</v>
+        <v>69.88</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>72.89</v>
+        <v>73.33</v>
       </c>
     </row>
     <row r="126">
@@ -8710,10 +8730,10 @@
         <v>49.47</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>65.51000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>69.3</v>
+        <v>69.72</v>
       </c>
     </row>
     <row r="127">
@@ -8729,10 +8749,10 @@
         <v>57.51</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>70.34</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>80.37</v>
+        <v>80.86</v>
       </c>
     </row>
     <row r="128">
@@ -8748,10 +8768,10 @@
         <v>105.62</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>101.03</v>
+        <v>101.63</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>147.32</v>
+        <v>148.2</v>
       </c>
     </row>
     <row r="129">
@@ -8767,10 +8787,10 @@
         <v>51.64</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>68.56</v>
+        <v>68.97</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>71.89</v>
+        <v>72.31999999999999</v>
       </c>
     </row>
     <row r="130">
@@ -8786,10 +8806,10 @@
         <v>50.99</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>63.85</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>70.84</v>
+        <v>71.27</v>
       </c>
     </row>
     <row r="131">
@@ -8805,10 +8825,10 @@
         <v>46.48</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>60.74</v>
+        <v>61.1</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>64.47</v>
+        <v>64.84999999999999</v>
       </c>
     </row>
     <row r="132">
@@ -8824,10 +8844,10 @@
         <v>53.42</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>66.73999999999999</v>
+        <v>67.14</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>73.97</v>
+        <v>74.41</v>
       </c>
     </row>
     <row r="133">
@@ -8843,10 +8863,10 @@
         <v>53.9</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>67.97</v>
+        <v>68.38</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>74.51000000000001</v>
+        <v>74.95999999999999</v>
       </c>
     </row>
     <row r="134">
@@ -8862,10 +8882,10 @@
         <v>43.69</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>53.27</v>
+        <v>53.59</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>60.31</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="135">
@@ -8881,10 +8901,10 @@
         <v>40.67</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>47.57</v>
+        <v>47.86</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>56.06</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="136">
@@ -8900,10 +8920,10 @@
         <v>42.07</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>49.91</v>
+        <v>50.21</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>57.91</v>
+        <v>58.26</v>
       </c>
     </row>
     <row r="137">
@@ -8919,10 +8939,10 @@
         <v>30.63</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>36.58</v>
+        <v>36.8</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>42.14</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="138">
@@ -8938,10 +8958,10 @@
         <v>34.46</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>39.26</v>
+        <v>39.5</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>47.38</v>
+        <v>47.66</v>
       </c>
     </row>
     <row r="139">
@@ -8957,10 +8977,10 @@
         <v>31.31</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>36.46</v>
+        <v>36.68</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>43.02</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="140">
@@ -8976,10 +8996,10 @@
         <v>33.61</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>35.84</v>
+        <v>36.05</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>46.15</v>
+        <v>46.43</v>
       </c>
     </row>
     <row r="141">
@@ -8995,10 +9015,10 @@
         <v>35.21</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>38.46</v>
+        <v>38.69</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>48.32</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="142">
@@ -9014,10 +9034,10 @@
         <v>31.79</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>35.39</v>
+        <v>35.61</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>43.6</v>
+        <v>43.86</v>
       </c>
     </row>
     <row r="143">
@@ -9033,10 +9053,10 @@
         <v>35.26</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>39.55</v>
+        <v>39.79</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>48.24</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="144">
@@ -9052,10 +9072,10 @@
         <v>38.41</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>40.74</v>
+        <v>40.99</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>52.42</v>
+        <v>52.74</v>
       </c>
     </row>
     <row r="145">
@@ -9071,10 +9091,10 @@
         <v>41.52</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>46.85</v>
+        <v>47.13</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>56.53</v>
+        <v>56.87</v>
       </c>
     </row>
     <row r="146">
@@ -9090,10 +9110,10 @@
         <v>42.82</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>47.26</v>
+        <v>47.54</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>58.23</v>
+        <v>58.58</v>
       </c>
     </row>
     <row r="147">
@@ -9109,10 +9129,10 @@
         <v>42.1</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>47.59</v>
+        <v>47.87</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>57.18</v>
+        <v>57.52</v>
       </c>
     </row>
     <row r="148">
@@ -9128,10 +9148,10 @@
         <v>50.84</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>60.43</v>
+        <v>60.79</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>68.95999999999999</v>
+        <v>69.37</v>
       </c>
     </row>
     <row r="149">
@@ -9147,10 +9167,10 @@
         <v>45.47</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>48.26</v>
+        <v>48.55</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>61.59</v>
+        <v>61.96</v>
       </c>
     </row>
     <row r="150">
@@ -9166,10 +9186,10 @@
         <v>45.23</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>47.24</v>
+        <v>47.53</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>61.19</v>
+        <v>61.56</v>
       </c>
     </row>
     <row r="151">
@@ -9185,10 +9205,10 @@
         <v>62.67</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>64.87</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>84.68000000000001</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -9204,10 +9224,10 @@
         <v>72.90000000000001</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>63.48</v>
+        <v>63.86</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>98.56</v>
+        <v>99.15000000000001</v>
       </c>
     </row>
     <row r="153">
@@ -9223,10 +9243,10 @@
         <v>44.52</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>47.92</v>
+        <v>48.21</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>60.23</v>
+        <v>60.59</v>
       </c>
     </row>
     <row r="154">
@@ -9242,10 +9262,10 @@
         <v>59.65</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>62.13</v>
+        <v>62.5</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>80.76000000000001</v>
+        <v>81.23999999999999</v>
       </c>
     </row>
     <row r="155">
@@ -9261,10 +9281,10 @@
         <v>61.49</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>62.02</v>
+        <v>62.4</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>83.13</v>
+        <v>83.62</v>
       </c>
     </row>
     <row r="156">
@@ -9280,10 +9300,10 @@
         <v>76.45999999999999</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>73.22</v>
+        <v>73.66</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>103.21</v>
+        <v>103.83</v>
       </c>
     </row>
     <row r="157">
@@ -9299,10 +9319,10 @@
         <v>118.54</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>125.05</v>
+        <v>125.8</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>159.78</v>
+        <v>160.74</v>
       </c>
     </row>
     <row r="158">
@@ -9318,10 +9338,10 @@
         <v>86.77</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>86.93000000000001</v>
+        <v>87.45</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>116.69</v>
+        <v>117.39</v>
       </c>
     </row>
     <row r="159">
@@ -9337,10 +9357,10 @@
         <v>55.76</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>58.01</v>
+        <v>58.36</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>74.81</v>
+        <v>75.26000000000001</v>
       </c>
     </row>
     <row r="160">
@@ -9356,10 +9376,10 @@
         <v>48.5</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>54.91</v>
+        <v>55.24</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>64.92</v>
+        <v>65.31</v>
       </c>
     </row>
     <row r="161">
@@ -9375,10 +9395,10 @@
         <v>41.02</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>44.33</v>
+        <v>44.6</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>54.81</v>
+        <v>55.14</v>
       </c>
     </row>
     <row r="162">
@@ -9394,10 +9414,10 @@
         <v>46.93</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>48.11</v>
+        <v>48.4</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>62.6</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="163">
@@ -9413,10 +9433,10 @@
         <v>37.59</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>39.81</v>
+        <v>40.05</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>50.05</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="164">
@@ -9432,10 +9452,10 @@
         <v>81.03</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>82.48</v>
+        <v>82.98</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>107.73</v>
+        <v>108.37</v>
       </c>
     </row>
     <row r="165">
@@ -9451,10 +9471,10 @@
         <v>114.18</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>114.23</v>
+        <v>114.91</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>151.57</v>
+        <v>152.48</v>
       </c>
     </row>
     <row r="166">
@@ -9470,10 +9490,10 @@
         <v>112.64</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>120.12</v>
+        <v>120.84</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>149.3</v>
+        <v>150.19</v>
       </c>
     </row>
     <row r="167">
@@ -9489,10 +9509,10 @@
         <v>123.35</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>143.32</v>
+        <v>144.18</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>163.38</v>
+        <v>164.36</v>
       </c>
     </row>
     <row r="168">
@@ -9508,10 +9528,10 @@
         <v>123.09</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>142.89</v>
+        <v>143.75</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>162.93</v>
+        <v>163.91</v>
       </c>
     </row>
     <row r="169">
@@ -9527,10 +9547,10 @@
         <v>105</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>130.3</v>
+        <v>131.08</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>138.9</v>
+        <v>139.73</v>
       </c>
     </row>
     <row r="170">
@@ -9546,10 +9566,10 @@
         <v>131.48</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>154.96</v>
+        <v>155.89</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>173.57</v>
+        <v>174.61</v>
       </c>
     </row>
     <row r="171">
@@ -9565,10 +9585,10 @@
         <v>119.74</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>135.13</v>
+        <v>135.94</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>157.75</v>
+        <v>158.7</v>
       </c>
     </row>
     <row r="172">
@@ -9584,10 +9604,10 @@
         <v>89.62</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>104.43</v>
+        <v>105.06</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>117.83</v>
+        <v>118.54</v>
       </c>
     </row>
     <row r="173">
@@ -9603,10 +9623,10 @@
         <v>82.48</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>96.17</v>
+        <v>96.75</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>108.2</v>
+        <v>108.85</v>
       </c>
     </row>
     <row r="174">
@@ -9622,10 +9642,10 @@
         <v>112.43</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>125.06</v>
+        <v>125.81</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>147.16</v>
+        <v>148.05</v>
       </c>
     </row>
     <row r="175">
@@ -9641,10 +9661,10 @@
         <v>97.75</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>110.82</v>
+        <v>111.48</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>127.66</v>
+        <v>128.43</v>
       </c>
     </row>
     <row r="176">
@@ -9660,10 +9680,10 @@
         <v>183</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>174.07</v>
+        <v>175.12</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>238.65</v>
+        <v>240.09</v>
       </c>
     </row>
     <row r="177">
@@ -9679,10 +9699,10 @@
         <v>124.33</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>126.88</v>
+        <v>127.64</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>161.91</v>
+        <v>162.88</v>
       </c>
     </row>
     <row r="178">
@@ -9698,10 +9718,10 @@
         <v>82.25</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>98.84</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>106.95</v>
+        <v>107.59</v>
       </c>
     </row>
     <row r="179">
@@ -9717,10 +9737,10 @@
         <v>87.09</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>96.16</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>113.11</v>
+        <v>113.79</v>
       </c>
     </row>
     <row r="180">
@@ -9736,10 +9756,10 @@
         <v>95.98</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>103.51</v>
+        <v>104.13</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>124.51</v>
+        <v>125.26</v>
       </c>
     </row>
     <row r="181">
@@ -9755,10 +9775,10 @@
         <v>112.11</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>121.43</v>
+        <v>122.16</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>145.26</v>
+        <v>146.13</v>
       </c>
     </row>
     <row r="182">
@@ -9774,10 +9794,10 @@
         <v>88.33</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>90.7</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>114.28</v>
+        <v>114.97</v>
       </c>
     </row>
     <row r="183">
@@ -9793,10 +9813,10 @@
         <v>102.2</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>102.29</v>
+        <v>102.9</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>132.04</v>
+        <v>132.83</v>
       </c>
     </row>
     <row r="184">
@@ -9812,10 +9832,10 @@
         <v>108.02</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>119.79</v>
+        <v>120.51</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>139.36</v>
+        <v>140.19</v>
       </c>
     </row>
     <row r="185">
@@ -9831,10 +9851,10 @@
         <v>109.7</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>128.57</v>
+        <v>129.34</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>141.28</v>
+        <v>142.13</v>
       </c>
     </row>
     <row r="186">
@@ -9850,10 +9870,10 @@
         <v>105.48</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>125.79</v>
+        <v>126.54</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>135.61</v>
+        <v>136.42</v>
       </c>
     </row>
     <row r="187">
@@ -9869,10 +9889,10 @@
         <v>113.92</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>117.81</v>
+        <v>118.51</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>146.21</v>
+        <v>147.09</v>
       </c>
     </row>
     <row r="188">
@@ -9888,10 +9908,10 @@
         <v>423.33</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>321.3</v>
+        <v>323.22</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>543.34</v>
+        <v>546.6</v>
       </c>
     </row>
     <row r="189">
@@ -9907,10 +9927,10 @@
         <v>120.86</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>142.68</v>
+        <v>143.54</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>155.13</v>
+        <v>156.06</v>
       </c>
     </row>
     <row r="190">
@@ -9926,10 +9946,10 @@
         <v>177.81</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>168.29</v>
+        <v>169.3</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>228.24</v>
+        <v>229.61</v>
       </c>
     </row>
     <row r="191">
@@ -9945,10 +9965,10 @@
         <v>106.79</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>126.11</v>
+        <v>126.87</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>136.81</v>
+        <v>137.63</v>
       </c>
     </row>
     <row r="192">
@@ -9964,10 +9984,10 @@
         <v>104.25</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>117.5</v>
+        <v>118.2</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>133.29</v>
+        <v>134.09</v>
       </c>
     </row>
     <row r="193">
@@ -9983,10 +10003,10 @@
         <v>122.01</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>129.91</v>
+        <v>130.69</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>155.69</v>
+        <v>156.62</v>
       </c>
     </row>
     <row r="194">
@@ -10002,10 +10022,10 @@
         <v>105.02</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>109.43</v>
+        <v>110.09</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>133.76</v>
+        <v>134.56</v>
       </c>
     </row>
     <row r="195">
@@ -10021,10 +10041,10 @@
         <v>130.29</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>133.42</v>
+        <v>134.22</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>165.63</v>
+        <v>166.62</v>
       </c>
     </row>
     <row r="196">
@@ -10040,10 +10060,10 @@
         <v>121.93</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>132.93</v>
+        <v>133.72</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>154.71</v>
+        <v>155.64</v>
       </c>
     </row>
     <row r="197">
@@ -10059,10 +10079,10 @@
         <v>113.03</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>127.48</v>
+        <v>128.25</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>143.09</v>
+        <v>143.95</v>
       </c>
     </row>
     <row r="198">
@@ -10078,10 +10098,10 @@
         <v>69.79000000000001</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>85.87</v>
+        <v>86.38</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>88.15000000000001</v>
+        <v>88.68000000000001</v>
       </c>
     </row>
     <row r="199">
@@ -10097,10 +10117,10 @@
         <v>77.45999999999999</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>77.37</v>
+        <v>77.83</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>97.62</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="200">
@@ -10116,10 +10136,10 @@
         <v>255.88</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>179.93</v>
+        <v>181.01</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>322.07</v>
+        <v>324</v>
       </c>
     </row>
     <row r="201">
@@ -10135,10 +10155,10 @@
         <v>55.83</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>60.73</v>
+        <v>61.1</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>70.18000000000001</v>
+        <v>70.61</v>
       </c>
     </row>
     <row r="202">
@@ -10154,10 +10174,10 @@
         <v>50.47</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>54.37</v>
+        <v>54.69</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>63.37</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="203">
@@ -10173,10 +10193,10 @@
         <v>41.9</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>44.01</v>
+        <v>44.28</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>52.95</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="204">
@@ -10192,10 +10212,10 @@
         <v>47.04</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>48.7</v>
+        <v>48.99</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>59.83</v>
+        <v>60.19</v>
       </c>
     </row>
     <row r="205">
@@ -10211,10 +10231,10 @@
         <v>62.91</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>62.3</v>
+        <v>62.67</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>80.54000000000001</v>
+        <v>81.02</v>
       </c>
     </row>
     <row r="206">
@@ -10230,10 +10250,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>81</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>95.54000000000001</v>
+        <v>96.11</v>
       </c>
     </row>
     <row r="207">
@@ -10249,10 +10269,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>68.04000000000001</v>
+        <v>68.45</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>84.14</v>
+        <v>84.64</v>
       </c>
     </row>
     <row r="208">
@@ -10268,10 +10288,10 @@
         <v>39.08</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>43.68</v>
+        <v>43.94</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>49.27</v>
+        <v>49.56</v>
       </c>
     </row>
     <row r="209">
@@ -10287,10 +10307,10 @@
         <v>55.4</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>56.3</v>
+        <v>56.63</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>69.63</v>
+        <v>70.05</v>
       </c>
     </row>
     <row r="210">
@@ -10306,10 +10326,10 @@
         <v>49.88</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>55.23</v>
+        <v>55.56</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>62.51</v>
+        <v>62.88</v>
       </c>
     </row>
     <row r="211">
@@ -10325,10 +10345,10 @@
         <v>23.5</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>29.72</v>
+        <v>29.9</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>29.36</v>
+        <v>29.54</v>
       </c>
     </row>
     <row r="212">
@@ -10344,10 +10364,10 @@
         <v>20.68</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>28.46</v>
+        <v>28.63</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>25.79</v>
+        <v>25.94</v>
       </c>
     </row>
     <row r="213">
@@ -10363,10 +10383,10 @@
         <v>24.89</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>27.19</v>
+        <v>27.36</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>30.98</v>
+        <v>31.16</v>
       </c>
     </row>
     <row r="214">
@@ -10382,10 +10402,10 @@
         <v>32.84</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>37.71</v>
+        <v>37.94</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>40.79</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="215">
@@ -10401,10 +10421,10 @@
         <v>62.46</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>61.3</v>
+        <v>61.67</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.86</v>
       </c>
     </row>
     <row r="216">
@@ -10420,10 +10440,10 @@
         <v>114.98</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>90.04000000000001</v>
+        <v>90.58</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>142.14</v>
+        <v>142.99</v>
       </c>
     </row>
     <row r="217">
@@ -10439,10 +10459,10 @@
         <v>107.95</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>108.42</v>
+        <v>109.07</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>133.12</v>
+        <v>133.92</v>
       </c>
     </row>
     <row r="218">
@@ -10458,10 +10478,10 @@
         <v>126.87</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>112.79</v>
+        <v>113.46</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>156.01</v>
+        <v>156.95</v>
       </c>
     </row>
     <row r="219">
@@ -10477,10 +10497,10 @@
         <v>55.18</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>57.63</v>
+        <v>57.98</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>67.66</v>
+        <v>68.06999999999999</v>
       </c>
     </row>
     <row r="220">
@@ -10496,10 +10516,10 @@
         <v>33.73</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>41.24</v>
+        <v>41.49</v>
       </c>
     </row>
     <row r="221">
@@ -10515,10 +10535,10 @@
         <v>15.09</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>22.48</v>
+        <v>22.61</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>18.37</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="222">
@@ -10534,10 +10554,10 @@
         <v>40.78</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>42.46</v>
+        <v>42.72</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>49.45</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="223">
@@ -10553,10 +10573,10 @@
         <v>30.8</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>38.91</v>
+        <v>39.15</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>37.19</v>
+        <v>37.41</v>
       </c>
     </row>
     <row r="224">
@@ -10572,10 +10592,10 @@
         <v>75.01000000000001</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>72.91</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>89.92</v>
+        <v>90.45999999999999</v>
       </c>
     </row>
     <row r="225">
@@ -10591,10 +10611,10 @@
         <v>48.54</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>64.48</v>
+        <v>64.86</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>57.78</v>
+        <v>58.12</v>
       </c>
     </row>
     <row r="226">
@@ -10610,10 +10630,10 @@
         <v>56.47</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>64.73999999999999</v>
+        <v>65.13</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>66.73999999999999</v>
+        <v>67.14</v>
       </c>
     </row>
     <row r="227">
@@ -10629,10 +10649,10 @@
         <v>168.15</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>166.25</v>
+        <v>167.25</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>197.55</v>
+        <v>198.74</v>
       </c>
     </row>
     <row r="228">
@@ -10648,10 +10668,10 @@
         <v>264.24</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>272.88</v>
+        <v>274.51</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>308.62</v>
+        <v>310.47</v>
       </c>
     </row>
     <row r="229">
@@ -10667,10 +10687,10 @@
         <v>375.96</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>344.25</v>
+        <v>346.32</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>436.52</v>
+        <v>439.14</v>
       </c>
     </row>
     <row r="230">
@@ -10686,10 +10706,10 @@
         <v>432</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>392.76</v>
+        <v>395.12</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>498.54</v>
+        <v>501.53</v>
       </c>
     </row>
     <row r="231">
@@ -10705,10 +10725,10 @@
         <v>137.33</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>138.8</v>
+        <v>139.64</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>157.52</v>
+        <v>158.47</v>
       </c>
     </row>
     <row r="232">
@@ -10724,10 +10744,10 @@
         <v>130.9</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>127.43</v>
+        <v>128.2</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>149.24</v>
+        <v>150.14</v>
       </c>
     </row>
     <row r="233">
@@ -10743,10 +10763,10 @@
         <v>97.36</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>112.07</v>
+        <v>112.74</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>110.32</v>
+        <v>110.98</v>
       </c>
     </row>
     <row r="234">
@@ -10762,10 +10782,10 @@
         <v>58.3</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>66.03</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>65.66</v>
+        <v>66.05</v>
       </c>
     </row>
     <row r="235">
@@ -10781,10 +10801,10 @@
         <v>11.57</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>35.02</v>
+        <v>35.23</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>12.95</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="236">
@@ -10800,10 +10820,10 @@
         <v>32.05</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>53.59</v>
+        <v>53.91</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>35.72</v>
+        <v>35.93</v>
       </c>
     </row>
     <row r="237">
@@ -10819,10 +10839,10 @@
         <v>55.29</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>64.36</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>61.34</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="238">
@@ -10838,10 +10858,10 @@
         <v>54.59</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>68.5</v>
+        <v>68.91</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>60.29</v>
+        <v>60.65</v>
       </c>
     </row>
     <row r="239">
@@ -10857,10 +10877,10 @@
         <v>86.78</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>92.09</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>95.56999999999999</v>
+        <v>96.15000000000001</v>
       </c>
     </row>
     <row r="240">
@@ -10876,10 +10896,10 @@
         <v>145.97</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>139.64</v>
+        <v>140.47</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>160.3</v>
+        <v>161.26</v>
       </c>
     </row>
     <row r="241">
@@ -10895,10 +10915,10 @@
         <v>85.79000000000001</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>59.71</v>
+        <v>60.07</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>93.95</v>
+        <v>94.51000000000001</v>
       </c>
     </row>
     <row r="242">
@@ -10914,10 +10934,10 @@
         <v>76.38</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>60.23</v>
+        <v>60.59</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>83.31999999999999</v>
+        <v>83.81999999999999</v>
       </c>
     </row>
     <row r="243">
@@ -10933,10 +10953,10 @@
         <v>80.04000000000001</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>70.27</v>
+        <v>70.69</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>86.98</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="244">
@@ -10952,10 +10972,10 @@
         <v>28.16</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>28.48</v>
+        <v>28.65</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>30.49</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="245">
@@ -10971,10 +10991,10 @@
         <v>15.14</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>18.57</v>
+        <v>18.68</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>16.36</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="246">
@@ -10990,10 +11010,10 @@
         <v>31.79</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>37.67</v>
+        <v>37.89</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>34.27</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="247">
@@ -11009,10 +11029,10 @@
         <v>25.23</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>27.21</v>
+        <v>27.37</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>27.14</v>
+        <v>27.31</v>
       </c>
     </row>
     <row r="248">
@@ -11028,10 +11048,10 @@
         <v>17.65</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>23.7</v>
+        <v>23.84</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>18.93</v>
+        <v>19.04</v>
       </c>
     </row>
     <row r="249">
@@ -11047,10 +11067,10 @@
         <v>133.13</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>88.68000000000001</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>142.34</v>
+        <v>143.2</v>
       </c>
     </row>
     <row r="250">
@@ -11066,10 +11086,10 @@
         <v>46.25</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>55.42</v>
+        <v>55.75</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>49.3</v>
+        <v>49.59</v>
       </c>
     </row>
     <row r="251">
@@ -11085,10 +11105,10 @@
         <v>80.23</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>90.08</v>
+        <v>90.62</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>85.22</v>
+        <v>85.73</v>
       </c>
     </row>
     <row r="252">
@@ -11104,10 +11124,10 @@
         <v>146.58</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>140.75</v>
+        <v>141.6</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>155.16</v>
+        <v>156.09</v>
       </c>
     </row>
     <row r="253">
@@ -11123,10 +11143,10 @@
         <v>198.82</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>173.24</v>
+        <v>174.28</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>209.73</v>
+        <v>210.99</v>
       </c>
     </row>
     <row r="254">
@@ -11142,10 +11162,10 @@
         <v>191.83</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>157.21</v>
+        <v>158.15</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>202.21</v>
+        <v>203.42</v>
       </c>
     </row>
     <row r="255">
@@ -11161,10 +11181,10 @@
         <v>216.14</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>151.05</v>
+        <v>151.95</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>227.67</v>
+        <v>229.03</v>
       </c>
     </row>
     <row r="256">
@@ -11180,10 +11200,10 @@
         <v>26.5</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>18.3</v>
+        <v>18.41</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>27.89</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="257">
@@ -11199,10 +11219,10 @@
         <v>10.18</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>21.42</v>
+        <v>21.54</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>10.71</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="258">
@@ -11218,10 +11238,10 @@
         <v>52.94</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>67.36</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>55.65</v>
+        <v>55.98</v>
       </c>
     </row>
     <row r="259">
@@ -11237,10 +11257,10 @@
         <v>39.93</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>54.89</v>
+        <v>55.22</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>41.95</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="260">
@@ -11256,10 +11276,10 @@
         <v>23.72</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>50.64</v>
+        <v>50.94</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>24.84</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="261">
@@ -11275,10 +11295,10 @@
         <v>76.73</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>71.56999999999999</v>
+        <v>72</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>80.11</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="262">
@@ -11294,10 +11314,10 @@
         <v>62.93</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>64.28</v>
+        <v>64.66</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>65.51000000000001</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="263">
@@ -11313,10 +11333,10 @@
         <v>70.56</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>77.63</v>
+        <v>78.09</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>73.27</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="264">
@@ -11332,10 +11352,10 @@
         <v>93.92</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>80.84</v>
+        <v>81.33</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>97.28</v>
+        <v>97.86</v>
       </c>
     </row>
     <row r="265">
@@ -11351,10 +11371,10 @@
         <v>463.18</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>273.39</v>
+        <v>275.03</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>478.57</v>
+        <v>481.44</v>
       </c>
     </row>
     <row r="266">
@@ -11370,10 +11390,10 @@
         <v>107.96</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>84.48999999999999</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>111.06</v>
+        <v>111.72</v>
       </c>
     </row>
     <row r="267">
@@ -11389,10 +11409,10 @@
         <v>107.79</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>95.45</v>
+        <v>96.02</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>110.4</v>
+        <v>111.06</v>
       </c>
     </row>
     <row r="268">
@@ -11408,10 +11428,10 @@
         <v>61.8</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>56.36</v>
+        <v>56.7</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>63.02</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="269">
@@ -11427,10 +11447,10 @@
         <v>45.13</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>52.28</v>
+        <v>52.6</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>45.93</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="270">
@@ -11446,10 +11466,10 @@
         <v>13.79</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>32.42</v>
+        <v>32.62</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>14.01</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="271">
@@ -11465,10 +11485,10 @@
         <v>16.99</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>27.89</v>
+        <v>28.06</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>17.22</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="272">
@@ -11484,10 +11504,10 @@
         <v>43.74</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>38.9</v>
+        <v>39.14</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>44.14</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="273">
@@ -11503,10 +11523,10 @@
         <v>40.2</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>45.26</v>
+        <v>45.54</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>40.38</v>
+        <v>40.62</v>
       </c>
     </row>
     <row r="274">
@@ -11522,10 +11542,10 @@
         <v>44.69</v>
       </c>
       <c r="D274" s="5" t="n">
-        <v>44.74</v>
+        <v>45.01</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>44.69</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="275">
@@ -11541,10 +11561,10 @@
         <v>37.67</v>
       </c>
       <c r="D275" s="5" t="n">
-        <v>35.68</v>
+        <v>35.82</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>37.67</v>
+        <v>37.82</v>
       </c>
     </row>
     <row r="276">
@@ -11560,10 +11580,10 @@
         <v>73.73999999999999</v>
       </c>
       <c r="D276" s="5" t="n">
-        <v>64.77</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>73.73999999999999</v>
+        <v>73.89</v>
       </c>
     </row>
     <row r="277">
@@ -11585,8 +11605,27 @@
         <v>78.04000000000001</v>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B278" s="5" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="D278" s="5" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>90.75</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B277">
+  <conditionalFormatting sqref="B2:B278">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11598,7 +11637,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C277">
+  <conditionalFormatting sqref="C2:C278">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11610,7 +11649,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D277">
+  <conditionalFormatting sqref="D2:D278">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11622,7 +11661,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E277">
+  <conditionalFormatting sqref="E2:E278">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/VIC_historical_prices.xlsx
+++ b/outputs/VIC_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>52.1</v>
+        <v>49.37</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>54.53</v>
+        <v>51.28</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>52.8</v>
+        <v>49.83</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>55.21</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>66.7</v>
+        <v>63.25</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>79.13</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>68.98</v>
+        <v>65.16</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>81.87</v>
+        <v>75.19</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>68.26000000000001</v>
+        <v>68.14</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>80.39</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>71.45</v>
+        <v>71.17</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>84.15000000000001</v>
+        <v>83.63</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>78.5</v>
+        <v>78.72</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>91.04000000000001</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>86.31999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>100.05</v>
+        <v>100.06</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>78.28</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>94.03</v>
+        <v>94.14</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>93.73999999999999</v>
+        <v>93.75</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>112.84</v>
+        <v>112.79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Jul 2026</t>
+          <t>Data through: Aug 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6313,6 +6313,26 @@
       </c>
       <c r="F278" s="7" t="inlineStr"/>
     </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B279" s="5" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="C279" s="5" t="n">
+        <v>68.86</v>
+      </c>
+      <c r="D279" s="5" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="E279" s="5" t="n">
+        <v>68.86</v>
+      </c>
+      <c r="F279" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6324,7 +6344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E278"/>
+  <dimension ref="A1:E279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11624,8 +11644,27 @@
         <v>90.75</v>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B279" s="5" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="C279" s="5" t="n">
+        <v>68.86</v>
+      </c>
+      <c r="D279" s="5" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="E279" s="5" t="n">
+        <v>68.86</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B278">
+  <conditionalFormatting sqref="B2:B279">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11637,7 +11676,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C278">
+  <conditionalFormatting sqref="C2:C279">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11649,7 +11688,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D278">
+  <conditionalFormatting sqref="D2:D279">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11661,7 +11700,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E278">
+  <conditionalFormatting sqref="E2:E279">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/VIC_historical_prices.xlsx
+++ b/outputs/VIC_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>49.37</v>
+        <v>47.83</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>51.28</v>
+        <v>49.21</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>49.83</v>
+        <v>48.17</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>51.7</v>
+        <v>49.49</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>63.25</v>
+        <v>64.06</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>72.98999999999999</v>
+        <v>73.42</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>65.16</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>75.19</v>
+        <v>75.56</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>68.14</v>
+        <v>68.44</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>80.06999999999999</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>71.17</v>
+        <v>71.39</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>83.63</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>78.72</v>
+        <v>78.87</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>91.26000000000001</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>86.36</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>100.06</v>
+        <v>99.98</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>78.43000000000001</v>
+        <v>78.39</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>94.14</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>93.75</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>112.79</v>
+        <v>112.55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Aug 2026</t>
+          <t>Data through: Sep 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F279"/>
+  <dimension ref="A1:F280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6333,6 +6333,26 @@
       </c>
       <c r="F279" s="7" t="inlineStr"/>
     </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="B280" s="5" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="C280" s="5" t="n">
+        <v>36.93</v>
+      </c>
+      <c r="D280" s="5" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="E280" s="5" t="n">
+        <v>36.93</v>
+      </c>
+      <c r="F280" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6344,7 +6364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E279"/>
+  <dimension ref="A1:E280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11663,8 +11683,27 @@
         <v>68.86</v>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="B280" s="5" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="C280" s="5" t="n">
+        <v>36.93</v>
+      </c>
+      <c r="D280" s="5" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="E280" s="5" t="n">
+        <v>36.93</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B279">
+  <conditionalFormatting sqref="B2:B280">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11676,7 +11715,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C279">
+  <conditionalFormatting sqref="C2:C280">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11688,7 +11727,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D279">
+  <conditionalFormatting sqref="D2:D280">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11700,7 +11739,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E279">
+  <conditionalFormatting sqref="E2:E280">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/VIC_historical_prices.xlsx
+++ b/outputs/VIC_historical_prices.xlsx
@@ -531,13 +531,13 @@
         <v>47.83</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>49.21</v>
+        <v>49.24</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>48.17</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>49.49</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="6">
@@ -569,13 +569,13 @@
         <v>68.44</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>80.31999999999999</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>71.39</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>83.8</v>
+        <v>83.73999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>78.87</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>91.31999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>86.40000000000001</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>99.98</v>
+        <v>99.84999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -607,13 +607,13 @@
         <v>78.39</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>94.04000000000001</v>
+        <v>93.42</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>93.59999999999999</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>112.55</v>
+        <v>111.75</v>
       </c>
     </row>
     <row r="11">
@@ -687,13 +687,13 @@
         <v>25.62</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>32.99</v>
+        <v>33.07</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>47.9</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>61.68</v>
+        <v>61.83</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
     </row>
@@ -707,13 +707,13 @@
         <v>20.15</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>23.45</v>
+        <v>23.54</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>37.6</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>43.76</v>
+        <v>43.93</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
     </row>
@@ -727,13 +727,13 @@
         <v>20.73</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>25.19</v>
+        <v>25.18</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>38.61</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>46.92</v>
+        <v>46.9</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
     </row>
@@ -747,13 +747,13 @@
         <v>20.74</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25.19</v>
+        <v>25.05</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>38.56</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>46.84</v>
+        <v>46.57</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
     </row>
@@ -767,13 +767,13 @@
         <v>21.18</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>26.23</v>
+        <v>25.87</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>39.31</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>48.68</v>
+        <v>48.02</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
     </row>
@@ -787,13 +787,13 @@
         <v>24.97</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>34.01</v>
+        <v>33.9</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>46.26</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>63.01</v>
+        <v>62.81</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
     </row>
@@ -807,13 +807,13 @@
         <v>22.52</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>30.37</v>
+        <v>30.13</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>41.6</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>56.1</v>
+        <v>55.66</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
@@ -827,13 +827,13 @@
         <v>38.62</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>48.76</v>
+        <v>48.3</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>71.13</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>89.81</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
     </row>
@@ -847,13 +847,13 @@
         <v>21.48</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>28.54</v>
+        <v>28.1</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>39.45</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>52.41</v>
+        <v>51.6</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
     </row>
@@ -867,13 +867,13 @@
         <v>29.46</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>36.99</v>
+        <v>36.91</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>54.02</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>67.83</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
     </row>
@@ -887,13 +887,13 @@
         <v>31.29</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>39.67</v>
+        <v>39.52</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>57.29</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>72.63</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -907,13 +907,13 @@
         <v>28.63</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>34.73</v>
+        <v>34.78</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>52.33</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>63.48</v>
+        <v>63.58</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
@@ -927,13 +927,13 @@
         <v>31.37</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>43.7</v>
+        <v>43.74</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>57.26</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>79.77</v>
+        <v>79.84</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -947,13 +947,13 @@
         <v>22.55</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>27.37</v>
+        <v>27.28</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>41.11</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>49.89</v>
+        <v>49.73</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -967,13 +967,13 @@
         <v>27.2</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>31.48</v>
+        <v>31.28</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>49.52</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>57.31</v>
+        <v>56.94</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -987,13 +987,13 @@
         <v>44.88</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>70.45</v>
+        <v>70.44</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>81.48999999999999</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>127.93</v>
+        <v>127.91</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -1007,13 +1007,13 @@
         <v>35.66</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>44.55</v>
+        <v>43.97</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>64.59</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>80.69</v>
+        <v>79.64</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
     </row>
@@ -1027,13 +1027,13 @@
         <v>27.36</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>33</v>
+        <v>32.66</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>49.43</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>59.62</v>
+        <v>59</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -1047,13 +1047,13 @@
         <v>22.84</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>29.72</v>
+        <v>29.7</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>41.17</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>53.57</v>
+        <v>53.54</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
     </row>
@@ -1067,13 +1067,13 @@
         <v>21.83</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>27.43</v>
+        <v>27.12</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>39.26</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>49.34</v>
+        <v>48.78</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
     </row>
@@ -1087,13 +1087,13 @@
         <v>18.7</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>21.15</v>
+        <v>20.94</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>33.56</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>37.96</v>
+        <v>37.58</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
     </row>
@@ -1107,13 +1107,13 @@
         <v>30.63</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>37.8</v>
+        <v>37.71</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>54.86</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>67.7</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
     </row>
@@ -1127,13 +1127,13 @@
         <v>24.56</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>43.9</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>52.19</v>
+        <v>51.84</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
     </row>
@@ -1147,13 +1147,13 @@
         <v>23.54</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>27.29</v>
+        <v>27.23</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>41.99</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>48.68</v>
+        <v>48.58</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
     </row>
@@ -1167,13 +1167,13 @@
         <v>26.51</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>32.37</v>
+        <v>32.3</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>47.14</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>57.56</v>
+        <v>57.43</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
     </row>
@@ -1187,13 +1187,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>40.25</v>
+        <v>40.15</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>53.17</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>71.33</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
     </row>
@@ -1207,13 +1207,13 @@
         <v>29.14</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>37.44</v>
+        <v>37.3</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>51.47</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>66.13</v>
+        <v>65.89</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
     </row>
@@ -1227,13 +1227,13 @@
         <v>22.64</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>28.49</v>
+        <v>28.44</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>39.92</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>50.24</v>
+        <v>50.15</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
     </row>
@@ -1247,13 +1247,13 @@
         <v>30.7</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>46.39</v>
+        <v>46.09</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>54.04</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>81.66</v>
+        <v>81.13</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
     </row>
@@ -1267,13 +1267,13 @@
         <v>34.24</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>49.23</v>
+        <v>49.13</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>60.17</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>86.51000000000001</v>
+        <v>86.34</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
     </row>
@@ -1287,13 +1287,13 @@
         <v>53.44</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>88.63</v>
+        <v>88.39</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>93.64</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>155.3</v>
+        <v>154.88</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
     </row>
@@ -1307,13 +1307,13 @@
         <v>56</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>105.51</v>
+        <v>105.26</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>97.84999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>184.36</v>
+        <v>183.92</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
     </row>
@@ -1327,13 +1327,13 @@
         <v>23.36</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>29.33</v>
+        <v>29.05</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>40.7</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>51.1</v>
+        <v>50.61</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
     </row>
@@ -1347,13 +1347,13 @@
         <v>22.59</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>27.86</v>
+        <v>27.89</v>
       </c>
       <c r="D35" s="5" t="n">
         <v>39.15</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>48.29</v>
+        <v>48.34</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
     </row>
@@ -1367,13 +1367,13 @@
         <v>28.25</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>37.94</v>
+        <v>37.92</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>48.71</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>65.41</v>
+        <v>65.38</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
     </row>
@@ -1387,13 +1387,13 @@
         <v>34.61</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>42.49</v>
+        <v>42.6</v>
       </c>
       <c r="D37" s="5" t="n">
         <v>59.36</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>72.88</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
     </row>
@@ -1407,13 +1407,13 @@
         <v>47.2</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>71.86</v>
+        <v>71.95</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>80.72</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>122.89</v>
+        <v>123.04</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
     </row>
@@ -1427,13 +1427,13 @@
         <v>32.21</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>39.11</v>
+        <v>38.93</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>54.92</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>66.69</v>
+        <v>66.38</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
     </row>
@@ -1447,13 +1447,13 @@
         <v>30.8</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>38.91</v>
+        <v>38.74</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>52.36</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>66.15000000000001</v>
+        <v>65.86</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
     </row>
@@ -1467,13 +1467,13 @@
         <v>27.66</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>34.69</v>
+        <v>34.58</v>
       </c>
       <c r="D41" s="5" t="n">
         <v>47.04</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>59</v>
+        <v>58.81</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
     </row>
@@ -1487,13 +1487,13 @@
         <v>32.71</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>42.78</v>
+        <v>42.04</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>55.65</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>72.79000000000001</v>
+        <v>71.53</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
     </row>
@@ -1507,13 +1507,13 @@
         <v>22.28</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>28.32</v>
+        <v>28.05</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>37.92</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>48.2</v>
+        <v>47.74</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
     </row>
@@ -1527,13 +1527,13 @@
         <v>91.45999999999999</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>165.37</v>
+        <v>165.27</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>155.63</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>281.39</v>
+        <v>281.22</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
     </row>
@@ -1547,13 +1547,13 @@
         <v>47.44</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>69.13</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="D45" s="5" t="n">
         <v>80.7</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>117.6</v>
+        <v>116.64</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
     </row>
@@ -1567,13 +1567,13 @@
         <v>53.28</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>74.84999999999999</v>
+        <v>74.37</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>90.61</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>127.29</v>
+        <v>126.48</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
     </row>
@@ -1587,13 +1587,13 @@
         <v>67.76000000000001</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>81.62</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>114.76</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>138.24</v>
+        <v>137.17</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
     </row>
@@ -1607,13 +1607,13 @@
         <v>62.64</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>75.48999999999999</v>
+        <v>74.97</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>105.66</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>127.34</v>
+        <v>126.46</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
     </row>
@@ -1627,13 +1627,13 @@
         <v>143.28</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>218.05</v>
+        <v>218.49</v>
       </c>
       <c r="D49" s="5" t="n">
         <v>240.71</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>366.32</v>
+        <v>367.06</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
     </row>
@@ -1647,13 +1647,13 @@
         <v>85.55</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>115.22</v>
+        <v>114.96</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>143.39</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>193.12</v>
+        <v>192.69</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
     </row>
@@ -1667,13 +1667,13 @@
         <v>41.73</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>50.83</v>
+        <v>50.52</v>
       </c>
       <c r="D51" s="5" t="n">
         <v>69.78</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>85</v>
+        <v>84.48</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
     </row>
@@ -1687,13 +1687,13 @@
         <v>44.58</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>55.04</v>
+        <v>54.66</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>74.38</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>91.83</v>
+        <v>91.2</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
     </row>
@@ -1707,13 +1707,13 @@
         <v>35.51</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>45.32</v>
+        <v>45.03</v>
       </c>
       <c r="D53" s="5" t="n">
         <v>59.06</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>75.38</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
     </row>
@@ -1727,13 +1727,13 @@
         <v>42.73</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>54.55</v>
+        <v>53.86</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>70.84999999999999</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>90.45</v>
+        <v>89.31</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
     </row>
@@ -1747,13 +1747,13 @@
         <v>44.79</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>62.08</v>
+        <v>61.74</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>74.04000000000001</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>102.62</v>
+        <v>102.06</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
     </row>
@@ -1767,13 +1767,13 @@
         <v>40.37</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>55.11</v>
+        <v>54.78</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>66.44</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>90.7</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
     </row>
@@ -1787,13 +1787,13 @@
         <v>36.88</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>52.11</v>
+        <v>51.53</v>
       </c>
       <c r="D57" s="5" t="n">
         <v>60.43</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>85.38</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
     </row>
@@ -1807,13 +1807,13 @@
         <v>52.14</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>84.56999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>85.05</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>137.95</v>
+        <v>137.19</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
     </row>
@@ -1827,13 +1827,13 @@
         <v>39.86</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>50.14</v>
+        <v>49.7</v>
       </c>
       <c r="D59" s="5" t="n">
         <v>64.70999999999999</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>81.40000000000001</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
@@ -1847,13 +1847,13 @@
         <v>54.03</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>64.59</v>
+        <v>63.89</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>87.29000000000001</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>104.35</v>
+        <v>103.22</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
     </row>
@@ -1867,13 +1867,13 @@
         <v>42.04</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>52.09</v>
+        <v>51.98</v>
       </c>
       <c r="D61" s="5" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>83.75</v>
+        <v>83.58</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
@@ -1887,13 +1887,13 @@
         <v>43.04</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>60.12</v>
+        <v>60.1</v>
       </c>
       <c r="D62" s="5" t="n">
         <v>68.94</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>96.29000000000001</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
     </row>
@@ -1907,13 +1907,13 @@
         <v>40.91</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>50.92</v>
+        <v>50.49</v>
       </c>
       <c r="D63" s="5" t="n">
         <v>65.27</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>81.23999999999999</v>
+        <v>80.56</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
     </row>
@@ -1927,13 +1927,13 @@
         <v>36.62</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>47.77</v>
+        <v>47.53</v>
       </c>
       <c r="D64" s="5" t="n">
         <v>58.2</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>75.93000000000001</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
     </row>
@@ -1947,13 +1947,13 @@
         <v>39.37</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>51.76</v>
+        <v>50.87</v>
       </c>
       <c r="D65" s="5" t="n">
         <v>62.64</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>82.36</v>
+        <v>80.94</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
     </row>
@@ -1967,13 +1967,13 @@
         <v>34.56</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>45.33</v>
+        <v>44.54</v>
       </c>
       <c r="D66" s="5" t="n">
         <v>55.05</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>72.2</v>
+        <v>70.95</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
     </row>
@@ -1987,13 +1987,13 @@
         <v>22.49</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>27.82</v>
+        <v>27.59</v>
       </c>
       <c r="D67" s="5" t="n">
         <v>35.86</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>44.36</v>
+        <v>44</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
     </row>
@@ -2007,13 +2007,13 @@
         <v>125.54</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>248.2</v>
+        <v>248.01</v>
       </c>
       <c r="D68" s="5" t="n">
         <v>200.11</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>395.64</v>
+        <v>395.33</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
     </row>
@@ -2027,13 +2027,13 @@
         <v>33.4</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>44.74</v>
+        <v>44.12</v>
       </c>
       <c r="D69" s="5" t="n">
         <v>53.22</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>71.29000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
     </row>
@@ -2047,13 +2047,13 @@
         <v>25.27</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>32.56</v>
+        <v>32.01</v>
       </c>
       <c r="D70" s="5" t="n">
         <v>40.25</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>51.86</v>
+        <v>50.99</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
     </row>
@@ -2067,13 +2067,13 @@
         <v>37.3</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>49.27</v>
+        <v>48.96</v>
       </c>
       <c r="D71" s="5" t="n">
         <v>59.32</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>78.34999999999999</v>
+        <v>77.86</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
     </row>
@@ -2087,13 +2087,13 @@
         <v>31.45</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>37.87</v>
+        <v>37.6</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>49.93</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>60.12</v>
+        <v>59.69</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
     </row>
@@ -2107,13 +2107,13 @@
         <v>30.07</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>37.13</v>
+        <v>37.07</v>
       </c>
       <c r="D73" s="5" t="n">
         <v>47.66</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>58.85</v>
+        <v>58.75</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
     </row>
@@ -2127,13 +2127,13 @@
         <v>26.84</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>32.55</v>
+        <v>32.46</v>
       </c>
       <c r="D74" s="5" t="n">
         <v>42.41</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>51.43</v>
+        <v>51.29</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
     </row>
@@ -2147,13 +2147,13 @@
         <v>22.44</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>28.02</v>
+        <v>27.81</v>
       </c>
       <c r="D75" s="5" t="n">
         <v>35.34</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>44.13</v>
+        <v>43.8</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
     </row>
@@ -2167,13 +2167,13 @@
         <v>22.94</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>27.43</v>
+        <v>27.42</v>
       </c>
       <c r="D76" s="5" t="n">
         <v>36.02</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>43.07</v>
+        <v>43.05</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
     </row>
@@ -2187,13 +2187,13 @@
         <v>25.56</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>31.55</v>
+        <v>30.83</v>
       </c>
       <c r="D77" s="5" t="n">
         <v>40.06</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>49.45</v>
+        <v>48.32</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
     </row>
@@ -2207,13 +2207,13 @@
         <v>32.43</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>44.98</v>
+        <v>44.77</v>
       </c>
       <c r="D78" s="5" t="n">
         <v>50.74</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>70.37</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
     </row>
@@ -2227,13 +2227,13 @@
         <v>23.51</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>29.49</v>
+        <v>29.38</v>
       </c>
       <c r="D79" s="5" t="n">
         <v>36.72</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>46.06</v>
+        <v>45.88</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
     </row>
@@ -2247,13 +2247,13 @@
         <v>60.95</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>114.74</v>
+        <v>114.66</v>
       </c>
       <c r="D80" s="5" t="n">
         <v>94.89</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>178.64</v>
+        <v>178.52</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
     </row>
@@ -2267,13 +2267,13 @@
         <v>67.91</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>124.09</v>
+        <v>123.77</v>
       </c>
       <c r="D81" s="5" t="n">
         <v>105.4</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>192.6</v>
+        <v>192.1</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
     </row>
@@ -2287,13 +2287,13 @@
         <v>22.86</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>27.11</v>
+        <v>26.87</v>
       </c>
       <c r="D82" s="5" t="n">
         <v>35.37</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>41.95</v>
+        <v>41.58</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
     </row>
@@ -2307,13 +2307,13 @@
         <v>71.56</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>131.25</v>
+        <v>131.27</v>
       </c>
       <c r="D83" s="5" t="n">
         <v>110.5</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>202.68</v>
+        <v>202.71</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
     </row>
@@ -2327,13 +2327,13 @@
         <v>30.49</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>34.97</v>
+        <v>34.5</v>
       </c>
       <c r="D84" s="5" t="n">
         <v>46.99</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>53.89</v>
+        <v>53.17</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
     </row>
@@ -2347,13 +2347,13 @@
         <v>31.4</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>36.19</v>
+        <v>36.24</v>
       </c>
       <c r="D85" s="5" t="n">
         <v>48.29</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>55.66</v>
+        <v>55.74</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
     </row>
@@ -2367,13 +2367,13 @@
         <v>26.65</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>30.36</v>
+        <v>30.25</v>
       </c>
       <c r="D86" s="5" t="n">
         <v>40.89</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>46.58</v>
+        <v>46.41</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
     </row>
@@ -2387,13 +2387,13 @@
         <v>27.05</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>30.73</v>
+        <v>30.63</v>
       </c>
       <c r="D87" s="5" t="n">
         <v>41.4</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>47.04</v>
+        <v>46.88</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
     </row>
@@ -2407,13 +2407,13 @@
         <v>22.12</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>24.89</v>
+        <v>24.81</v>
       </c>
       <c r="D88" s="5" t="n">
         <v>33.78</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>38.01</v>
+        <v>37.89</v>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
     </row>
@@ -2427,13 +2427,13 @@
         <v>20.82</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>24.65</v>
+        <v>24.32</v>
       </c>
       <c r="D89" s="5" t="n">
         <v>31.75</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>37.59</v>
+        <v>37.09</v>
       </c>
       <c r="F89" s="7" t="inlineStr"/>
     </row>
@@ -2447,13 +2447,13 @@
         <v>18.42</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>21.04</v>
+        <v>20.74</v>
       </c>
       <c r="D90" s="5" t="n">
         <v>28.06</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>32.05</v>
+        <v>31.59</v>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
     </row>
@@ -2467,13 +2467,13 @@
         <v>16.52</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>18.96</v>
+        <v>18.84</v>
       </c>
       <c r="D91" s="5" t="n">
         <v>25.13</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>28.84</v>
+        <v>28.66</v>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
     </row>
@@ -2487,13 +2487,13 @@
         <v>41.07</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>66.16</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D92" s="5" t="n">
         <v>62.15</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>100.12</v>
+        <v>99.73</v>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
     </row>
@@ -2507,13 +2507,13 @@
         <v>40.46</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>59.69</v>
+        <v>59.12</v>
       </c>
       <c r="D93" s="5" t="n">
         <v>60.92</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>89.87</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
     </row>
@@ -2527,13 +2527,13 @@
         <v>24.96</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>28.62</v>
+        <v>28.33</v>
       </c>
       <c r="D94" s="5" t="n">
         <v>37.39</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>42.87</v>
+        <v>42.44</v>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
     </row>
@@ -2567,13 +2567,13 @@
         <v>34.35</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>40.58</v>
+        <v>40.34</v>
       </c>
       <c r="D96" s="5" t="n">
         <v>51.14</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>60.42</v>
+        <v>60.06</v>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
     </row>
@@ -2587,13 +2587,13 @@
         <v>27.92</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>33.89</v>
+        <v>33.79</v>
       </c>
       <c r="D97" s="5" t="n">
         <v>41.44</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>50.3</v>
+        <v>50.15</v>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
     </row>
@@ -2607,13 +2607,13 @@
         <v>29.49</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>37.84</v>
+        <v>37.74</v>
       </c>
       <c r="D98" s="5" t="n">
         <v>43.68</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>56.05</v>
+        <v>55.91</v>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
     </row>
@@ -2627,13 +2627,13 @@
         <v>29.95</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>35.44</v>
+        <v>35.21</v>
       </c>
       <c r="D99" s="5" t="n">
         <v>44.28</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>52.39</v>
+        <v>52.05</v>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
     </row>
@@ -2647,13 +2647,13 @@
         <v>26.98</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>31.61</v>
+        <v>31.48</v>
       </c>
       <c r="D100" s="5" t="n">
         <v>39.81</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>46.64</v>
+        <v>46.45</v>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
     </row>
@@ -2667,13 +2667,13 @@
         <v>23.61</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>29</v>
+        <v>28.55</v>
       </c>
       <c r="D101" s="5" t="n">
         <v>34.84</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>42.79</v>
+        <v>42.13</v>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
     </row>
@@ -2687,13 +2687,13 @@
         <v>26.58</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>30.77</v>
+        <v>30.42</v>
       </c>
       <c r="D102" s="5" t="n">
         <v>39.22</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>45.4</v>
+        <v>44.88</v>
       </c>
       <c r="F102" s="7" t="inlineStr"/>
     </row>
@@ -2707,13 +2707,13 @@
         <v>22.18</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>25.62</v>
+        <v>25.43</v>
       </c>
       <c r="D103" s="5" t="n">
         <v>32.73</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>37.8</v>
+        <v>37.52</v>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
     </row>
@@ -2727,13 +2727,13 @@
         <v>24.03</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>29.13</v>
+        <v>28.96</v>
       </c>
       <c r="D104" s="5" t="n">
         <v>35.45</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>42.97</v>
+        <v>42.72</v>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
     </row>
@@ -2747,13 +2747,13 @@
         <v>25.85</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>30.01</v>
+        <v>29.72</v>
       </c>
       <c r="D105" s="5" t="n">
         <v>38.13</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>44.26</v>
+        <v>43.83</v>
       </c>
       <c r="F105" s="7" t="inlineStr"/>
     </row>
@@ -2767,13 +2767,13 @@
         <v>23.7</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>27.89</v>
+        <v>27.57</v>
       </c>
       <c r="D106" s="5" t="n">
         <v>34.95</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>41.13</v>
+        <v>40.66</v>
       </c>
       <c r="F106" s="7" t="inlineStr"/>
     </row>
@@ -2787,13 +2787,13 @@
         <v>32.01</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>36.3</v>
+        <v>36.22</v>
       </c>
       <c r="D107" s="5" t="n">
         <v>47.12</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>53.44</v>
+        <v>53.32</v>
       </c>
       <c r="F107" s="7" t="inlineStr"/>
     </row>
@@ -2827,13 +2827,13 @@
         <v>36.75</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>42.66</v>
+        <v>42.49</v>
       </c>
       <c r="D109" s="5" t="n">
         <v>53.91</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>62.58</v>
+        <v>62.33</v>
       </c>
       <c r="F109" s="7" t="inlineStr"/>
     </row>
@@ -2847,13 +2847,13 @@
         <v>73.45999999999999</v>
       </c>
       <c r="C110" s="9" t="n">
-        <v>90.05</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="D110" s="9" t="n">
         <v>107.28</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>131.51</v>
+        <v>131.01</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -2871,13 +2871,13 @@
         <v>55.76</v>
       </c>
       <c r="C111" s="9" t="n">
-        <v>58.79</v>
+        <v>58.42</v>
       </c>
       <c r="D111" s="9" t="n">
         <v>81.06</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>85.47</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -2895,13 +2895,13 @@
         <v>53.48</v>
       </c>
       <c r="C112" s="9" t="n">
-        <v>60.96</v>
+        <v>60.79</v>
       </c>
       <c r="D112" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>88.23</v>
+        <v>87.98</v>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
@@ -2919,13 +2919,13 @@
         <v>51.27</v>
       </c>
       <c r="C113" s="9" t="n">
-        <v>55</v>
+        <v>54.54</v>
       </c>
       <c r="D113" s="9" t="n">
         <v>74.14</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>79.53</v>
+        <v>78.87</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
@@ -2943,13 +2943,13 @@
         <v>77.18000000000001</v>
       </c>
       <c r="C114" s="9" t="n">
-        <v>108.73</v>
+        <v>108.42</v>
       </c>
       <c r="D114" s="9" t="n">
         <v>111.51</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>157.1</v>
+        <v>156.65</v>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
@@ -2967,13 +2967,13 @@
         <v>52.18</v>
       </c>
       <c r="C115" s="9" t="n">
-        <v>58.92</v>
+        <v>58.79</v>
       </c>
       <c r="D115" s="9" t="n">
         <v>75.33</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>85.06</v>
+        <v>84.87</v>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
@@ -2991,13 +2991,13 @@
         <v>54.27</v>
       </c>
       <c r="C116" s="9" t="n">
-        <v>65.31</v>
+        <v>65.27</v>
       </c>
       <c r="D116" s="9" t="n">
         <v>78.26000000000001</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>94.18000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
@@ -3015,13 +3015,13 @@
         <v>53.59</v>
       </c>
       <c r="C117" s="9" t="n">
-        <v>59.78</v>
+        <v>59.25</v>
       </c>
       <c r="D117" s="9" t="n">
         <v>77.19</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>86.11</v>
+        <v>85.34</v>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
@@ -3039,13 +3039,13 @@
         <v>52.31</v>
       </c>
       <c r="C118" s="9" t="n">
-        <v>60.03</v>
+        <v>59.68</v>
       </c>
       <c r="D118" s="9" t="n">
         <v>75.26000000000001</v>
       </c>
       <c r="E118" s="9" t="n">
-        <v>86.37</v>
+        <v>85.87</v>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
@@ -3063,13 +3063,13 @@
         <v>50.02</v>
       </c>
       <c r="C119" s="9" t="n">
-        <v>53.46</v>
+        <v>53.14</v>
       </c>
       <c r="D119" s="9" t="n">
         <v>71.88</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>76.81999999999999</v>
+        <v>76.36</v>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         <v>54.85</v>
       </c>
       <c r="C120" s="9" t="n">
-        <v>61.01</v>
+        <v>60.42</v>
       </c>
       <c r="D120" s="9" t="n">
         <v>78.72</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>87.56</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
@@ -3111,13 +3111,13 @@
         <v>60.9</v>
       </c>
       <c r="C121" s="9" t="n">
-        <v>70.51000000000001</v>
+        <v>70.08</v>
       </c>
       <c r="D121" s="9" t="n">
         <v>87.29000000000001</v>
       </c>
       <c r="E121" s="9" t="n">
-        <v>101.06</v>
+        <v>100.45</v>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
@@ -3135,13 +3135,13 @@
         <v>58.35</v>
       </c>
       <c r="C122" s="9" t="n">
-        <v>62.4</v>
+        <v>61.74</v>
       </c>
       <c r="D122" s="9" t="n">
         <v>83.3</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>89.08</v>
+        <v>88.13</v>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
@@ -3159,13 +3159,13 @@
         <v>54.12</v>
       </c>
       <c r="C123" s="9" t="n">
-        <v>57.79</v>
+        <v>57.53</v>
       </c>
       <c r="D123" s="9" t="n">
         <v>76.95</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>82.16</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
@@ -3183,13 +3183,13 @@
         <v>49.25</v>
       </c>
       <c r="C124" s="9" t="n">
-        <v>52.11</v>
+        <v>51.96</v>
       </c>
       <c r="D124" s="9" t="n">
         <v>69.73999999999999</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>73.79000000000001</v>
+        <v>73.58</v>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
@@ -3207,13 +3207,13 @@
         <v>49.47</v>
       </c>
       <c r="C125" s="9" t="n">
-        <v>51.91</v>
+        <v>51.51</v>
       </c>
       <c r="D125" s="9" t="n">
         <v>69.88</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>73.33</v>
+        <v>72.77</v>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
@@ -3231,13 +3231,13 @@
         <v>46.76</v>
       </c>
       <c r="C126" s="9" t="n">
-        <v>49.47</v>
+        <v>49.21</v>
       </c>
       <c r="D126" s="9" t="n">
         <v>65.90000000000001</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>69.72</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>50.33</v>
       </c>
       <c r="C127" s="9" t="n">
-        <v>57.51</v>
+        <v>57.33</v>
       </c>
       <c r="D127" s="9" t="n">
         <v>70.76000000000001</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>80.86</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
@@ -3279,13 +3279,13 @@
         <v>72.43000000000001</v>
       </c>
       <c r="C128" s="9" t="n">
-        <v>105.62</v>
+        <v>105.36</v>
       </c>
       <c r="D128" s="9" t="n">
         <v>101.63</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>148.2</v>
+        <v>147.84</v>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
@@ -3303,13 +3303,13 @@
         <v>49.25</v>
       </c>
       <c r="C129" s="9" t="n">
-        <v>51.64</v>
+        <v>51.23</v>
       </c>
       <c r="D129" s="9" t="n">
         <v>68.97</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>72.31999999999999</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
@@ -3327,13 +3327,13 @@
         <v>45.96</v>
       </c>
       <c r="C130" s="9" t="n">
-        <v>50.99</v>
+        <v>50.43</v>
       </c>
       <c r="D130" s="9" t="n">
         <v>64.23999999999999</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>71.27</v>
+        <v>70.48</v>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
@@ -3351,13 +3351,13 @@
         <v>43.79</v>
       </c>
       <c r="C131" s="9" t="n">
-        <v>46.48</v>
+        <v>46.35</v>
       </c>
       <c r="D131" s="9" t="n">
         <v>61.1</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>64.84999999999999</v>
+        <v>64.67</v>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
@@ -3375,13 +3375,13 @@
         <v>48.2</v>
       </c>
       <c r="C132" s="9" t="n">
-        <v>53.42</v>
+        <v>53.06</v>
       </c>
       <c r="D132" s="9" t="n">
         <v>67.14</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>74.41</v>
+        <v>73.91</v>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
@@ -3399,13 +3399,13 @@
         <v>49.17</v>
       </c>
       <c r="C133" s="9" t="n">
-        <v>53.9</v>
+        <v>53.86</v>
       </c>
       <c r="D133" s="9" t="n">
         <v>68.38</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>74.95999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
@@ -3423,13 +3423,13 @@
         <v>38.59</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>43.69</v>
+        <v>43.59</v>
       </c>
       <c r="D134" s="5" t="n">
         <v>53.59</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>60.67</v>
+        <v>60.53</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
     </row>
@@ -3443,13 +3443,13 @@
         <v>34.51</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>40.67</v>
+        <v>40.37</v>
       </c>
       <c r="D135" s="5" t="n">
         <v>47.86</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>56.4</v>
+        <v>55.98</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
     </row>
@@ -3463,13 +3463,13 @@
         <v>36.26</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>42.07</v>
+        <v>41.59</v>
       </c>
       <c r="D136" s="5" t="n">
         <v>50.21</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>58.26</v>
+        <v>57.59</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
     </row>
@@ -3483,13 +3483,13 @@
         <v>26.59</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>30.63</v>
+        <v>30.36</v>
       </c>
       <c r="D137" s="5" t="n">
         <v>36.8</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>42.39</v>
+        <v>42.02</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
     </row>
@@ -3503,13 +3503,13 @@
         <v>28.56</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>34.46</v>
+        <v>34.02</v>
       </c>
       <c r="D138" s="5" t="n">
         <v>39.5</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>47.66</v>
+        <v>47.05</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
     </row>
@@ -3523,13 +3523,13 @@
         <v>26.54</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>31.31</v>
+        <v>31.02</v>
       </c>
       <c r="D139" s="5" t="n">
         <v>36.68</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>43.28</v>
+        <v>42.88</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
     </row>
@@ -3543,13 +3543,13 @@
         <v>26.1</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>33.61</v>
+        <v>33.35</v>
       </c>
       <c r="D140" s="5" t="n">
         <v>36.05</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>46.43</v>
+        <v>46.07</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
     </row>
@@ -3563,13 +3563,13 @@
         <v>28.03</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>35.21</v>
+        <v>34.67</v>
       </c>
       <c r="D141" s="5" t="n">
         <v>38.69</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>48.61</v>
+        <v>47.86</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
     </row>
@@ -3583,13 +3583,13 @@
         <v>25.81</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>31.79</v>
+        <v>30.8</v>
       </c>
       <c r="D142" s="5" t="n">
         <v>35.61</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>43.86</v>
+        <v>42.49</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
     </row>
@@ -3603,13 +3603,13 @@
         <v>28.91</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>35.26</v>
+        <v>34.91</v>
       </c>
       <c r="D143" s="5" t="n">
         <v>39.79</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>48.53</v>
+        <v>48.05</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
     </row>
@@ -3623,13 +3623,13 @@
         <v>29.85</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>38.41</v>
+        <v>38.04</v>
       </c>
       <c r="D144" s="5" t="n">
         <v>40.99</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>52.74</v>
+        <v>52.23</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
     </row>
@@ -3643,13 +3643,13 @@
         <v>34.41</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>41.52</v>
+        <v>40.94</v>
       </c>
       <c r="D145" s="5" t="n">
         <v>47.13</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>56.87</v>
+        <v>56.08</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
     </row>
@@ -3663,13 +3663,13 @@
         <v>34.75</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>42.82</v>
+        <v>42.4</v>
       </c>
       <c r="D146" s="5" t="n">
         <v>47.54</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>58.58</v>
+        <v>58</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
     </row>
@@ -3683,13 +3683,13 @@
         <v>35.04</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>42.1</v>
+        <v>41.42</v>
       </c>
       <c r="D147" s="5" t="n">
         <v>47.87</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>57.52</v>
+        <v>56.59</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
     </row>
@@ -3703,13 +3703,13 @@
         <v>44.55</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>50.84</v>
+        <v>50.53</v>
       </c>
       <c r="D148" s="5" t="n">
         <v>60.79</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>69.37</v>
+        <v>68.95</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
     </row>
@@ -3723,13 +3723,13 @@
         <v>35.63</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>45.47</v>
+        <v>44.46</v>
       </c>
       <c r="D149" s="5" t="n">
         <v>48.55</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>61.96</v>
+        <v>60.59</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
     </row>
@@ -3743,13 +3743,13 @@
         <v>34.92</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>45.23</v>
+        <v>44.68</v>
       </c>
       <c r="D150" s="5" t="n">
         <v>47.53</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>61.56</v>
+        <v>60.81</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
     </row>
@@ -3763,13 +3763,13 @@
         <v>48.01</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>62.67</v>
+        <v>61.92</v>
       </c>
       <c r="D151" s="5" t="n">
         <v>65.26000000000001</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>85.18000000000001</v>
+        <v>84.16</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
     </row>
@@ -3783,13 +3783,13 @@
         <v>46.95</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>72.90000000000001</v>
+        <v>72.53</v>
       </c>
       <c r="D152" s="5" t="n">
         <v>63.86</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>99.15000000000001</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
     </row>
@@ -3803,13 +3803,13 @@
         <v>35.42</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>44.52</v>
+        <v>43.88</v>
       </c>
       <c r="D153" s="5" t="n">
         <v>48.21</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>60.59</v>
+        <v>59.72</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
     </row>
@@ -3823,13 +3823,13 @@
         <v>45.89</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>59.65</v>
+        <v>58.3</v>
       </c>
       <c r="D154" s="5" t="n">
         <v>62.5</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>81.23999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
     </row>
@@ -3843,13 +3843,13 @@
         <v>45.88</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>61.49</v>
+        <v>59.14</v>
       </c>
       <c r="D155" s="5" t="n">
         <v>62.4</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>83.62</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
     </row>
@@ -3863,13 +3863,13 @@
         <v>54.24</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>76.45999999999999</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="D156" s="5" t="n">
         <v>73.66</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>103.83</v>
+        <v>99.91</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
     </row>
@@ -3883,13 +3883,13 @@
         <v>92.77</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>118.54</v>
+        <v>114.45</v>
       </c>
       <c r="D157" s="5" t="n">
         <v>125.8</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>160.74</v>
+        <v>155.19</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
     </row>
@@ -3903,13 +3903,13 @@
         <v>64.64</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>86.77</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="D158" s="5" t="n">
         <v>87.45</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>117.39</v>
+        <v>114.3</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
     </row>
@@ -3923,13 +3923,13 @@
         <v>43.24</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>55.76</v>
+        <v>53.5</v>
       </c>
       <c r="D159" s="5" t="n">
         <v>58.36</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>75.26000000000001</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
     </row>
@@ -3943,13 +3943,13 @@
         <v>41.02</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>48.5</v>
+        <v>47.59</v>
       </c>
       <c r="D160" s="5" t="n">
         <v>55.24</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>65.31</v>
+        <v>64.08</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
     </row>
@@ -3963,13 +3963,13 @@
         <v>33.18</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>41.02</v>
+        <v>38.38</v>
       </c>
       <c r="D161" s="5" t="n">
         <v>44.6</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>55.14</v>
+        <v>51.59</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
     </row>
@@ -3983,13 +3983,13 @@
         <v>36.07</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>46.93</v>
+        <v>45.05</v>
       </c>
       <c r="D162" s="5" t="n">
         <v>48.4</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>62.97</v>
+        <v>60.45</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
     </row>
@@ -4003,13 +4003,13 @@
         <v>29.9</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>37.59</v>
+        <v>37.06</v>
       </c>
       <c r="D163" s="5" t="n">
         <v>40.05</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>50.35</v>
+        <v>49.64</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
     </row>
@@ -4023,13 +4023,13 @@
         <v>62.04</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>81.03</v>
+        <v>80.27</v>
       </c>
       <c r="D164" s="5" t="n">
         <v>82.98</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>108.37</v>
+        <v>107.36</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
     </row>
@@ -4043,13 +4043,13 @@
         <v>86.05</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>114.18</v>
+        <v>111.69</v>
       </c>
       <c r="D165" s="5" t="n">
         <v>114.91</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>152.48</v>
+        <v>149.15</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
     </row>
@@ -4063,13 +4063,13 @@
         <v>90.63</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>112.64</v>
+        <v>110.35</v>
       </c>
       <c r="D166" s="5" t="n">
         <v>120.84</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>150.19</v>
+        <v>147.14</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
     </row>
@@ -4083,13 +4083,13 @@
         <v>108.2</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>123.35</v>
+        <v>121.78</v>
       </c>
       <c r="D167" s="5" t="n">
         <v>144.18</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>164.36</v>
+        <v>162.27</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
     </row>
@@ -4103,13 +4103,13 @@
         <v>107.95</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>123.09</v>
+        <v>121.22</v>
       </c>
       <c r="D168" s="5" t="n">
         <v>143.75</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>163.91</v>
+        <v>161.42</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
     </row>
@@ -4123,13 +4123,13 @@
         <v>98.5</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>105</v>
+        <v>103.65</v>
       </c>
       <c r="D169" s="5" t="n">
         <v>131.08</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>139.73</v>
+        <v>137.93</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
     </row>
@@ -4143,13 +4143,13 @@
         <v>117.38</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>131.48</v>
+        <v>129.67</v>
       </c>
       <c r="D170" s="5" t="n">
         <v>155.89</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>174.61</v>
+        <v>172.21</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
     </row>
@@ -4163,13 +4163,13 @@
         <v>102.57</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>119.74</v>
+        <v>116.97</v>
       </c>
       <c r="D171" s="5" t="n">
         <v>135.94</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>158.7</v>
+        <v>155.03</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
     </row>
@@ -4183,13 +4183,13 @@
         <v>79.43000000000001</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>89.62</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D172" s="5" t="n">
         <v>105.06</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>118.54</v>
+        <v>117.85</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
     </row>
@@ -4203,13 +4203,13 @@
         <v>73.31</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>82.48</v>
+        <v>81.72</v>
       </c>
       <c r="D173" s="5" t="n">
         <v>96.75</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>108.85</v>
+        <v>107.85</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
     </row>
@@ -4223,13 +4223,13 @@
         <v>95.54000000000001</v>
       </c>
       <c r="C174" s="5" t="n">
-        <v>112.43</v>
+        <v>111.45</v>
       </c>
       <c r="D174" s="5" t="n">
         <v>125.81</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>148.05</v>
+        <v>146.76</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
     </row>
@@ -4243,13 +4243,13 @@
         <v>84.84999999999999</v>
       </c>
       <c r="C175" s="5" t="n">
-        <v>97.75</v>
+        <v>97.2</v>
       </c>
       <c r="D175" s="5" t="n">
         <v>111.48</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>128.43</v>
+        <v>127.71</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
     </row>
@@ -4263,13 +4263,13 @@
         <v>133.48</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>183</v>
+        <v>182.54</v>
       </c>
       <c r="D176" s="5" t="n">
         <v>175.12</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>240.09</v>
+        <v>239.48</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
     </row>
@@ -4283,13 +4283,13 @@
         <v>97.43000000000001</v>
       </c>
       <c r="C177" s="5" t="n">
-        <v>124.33</v>
+        <v>123.66</v>
       </c>
       <c r="D177" s="5" t="n">
         <v>127.64</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>162.88</v>
+        <v>162</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
     </row>
@@ -4303,13 +4303,13 @@
         <v>76.01000000000001</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>82.25</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="D178" s="5" t="n">
         <v>99.43000000000001</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>107.59</v>
+        <v>106.56</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
     </row>
@@ -4323,13 +4323,13 @@
         <v>74.04000000000001</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>87.09</v>
+        <v>86.12</v>
       </c>
       <c r="D179" s="5" t="n">
         <v>96.73999999999999</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>113.79</v>
+        <v>112.52</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
     </row>
@@ -4343,13 +4343,13 @@
         <v>79.79000000000001</v>
       </c>
       <c r="C180" s="5" t="n">
-        <v>95.98</v>
+        <v>93.45</v>
       </c>
       <c r="D180" s="5" t="n">
         <v>104.13</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>125.26</v>
+        <v>121.96</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
     </row>
@@ -4363,13 +4363,13 @@
         <v>93.72</v>
       </c>
       <c r="C181" s="5" t="n">
-        <v>112.11</v>
+        <v>109.8</v>
       </c>
       <c r="D181" s="5" t="n">
         <v>122.16</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>146.13</v>
+        <v>143.12</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
     </row>
@@ -4383,13 +4383,13 @@
         <v>70.09999999999999</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>88.33</v>
+        <v>86.86</v>
       </c>
       <c r="D182" s="5" t="n">
         <v>91.23999999999999</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>114.97</v>
+        <v>113.06</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
     </row>
@@ -4403,13 +4403,13 @@
         <v>79.17</v>
       </c>
       <c r="C183" s="5" t="n">
-        <v>102.2</v>
+        <v>100.32</v>
       </c>
       <c r="D183" s="5" t="n">
         <v>102.9</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>132.83</v>
+        <v>130.39</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
     </row>
@@ -4423,13 +4423,13 @@
         <v>92.84999999999999</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>108.02</v>
+        <v>106.94</v>
       </c>
       <c r="D184" s="5" t="n">
         <v>120.51</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>140.19</v>
+        <v>138.79</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
     </row>
@@ -4443,13 +4443,13 @@
         <v>99.83</v>
       </c>
       <c r="C185" s="5" t="n">
-        <v>109.7</v>
+        <v>108.4</v>
       </c>
       <c r="D185" s="5" t="n">
         <v>129.34</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>142.13</v>
+        <v>140.44</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
     </row>
@@ -4463,13 +4463,13 @@
         <v>97.84</v>
       </c>
       <c r="C186" s="5" t="n">
-        <v>105.48</v>
+        <v>104.23</v>
       </c>
       <c r="D186" s="5" t="n">
         <v>126.54</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>136.42</v>
+        <v>134.81</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
     </row>
@@ -4483,13 +4483,13 @@
         <v>91.79000000000001</v>
       </c>
       <c r="C187" s="5" t="n">
-        <v>113.92</v>
+        <v>113.57</v>
       </c>
       <c r="D187" s="5" t="n">
         <v>118.51</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>147.09</v>
+        <v>146.63</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
     </row>
@@ -4503,13 +4503,13 @@
         <v>250.33</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>423.33</v>
+        <v>421.41</v>
       </c>
       <c r="D188" s="5" t="n">
         <v>323.22</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>546.6</v>
+        <v>544.12</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
     </row>
@@ -4523,13 +4523,13 @@
         <v>111.16</v>
       </c>
       <c r="C189" s="5" t="n">
-        <v>120.86</v>
+        <v>119.46</v>
       </c>
       <c r="D189" s="5" t="n">
         <v>143.54</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>156.06</v>
+        <v>154.25</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
     </row>
@@ -4543,13 +4543,13 @@
         <v>131.11</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>177.81</v>
+        <v>176.04</v>
       </c>
       <c r="D190" s="5" t="n">
         <v>169.3</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>229.61</v>
+        <v>227.32</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
     </row>
@@ -4563,13 +4563,13 @@
         <v>98.44</v>
       </c>
       <c r="C191" s="5" t="n">
-        <v>106.79</v>
+        <v>105.41</v>
       </c>
       <c r="D191" s="5" t="n">
         <v>126.87</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>137.63</v>
+        <v>135.85</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
     </row>
@@ -4583,13 +4583,13 @@
         <v>91.90000000000001</v>
       </c>
       <c r="C192" s="5" t="n">
-        <v>104.25</v>
+        <v>103.35</v>
       </c>
       <c r="D192" s="5" t="n">
         <v>118.2</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>134.09</v>
+        <v>132.93</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
     </row>
@@ -4603,13 +4603,13 @@
         <v>101.81</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>122.01</v>
+        <v>120.77</v>
       </c>
       <c r="D193" s="5" t="n">
         <v>130.69</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>156.62</v>
+        <v>155.03</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
     </row>
@@ -4623,13 +4623,13 @@
         <v>85.92</v>
       </c>
       <c r="C194" s="5" t="n">
-        <v>105.02</v>
+        <v>104.22</v>
       </c>
       <c r="D194" s="5" t="n">
         <v>110.09</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>134.56</v>
+        <v>133.53</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
     </row>
@@ -4643,13 +4643,13 @@
         <v>104.95</v>
       </c>
       <c r="C195" s="5" t="n">
-        <v>130.29</v>
+        <v>128.34</v>
       </c>
       <c r="D195" s="5" t="n">
         <v>134.22</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>166.62</v>
+        <v>164.13</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
     </row>
@@ -4663,13 +4663,13 @@
         <v>104.76</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>121.93</v>
+        <v>119.12</v>
       </c>
       <c r="D196" s="5" t="n">
         <v>133.72</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>155.64</v>
+        <v>152.05</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
     </row>
@@ -4683,13 +4683,13 @@
         <v>100.7</v>
       </c>
       <c r="C197" s="5" t="n">
-        <v>113.03</v>
+        <v>110.98</v>
       </c>
       <c r="D197" s="5" t="n">
         <v>128.25</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>143.95</v>
+        <v>141.34</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
     </row>
@@ -4703,13 +4703,13 @@
         <v>67.98</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>69.79000000000001</v>
+        <v>68.72</v>
       </c>
       <c r="D198" s="5" t="n">
         <v>86.38</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>88.68000000000001</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
     </row>
@@ -4723,13 +4723,13 @@
         <v>61.39</v>
       </c>
       <c r="C199" s="5" t="n">
-        <v>77.45999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="D199" s="5" t="n">
         <v>77.83</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>98.2</v>
+        <v>97.92</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
     </row>
@@ -4743,13 +4743,13 @@
         <v>142.95</v>
       </c>
       <c r="C200" s="5" t="n">
-        <v>255.88</v>
+        <v>255.49</v>
       </c>
       <c r="D200" s="5" t="n">
         <v>181.01</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>324</v>
+        <v>323.5</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
     </row>
@@ -4763,13 +4763,13 @@
         <v>48.31</v>
       </c>
       <c r="C201" s="5" t="n">
-        <v>55.83</v>
+        <v>55.07</v>
       </c>
       <c r="D201" s="5" t="n">
         <v>61.1</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>70.61</v>
+        <v>69.64</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
     </row>
@@ -4783,13 +4783,13 @@
         <v>43.3</v>
       </c>
       <c r="C202" s="5" t="n">
-        <v>50.47</v>
+        <v>49.68</v>
       </c>
       <c r="D202" s="5" t="n">
         <v>54.69</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>63.75</v>
+        <v>62.75</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
     </row>
@@ -4803,13 +4803,13 @@
         <v>34.83</v>
       </c>
       <c r="C203" s="5" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="D203" s="5" t="n">
         <v>44.28</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>53.27</v>
+        <v>53.14</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
     </row>
@@ -4823,13 +4823,13 @@
         <v>38.29</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>47.04</v>
+        <v>46.68</v>
       </c>
       <c r="D204" s="5" t="n">
         <v>48.99</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>60.19</v>
+        <v>59.73</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
     </row>
@@ -4843,13 +4843,13 @@
         <v>48.66</v>
       </c>
       <c r="C205" s="5" t="n">
-        <v>62.91</v>
+        <v>62.5</v>
       </c>
       <c r="D205" s="5" t="n">
         <v>62.67</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>81.02</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
     </row>
@@ -4863,13 +4863,13 @@
         <v>63.6</v>
       </c>
       <c r="C206" s="5" t="n">
-        <v>75.01000000000001</v>
+        <v>74.52</v>
       </c>
       <c r="D206" s="5" t="n">
         <v>81.48999999999999</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>96.11</v>
+        <v>95.48</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
     </row>
@@ -4883,13 +4883,13 @@
         <v>53.7</v>
       </c>
       <c r="C207" s="5" t="n">
-        <v>66.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D207" s="5" t="n">
         <v>68.45</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>84.64</v>
+        <v>83.62</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
     </row>
@@ -4903,13 +4903,13 @@
         <v>34.65</v>
       </c>
       <c r="C208" s="5" t="n">
-        <v>39.08</v>
+        <v>38.68</v>
       </c>
       <c r="D208" s="5" t="n">
         <v>43.94</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>49.56</v>
+        <v>49.06</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
     </row>
@@ -4923,13 +4923,13 @@
         <v>44.79</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>55.4</v>
+        <v>53.68</v>
       </c>
       <c r="D209" s="5" t="n">
         <v>56.63</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>70.05</v>
+        <v>67.88</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
     </row>
@@ -4943,13 +4943,13 @@
         <v>44.07</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>49.88</v>
+        <v>49.58</v>
       </c>
       <c r="D210" s="5" t="n">
         <v>55.56</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>62.88</v>
+        <v>62.5</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
     </row>
@@ -4963,13 +4963,13 @@
         <v>23.79</v>
       </c>
       <c r="C211" s="5" t="n">
-        <v>23.5</v>
+        <v>23.43</v>
       </c>
       <c r="D211" s="5" t="n">
         <v>29.9</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>29.54</v>
+        <v>29.45</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
     </row>
@@ -4983,13 +4983,13 @@
         <v>22.82</v>
       </c>
       <c r="C212" s="5" t="n">
-        <v>20.68</v>
+        <v>20.66</v>
       </c>
       <c r="D212" s="5" t="n">
         <v>28.63</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>25.94</v>
+        <v>25.92</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
     </row>
@@ -5003,13 +5003,13 @@
         <v>21.85</v>
       </c>
       <c r="C213" s="5" t="n">
-        <v>24.89</v>
+        <v>24.62</v>
       </c>
       <c r="D213" s="5" t="n">
         <v>27.36</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>31.16</v>
+        <v>30.83</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
     </row>
@@ -5023,13 +5023,13 @@
         <v>30.36</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>32.84</v>
+        <v>31.29</v>
       </c>
       <c r="D214" s="5" t="n">
         <v>37.94</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>41.04</v>
+        <v>39.1</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
     </row>
@@ -5043,13 +5043,13 @@
         <v>49.47</v>
       </c>
       <c r="C215" s="5" t="n">
-        <v>62.46</v>
+        <v>60.46</v>
       </c>
       <c r="D215" s="5" t="n">
         <v>61.67</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>77.86</v>
+        <v>75.37</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
     </row>
@@ -5063,13 +5063,13 @@
         <v>72.84</v>
       </c>
       <c r="C216" s="5" t="n">
-        <v>114.98</v>
+        <v>113.74</v>
       </c>
       <c r="D216" s="5" t="n">
         <v>90.58</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>142.99</v>
+        <v>141.45</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
     </row>
@@ -5083,13 +5083,13 @@
         <v>87.92</v>
       </c>
       <c r="C217" s="5" t="n">
-        <v>107.95</v>
+        <v>107.34</v>
       </c>
       <c r="D217" s="5" t="n">
         <v>109.07</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>133.92</v>
+        <v>133.16</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
     </row>
@@ -5103,13 +5103,13 @@
         <v>91.72</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>126.87</v>
+        <v>127.01</v>
       </c>
       <c r="D218" s="5" t="n">
         <v>113.46</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>156.95</v>
+        <v>157.12</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
     </row>
@@ -5123,13 +5123,13 @@
         <v>47</v>
       </c>
       <c r="C219" s="5" t="n">
-        <v>55.18</v>
+        <v>54.92</v>
       </c>
       <c r="D219" s="5" t="n">
         <v>57.98</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>68.06999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
     </row>
@@ -5143,13 +5143,13 @@
         <v>27.72</v>
       </c>
       <c r="C220" s="5" t="n">
-        <v>33.73</v>
+        <v>33.28</v>
       </c>
       <c r="D220" s="5" t="n">
         <v>34.1</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>41.49</v>
+        <v>40.94</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
     </row>
@@ -5163,13 +5163,13 @@
         <v>18.46</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>15.09</v>
+        <v>15.04</v>
       </c>
       <c r="D221" s="5" t="n">
         <v>22.61</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>18.48</v>
+        <v>18.42</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
     </row>
@@ -5183,13 +5183,13 @@
         <v>35.02</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>40.78</v>
+        <v>40.75</v>
       </c>
       <c r="D222" s="5" t="n">
         <v>42.72</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>49.74</v>
+        <v>49.71</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
     </row>
@@ -5203,13 +5203,13 @@
         <v>32.23</v>
       </c>
       <c r="C223" s="5" t="n">
-        <v>30.8</v>
+        <v>30.93</v>
       </c>
       <c r="D223" s="5" t="n">
         <v>39.15</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>37.41</v>
+        <v>37.57</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
     </row>
@@ -5223,13 +5223,13 @@
         <v>60.82</v>
       </c>
       <c r="C224" s="5" t="n">
-        <v>75.01000000000001</v>
+        <v>75.05</v>
       </c>
       <c r="D224" s="5" t="n">
         <v>73.34999999999999</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>90.45999999999999</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
     </row>
@@ -5243,13 +5243,13 @@
         <v>54.17</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>48.54</v>
+        <v>48.46</v>
       </c>
       <c r="D225" s="5" t="n">
         <v>64.86</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>58.12</v>
+        <v>58.03</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
     </row>
@@ -5263,13 +5263,13 @@
         <v>54.78</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>56.47</v>
+        <v>56.21</v>
       </c>
       <c r="D226" s="5" t="n">
         <v>65.13</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>67.14</v>
+        <v>66.83</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
     </row>
@@ -5283,13 +5283,13 @@
         <v>141.51</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>168.15</v>
+        <v>167.79</v>
       </c>
       <c r="D227" s="5" t="n">
         <v>167.25</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>198.74</v>
+        <v>198.31</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
     </row>
@@ -5303,13 +5303,13 @@
         <v>233.64</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>264.24</v>
+        <v>264.05</v>
       </c>
       <c r="D228" s="5" t="n">
         <v>274.51</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>310.47</v>
+        <v>310.24</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
     </row>
@@ -5323,13 +5323,13 @@
         <v>296.49</v>
       </c>
       <c r="C229" s="5" t="n">
-        <v>375.96</v>
+        <v>375.27</v>
       </c>
       <c r="D229" s="5" t="n">
         <v>346.32</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>439.14</v>
+        <v>438.34</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
     </row>
@@ -5343,13 +5343,13 @@
         <v>340.34</v>
       </c>
       <c r="C230" s="5" t="n">
-        <v>432</v>
+        <v>431.21</v>
       </c>
       <c r="D230" s="5" t="n">
         <v>395.12</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>501.53</v>
+        <v>500.61</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
     </row>
@@ -5363,13 +5363,13 @@
         <v>121.01</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>137.33</v>
+        <v>136.75</v>
       </c>
       <c r="D231" s="5" t="n">
         <v>139.64</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>158.47</v>
+        <v>157.8</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
     </row>
@@ -5383,13 +5383,13 @@
         <v>111.77</v>
       </c>
       <c r="C232" s="5" t="n">
-        <v>130.9</v>
+        <v>130.63</v>
       </c>
       <c r="D232" s="5" t="n">
         <v>128.2</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>150.14</v>
+        <v>149.83</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
     </row>
@@ -5403,13 +5403,13 @@
         <v>98.90000000000001</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>97.36</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="D233" s="5" t="n">
         <v>112.74</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>110.98</v>
+        <v>110.56</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
     </row>
@@ -5423,13 +5423,13 @@
         <v>58.63</v>
       </c>
       <c r="C234" s="5" t="n">
-        <v>58.3</v>
+        <v>58.52</v>
       </c>
       <c r="D234" s="5" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>66.05</v>
+        <v>66.3</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
     </row>
@@ -5443,13 +5443,13 @@
         <v>31.28</v>
       </c>
       <c r="C235" s="5" t="n">
-        <v>11.57</v>
+        <v>11.86</v>
       </c>
       <c r="D235" s="5" t="n">
         <v>35.23</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>13.03</v>
+        <v>13.36</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
     </row>
@@ -5463,13 +5463,13 @@
         <v>48.09</v>
       </c>
       <c r="C236" s="5" t="n">
-        <v>32.05</v>
+        <v>32.16</v>
       </c>
       <c r="D236" s="5" t="n">
         <v>53.91</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>35.93</v>
+        <v>36.05</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
     </row>
@@ -5483,13 +5483,13 @@
         <v>58.01</v>
       </c>
       <c r="C237" s="5" t="n">
-        <v>55.29</v>
+        <v>55.28</v>
       </c>
       <c r="D237" s="5" t="n">
         <v>64.73999999999999</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>61.71</v>
+        <v>61.7</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
     </row>
@@ -5503,13 +5503,13 @@
         <v>62.02</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>54.59</v>
+        <v>54.34</v>
       </c>
       <c r="D238" s="5" t="n">
         <v>68.91</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>60.65</v>
+        <v>60.38</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
     </row>
@@ -5523,13 +5523,13 @@
         <v>83.62</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>86.78</v>
+        <v>86.66</v>
       </c>
       <c r="D239" s="5" t="n">
         <v>92.65000000000001</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>96.15000000000001</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
     </row>
@@ -5543,13 +5543,13 @@
         <v>127.15</v>
       </c>
       <c r="C240" s="5" t="n">
-        <v>145.97</v>
+        <v>145.34</v>
       </c>
       <c r="D240" s="5" t="n">
         <v>140.47</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>161.26</v>
+        <v>160.57</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
     </row>
@@ -5563,13 +5563,13 @@
         <v>54.53</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>85.79000000000001</v>
+        <v>85.58</v>
       </c>
       <c r="D241" s="5" t="n">
         <v>60.07</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>94.51000000000001</v>
+        <v>94.28</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
     </row>
@@ -5583,13 +5583,13 @@
         <v>55.21</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>76.38</v>
+        <v>75.97</v>
       </c>
       <c r="D242" s="5" t="n">
         <v>60.59</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>83.81999999999999</v>
+        <v>83.37</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
     </row>
@@ -5603,13 +5603,13 @@
         <v>64.66</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>80.04000000000001</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="D243" s="5" t="n">
         <v>70.69</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>87.5</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
     </row>
@@ -5623,13 +5623,13 @@
         <v>26.31</v>
       </c>
       <c r="C244" s="5" t="n">
-        <v>28.16</v>
+        <v>28.25</v>
       </c>
       <c r="D244" s="5" t="n">
         <v>28.65</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>30.67</v>
+        <v>30.77</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
     </row>
@@ -5643,13 +5643,13 @@
         <v>17.19</v>
       </c>
       <c r="C245" s="5" t="n">
-        <v>15.14</v>
+        <v>15.18</v>
       </c>
       <c r="D245" s="5" t="n">
         <v>18.68</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>16.45</v>
+        <v>16.5</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
     </row>
@@ -5663,13 +5663,13 @@
         <v>34.94</v>
       </c>
       <c r="C246" s="5" t="n">
-        <v>31.79</v>
+        <v>31.91</v>
       </c>
       <c r="D246" s="5" t="n">
         <v>37.89</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>34.48</v>
+        <v>34.61</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
     </row>
@@ -5683,13 +5683,13 @@
         <v>25.29</v>
       </c>
       <c r="C247" s="5" t="n">
-        <v>25.23</v>
+        <v>25.38</v>
       </c>
       <c r="D247" s="5" t="n">
         <v>27.37</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>27.31</v>
+        <v>27.47</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
     </row>
@@ -5703,13 +5703,13 @@
         <v>22.1</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>17.65</v>
+        <v>17.76</v>
       </c>
       <c r="D248" s="5" t="n">
         <v>23.84</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>19.04</v>
+        <v>19.16</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
     </row>
@@ -5723,13 +5723,13 @@
         <v>82.94</v>
       </c>
       <c r="C249" s="5" t="n">
-        <v>133.13</v>
+        <v>133.12</v>
       </c>
       <c r="D249" s="5" t="n">
         <v>89.20999999999999</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>143.2</v>
+        <v>143.19</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
     </row>
@@ -5743,13 +5743,13 @@
         <v>51.99</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>46.25</v>
+        <v>46.11</v>
       </c>
       <c r="D250" s="5" t="n">
         <v>55.75</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>49.59</v>
+        <v>49.44</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
     </row>
@@ -5763,13 +5763,13 @@
         <v>84.8</v>
       </c>
       <c r="C251" s="5" t="n">
-        <v>80.23</v>
+        <v>79.92</v>
       </c>
       <c r="D251" s="5" t="n">
         <v>90.62</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>85.73</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
     </row>
@@ -5783,13 +5783,13 @@
         <v>132.97</v>
       </c>
       <c r="C252" s="5" t="n">
-        <v>146.58</v>
+        <v>145.96</v>
       </c>
       <c r="D252" s="5" t="n">
         <v>141.6</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>156.09</v>
+        <v>155.43</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
     </row>
@@ -5803,13 +5803,13 @@
         <v>164.23</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>198.82</v>
+        <v>198.44</v>
       </c>
       <c r="D253" s="5" t="n">
         <v>174.28</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>210.99</v>
+        <v>210.58</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
     </row>
@@ -5823,13 +5823,13 @@
         <v>149.14</v>
       </c>
       <c r="C254" s="5" t="n">
-        <v>191.83</v>
+        <v>191.27</v>
       </c>
       <c r="D254" s="5" t="n">
         <v>158.15</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>203.42</v>
+        <v>202.83</v>
       </c>
       <c r="F254" s="7" t="inlineStr"/>
     </row>
@@ -5843,13 +5843,13 @@
         <v>143.4</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>216.14</v>
+        <v>215.57</v>
       </c>
       <c r="D255" s="5" t="n">
         <v>151.95</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>229.03</v>
+        <v>228.43</v>
       </c>
       <c r="F255" s="7" t="inlineStr"/>
     </row>
@@ -5883,13 +5883,13 @@
         <v>20.36</v>
       </c>
       <c r="C257" s="5" t="n">
-        <v>10.18</v>
+        <v>10.31</v>
       </c>
       <c r="D257" s="5" t="n">
         <v>21.54</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>10.77</v>
+        <v>10.91</v>
       </c>
       <c r="F257" s="7" t="inlineStr"/>
     </row>
@@ -5903,13 +5903,13 @@
         <v>64.08</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>52.94</v>
+        <v>53.17</v>
       </c>
       <c r="D258" s="5" t="n">
         <v>67.76000000000001</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>55.98</v>
+        <v>56.23</v>
       </c>
       <c r="F258" s="7" t="inlineStr"/>
     </row>
@@ -5923,13 +5923,13 @@
         <v>52.25</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>39.93</v>
+        <v>40.31</v>
       </c>
       <c r="D259" s="5" t="n">
         <v>55.22</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>42.2</v>
+        <v>42.6</v>
       </c>
       <c r="F259" s="7" t="inlineStr"/>
     </row>
@@ -5943,13 +5943,13 @@
         <v>48.35</v>
       </c>
       <c r="C260" s="5" t="n">
-        <v>23.72</v>
+        <v>23.93</v>
       </c>
       <c r="D260" s="5" t="n">
         <v>50.94</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>24.99</v>
+        <v>25.21</v>
       </c>
       <c r="F260" s="7" t="inlineStr"/>
     </row>
@@ -5963,13 +5963,13 @@
         <v>68.55</v>
       </c>
       <c r="C261" s="5" t="n">
-        <v>76.73</v>
+        <v>76.84</v>
       </c>
       <c r="D261" s="5" t="n">
         <v>72</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>80.59999999999999</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="F261" s="7" t="inlineStr"/>
     </row>
@@ -5983,13 +5983,13 @@
         <v>61.75</v>
       </c>
       <c r="C262" s="5" t="n">
-        <v>62.93</v>
+        <v>62.81</v>
       </c>
       <c r="D262" s="5" t="n">
         <v>64.66</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>65.90000000000001</v>
+        <v>65.77</v>
       </c>
       <c r="F262" s="7" t="inlineStr"/>
     </row>
@@ -6003,13 +6003,13 @@
         <v>74.76000000000001</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>70.56</v>
+        <v>70.45</v>
       </c>
       <c r="D263" s="5" t="n">
         <v>78.09</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>73.70999999999999</v>
+        <v>73.59</v>
       </c>
       <c r="F263" s="7" t="inlineStr"/>
     </row>
@@ -6023,13 +6023,13 @@
         <v>78.05</v>
       </c>
       <c r="C264" s="5" t="n">
-        <v>93.92</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="D264" s="5" t="n">
         <v>81.33</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>97.86</v>
+        <v>97.61</v>
       </c>
       <c r="F264" s="7" t="inlineStr"/>
     </row>
@@ -6043,13 +6043,13 @@
         <v>264.6</v>
       </c>
       <c r="C265" s="5" t="n">
-        <v>463.18</v>
+        <v>462.78</v>
       </c>
       <c r="D265" s="5" t="n">
         <v>275.03</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>481.44</v>
+        <v>481.02</v>
       </c>
       <c r="F265" s="7" t="inlineStr"/>
     </row>
@@ -6063,13 +6063,13 @@
         <v>82.13</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>107.96</v>
+        <v>107.55</v>
       </c>
       <c r="D266" s="5" t="n">
         <v>84.98999999999999</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>111.72</v>
+        <v>111.3</v>
       </c>
       <c r="F266" s="7" t="inlineStr"/>
     </row>
@@ -6083,13 +6083,13 @@
         <v>93.19</v>
       </c>
       <c r="C267" s="5" t="n">
-        <v>107.79</v>
+        <v>107.41</v>
       </c>
       <c r="D267" s="5" t="n">
         <v>96.02</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>111.06</v>
+        <v>110.67</v>
       </c>
       <c r="F267" s="7" t="inlineStr"/>
     </row>
@@ -6103,13 +6103,13 @@
         <v>55.27</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>61.8</v>
+        <v>61.94</v>
       </c>
       <c r="D268" s="5" t="n">
         <v>56.7</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>63.4</v>
+        <v>63.54</v>
       </c>
       <c r="F268" s="7" t="inlineStr"/>
     </row>
@@ -6123,13 +6123,13 @@
         <v>51.37</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>45.13</v>
+        <v>45.17</v>
       </c>
       <c r="D269" s="5" t="n">
         <v>52.6</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>46.21</v>
+        <v>46.25</v>
       </c>
       <c r="F269" s="7" t="inlineStr"/>
     </row>
@@ -6143,13 +6143,13 @@
         <v>31.92</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>13.79</v>
+        <v>14.11</v>
       </c>
       <c r="D270" s="5" t="n">
         <v>32.62</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>14.09</v>
+        <v>14.42</v>
       </c>
       <c r="F270" s="7" t="inlineStr"/>
     </row>
@@ -6163,13 +6163,13 @@
         <v>27.51</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>16.99</v>
+        <v>17.32</v>
       </c>
       <c r="D271" s="5" t="n">
         <v>28.06</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>17.33</v>
+        <v>17.66</v>
       </c>
       <c r="F271" s="7" t="inlineStr"/>
     </row>
@@ -6183,13 +6183,13 @@
         <v>38.55</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>43.74</v>
+        <v>43.95</v>
       </c>
       <c r="D272" s="5" t="n">
         <v>39.14</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>44.4</v>
+        <v>44.62</v>
       </c>
       <c r="F272" s="7" t="inlineStr"/>
     </row>
@@ -6203,13 +6203,13 @@
         <v>45.06</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>40.2</v>
+        <v>40.32</v>
       </c>
       <c r="D273" s="5" t="n">
         <v>45.54</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>40.62</v>
+        <v>40.75</v>
       </c>
       <c r="F273" s="7" t="inlineStr"/>
     </row>
@@ -6223,13 +6223,13 @@
         <v>44.74</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>44.69</v>
+        <v>44.57</v>
       </c>
       <c r="D274" s="5" t="n">
         <v>45.01</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>44.96</v>
+        <v>44.84</v>
       </c>
       <c r="F274" s="7" t="inlineStr"/>
     </row>
@@ -6243,13 +6243,13 @@
         <v>35.68</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>37.67</v>
+        <v>37.64</v>
       </c>
       <c r="D275" s="5" t="n">
         <v>35.82</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>37.82</v>
+        <v>37.79</v>
       </c>
       <c r="F275" s="7" t="inlineStr"/>
     </row>
@@ -6263,13 +6263,13 @@
         <v>64.77</v>
       </c>
       <c r="C276" s="5" t="n">
-        <v>73.73999999999999</v>
+        <v>73.55</v>
       </c>
       <c r="D276" s="5" t="n">
         <v>64.90000000000001</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>73.89</v>
+        <v>73.7</v>
       </c>
       <c r="F276" s="7" t="inlineStr"/>
     </row>
@@ -6283,13 +6283,13 @@
         <v>66.81</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>78.04000000000001</v>
+        <v>77.88</v>
       </c>
       <c r="D277" s="5" t="n">
         <v>66.81</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>78.04000000000001</v>
+        <v>77.88</v>
       </c>
       <c r="F277" s="7" t="inlineStr"/>
     </row>
@@ -6303,13 +6303,13 @@
         <v>70.36</v>
       </c>
       <c r="C278" s="5" t="n">
-        <v>90.75</v>
+        <v>90.62</v>
       </c>
       <c r="D278" s="5" t="n">
         <v>70.36</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>90.75</v>
+        <v>90.62</v>
       </c>
       <c r="F278" s="7" t="inlineStr"/>
     </row>
@@ -6323,13 +6323,13 @@
         <v>60.4</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>68.86</v>
+        <v>68.78</v>
       </c>
       <c r="D279" s="5" t="n">
         <v>60.4</v>
       </c>
       <c r="E279" s="5" t="n">
-        <v>68.86</v>
+        <v>68.78</v>
       </c>
       <c r="F279" s="7" t="inlineStr"/>
     </row>
@@ -6343,13 +6343,13 @@
         <v>36.83</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>36.93</v>
+        <v>37.02</v>
       </c>
       <c r="D280" s="5" t="n">
         <v>36.83</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>36.93</v>
+        <v>37.02</v>
       </c>
       <c r="F280" s="7" t="inlineStr"/>
     </row>
@@ -6411,13 +6411,13 @@
         <v>25.62</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>32.99</v>
+        <v>33.07</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>47.9</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>61.68</v>
+        <v>61.83</v>
       </c>
     </row>
     <row r="3">
@@ -6430,13 +6430,13 @@
         <v>20.15</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>23.45</v>
+        <v>23.54</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>37.6</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>43.76</v>
+        <v>43.93</v>
       </c>
     </row>
     <row r="4">
@@ -6449,13 +6449,13 @@
         <v>20.73</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>25.19</v>
+        <v>25.18</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>38.61</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>46.92</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="5">
@@ -6468,13 +6468,13 @@
         <v>20.74</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25.19</v>
+        <v>25.05</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>38.56</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>46.84</v>
+        <v>46.57</v>
       </c>
     </row>
     <row r="6">
@@ -6487,13 +6487,13 @@
         <v>21.18</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>26.23</v>
+        <v>25.87</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>39.31</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>48.68</v>
+        <v>48.02</v>
       </c>
     </row>
     <row r="7">
@@ -6506,13 +6506,13 @@
         <v>24.97</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>34.01</v>
+        <v>33.9</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>46.26</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>63.01</v>
+        <v>62.81</v>
       </c>
     </row>
     <row r="8">
@@ -6525,13 +6525,13 @@
         <v>22.52</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>30.37</v>
+        <v>30.13</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>41.6</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>56.1</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="9">
@@ -6544,13 +6544,13 @@
         <v>38.62</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>48.76</v>
+        <v>48.3</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>71.13</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>89.81</v>
+        <v>88.95999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -6563,13 +6563,13 @@
         <v>21.48</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>28.54</v>
+        <v>28.1</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>39.45</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>52.41</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="11">
@@ -6582,13 +6582,13 @@
         <v>29.46</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>36.99</v>
+        <v>36.91</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>54.02</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>67.83</v>
+        <v>67.68000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -6601,13 +6601,13 @@
         <v>31.29</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>39.67</v>
+        <v>39.52</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>57.29</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>72.63</v>
+        <v>72.34999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -6620,13 +6620,13 @@
         <v>28.63</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>34.73</v>
+        <v>34.78</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>52.33</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>63.48</v>
+        <v>63.58</v>
       </c>
     </row>
     <row r="14">
@@ -6639,13 +6639,13 @@
         <v>31.37</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>43.7</v>
+        <v>43.74</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>57.26</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>79.77</v>
+        <v>79.84</v>
       </c>
     </row>
     <row r="15">
@@ -6658,13 +6658,13 @@
         <v>22.55</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>27.37</v>
+        <v>27.28</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>41.11</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>49.89</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="16">
@@ -6677,13 +6677,13 @@
         <v>27.2</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>31.48</v>
+        <v>31.28</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>49.52</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>57.31</v>
+        <v>56.94</v>
       </c>
     </row>
     <row r="17">
@@ -6696,13 +6696,13 @@
         <v>44.88</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>70.45</v>
+        <v>70.44</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>81.48999999999999</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>127.93</v>
+        <v>127.91</v>
       </c>
     </row>
     <row r="18">
@@ -6715,13 +6715,13 @@
         <v>35.66</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>44.55</v>
+        <v>43.97</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>64.59</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>80.69</v>
+        <v>79.64</v>
       </c>
     </row>
     <row r="19">
@@ -6734,13 +6734,13 @@
         <v>27.36</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>33</v>
+        <v>32.66</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>49.43</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>59.62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -6753,13 +6753,13 @@
         <v>22.84</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>29.72</v>
+        <v>29.7</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>41.17</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>53.57</v>
+        <v>53.54</v>
       </c>
     </row>
     <row r="21">
@@ -6772,13 +6772,13 @@
         <v>21.83</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>27.43</v>
+        <v>27.12</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>39.26</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>49.34</v>
+        <v>48.78</v>
       </c>
     </row>
     <row r="22">
@@ -6791,13 +6791,13 @@
         <v>18.7</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>21.15</v>
+        <v>20.94</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>33.56</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>37.96</v>
+        <v>37.58</v>
       </c>
     </row>
     <row r="23">
@@ -6810,13 +6810,13 @@
         <v>30.63</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>37.8</v>
+        <v>37.71</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>54.86</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>67.7</v>
+        <v>67.54000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -6829,13 +6829,13 @@
         <v>24.56</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>43.9</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>52.19</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="25">
@@ -6848,13 +6848,13 @@
         <v>23.54</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>27.29</v>
+        <v>27.23</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>41.99</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>48.68</v>
+        <v>48.58</v>
       </c>
     </row>
     <row r="26">
@@ -6867,13 +6867,13 @@
         <v>26.51</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>32.37</v>
+        <v>32.3</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>47.14</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>57.56</v>
+        <v>57.43</v>
       </c>
     </row>
     <row r="27">
@@ -6886,13 +6886,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>40.25</v>
+        <v>40.15</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>53.17</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>71.33</v>
+        <v>71.15000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -6905,13 +6905,13 @@
         <v>29.14</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>37.44</v>
+        <v>37.3</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>51.47</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>66.13</v>
+        <v>65.89</v>
       </c>
     </row>
     <row r="29">
@@ -6924,13 +6924,13 @@
         <v>22.64</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>28.49</v>
+        <v>28.44</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>39.92</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>50.24</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="30">
@@ -6943,13 +6943,13 @@
         <v>30.7</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>46.39</v>
+        <v>46.09</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>54.04</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>81.66</v>
+        <v>81.13</v>
       </c>
     </row>
     <row r="31">
@@ -6962,13 +6962,13 @@
         <v>34.24</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>49.23</v>
+        <v>49.13</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>60.17</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>86.51000000000001</v>
+        <v>86.34</v>
       </c>
     </row>
     <row r="32">
@@ -6981,13 +6981,13 @@
         <v>53.44</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>88.63</v>
+        <v>88.39</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>93.64</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>155.3</v>
+        <v>154.88</v>
       </c>
     </row>
     <row r="33">
@@ -7000,13 +7000,13 @@
         <v>56</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>105.51</v>
+        <v>105.26</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>97.84999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>184.36</v>
+        <v>183.92</v>
       </c>
     </row>
     <row r="34">
@@ -7019,13 +7019,13 @@
         <v>23.36</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>29.33</v>
+        <v>29.05</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>40.7</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>51.1</v>
+        <v>50.61</v>
       </c>
     </row>
     <row r="35">
@@ -7038,13 +7038,13 @@
         <v>22.59</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>27.86</v>
+        <v>27.89</v>
       </c>
       <c r="D35" s="5" t="n">
         <v>39.15</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>48.29</v>
+        <v>48.34</v>
       </c>
     </row>
     <row r="36">
@@ -7057,13 +7057,13 @@
         <v>28.25</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>37.94</v>
+        <v>37.92</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>48.71</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>65.41</v>
+        <v>65.38</v>
       </c>
     </row>
     <row r="37">
@@ -7076,13 +7076,13 @@
         <v>34.61</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>42.49</v>
+        <v>42.6</v>
       </c>
       <c r="D37" s="5" t="n">
         <v>59.36</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>72.88</v>
+        <v>73.06999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -7095,13 +7095,13 @@
         <v>47.2</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>71.86</v>
+        <v>71.95</v>
       </c>
       <c r="D38" s="5" t="n">
         <v>80.72</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>122.89</v>
+        <v>123.04</v>
       </c>
     </row>
     <row r="39">
@@ -7114,13 +7114,13 @@
         <v>32.21</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>39.11</v>
+        <v>38.93</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>54.92</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>66.69</v>
+        <v>66.38</v>
       </c>
     </row>
     <row r="40">
@@ -7133,13 +7133,13 @@
         <v>30.8</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>38.91</v>
+        <v>38.74</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>52.36</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>66.15000000000001</v>
+        <v>65.86</v>
       </c>
     </row>
     <row r="41">
@@ -7152,13 +7152,13 @@
         <v>27.66</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>34.69</v>
+        <v>34.58</v>
       </c>
       <c r="D41" s="5" t="n">
         <v>47.04</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>59</v>
+        <v>58.81</v>
       </c>
     </row>
     <row r="42">
@@ -7171,13 +7171,13 @@
         <v>32.71</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>42.78</v>
+        <v>42.04</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>55.65</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>72.79000000000001</v>
+        <v>71.53</v>
       </c>
     </row>
     <row r="43">
@@ -7190,13 +7190,13 @@
         <v>22.28</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>28.32</v>
+        <v>28.05</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>37.92</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>48.2</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="44">
@@ -7209,13 +7209,13 @@
         <v>91.45999999999999</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>165.37</v>
+        <v>165.27</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>155.63</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>281.39</v>
+        <v>281.22</v>
       </c>
     </row>
     <row r="45">
@@ -7228,13 +7228,13 @@
         <v>47.44</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>69.13</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="D45" s="5" t="n">
         <v>80.7</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>117.6</v>
+        <v>116.64</v>
       </c>
     </row>
     <row r="46">
@@ -7247,13 +7247,13 @@
         <v>53.28</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>74.84999999999999</v>
+        <v>74.37</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>90.61</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>127.29</v>
+        <v>126.48</v>
       </c>
     </row>
     <row r="47">
@@ -7266,13 +7266,13 @@
         <v>67.76000000000001</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>81.62</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>114.76</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>138.24</v>
+        <v>137.17</v>
       </c>
     </row>
     <row r="48">
@@ -7285,13 +7285,13 @@
         <v>62.64</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>75.48999999999999</v>
+        <v>74.97</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>105.66</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>127.34</v>
+        <v>126.46</v>
       </c>
     </row>
     <row r="49">
@@ -7304,13 +7304,13 @@
         <v>143.28</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>218.05</v>
+        <v>218.49</v>
       </c>
       <c r="D49" s="5" t="n">
         <v>240.71</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>366.32</v>
+        <v>367.06</v>
       </c>
     </row>
     <row r="50">
@@ -7323,13 +7323,13 @@
         <v>85.55</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>115.22</v>
+        <v>114.96</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>143.39</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>193.12</v>
+        <v>192.69</v>
       </c>
     </row>
     <row r="51">
@@ -7342,13 +7342,13 @@
         <v>41.73</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>50.83</v>
+        <v>50.52</v>
       </c>
       <c r="D51" s="5" t="n">
         <v>69.78</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>85</v>
+        <v>84.48</v>
       </c>
     </row>
     <row r="52">
@@ -7361,13 +7361,13 @@
         <v>44.58</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>55.04</v>
+        <v>54.66</v>
       </c>
       <c r="D52" s="5" t="n">
         <v>74.38</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>91.83</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="53">
@@ -7380,13 +7380,13 @@
         <v>35.51</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>45.32</v>
+        <v>45.03</v>
       </c>
       <c r="D53" s="5" t="n">
         <v>59.06</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>75.38</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -7399,13 +7399,13 @@
         <v>42.73</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>54.55</v>
+        <v>53.86</v>
       </c>
       <c r="D54" s="5" t="n">
         <v>70.84999999999999</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>90.45</v>
+        <v>89.31</v>
       </c>
     </row>
     <row r="55">
@@ -7418,13 +7418,13 @@
         <v>44.79</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>62.08</v>
+        <v>61.74</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>74.04000000000001</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>102.62</v>
+        <v>102.06</v>
       </c>
     </row>
     <row r="56">
@@ -7437,13 +7437,13 @@
         <v>40.37</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>55.11</v>
+        <v>54.78</v>
       </c>
       <c r="D56" s="5" t="n">
         <v>66.44</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>90.7</v>
+        <v>90.15000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -7456,13 +7456,13 @@
         <v>36.88</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>52.11</v>
+        <v>51.53</v>
       </c>
       <c r="D57" s="5" t="n">
         <v>60.43</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>85.38</v>
+        <v>84.43000000000001</v>
       </c>
     </row>
     <row r="58">
@@ -7475,13 +7475,13 @@
         <v>52.14</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>84.56999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>85.05</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>137.95</v>
+        <v>137.19</v>
       </c>
     </row>
     <row r="59">
@@ -7494,13 +7494,13 @@
         <v>39.86</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>50.14</v>
+        <v>49.7</v>
       </c>
       <c r="D59" s="5" t="n">
         <v>64.70999999999999</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>81.40000000000001</v>
+        <v>80.68000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -7513,13 +7513,13 @@
         <v>54.03</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>64.59</v>
+        <v>63.89</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>87.29000000000001</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>104.35</v>
+        <v>103.22</v>
       </c>
     </row>
     <row r="61">
@@ -7532,13 +7532,13 @@
         <v>42.04</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>52.09</v>
+        <v>51.98</v>
       </c>
       <c r="D61" s="5" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>83.75</v>
+        <v>83.58</v>
       </c>
     </row>
     <row r="62">
@@ -7551,13 +7551,13 @@
         <v>43.04</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>60.12</v>
+        <v>60.1</v>
       </c>
       <c r="D62" s="5" t="n">
         <v>68.94</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>96.29000000000001</v>
+        <v>96.26000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -7570,13 +7570,13 @@
         <v>40.91</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>50.92</v>
+        <v>50.49</v>
       </c>
       <c r="D63" s="5" t="n">
         <v>65.27</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>81.23999999999999</v>
+        <v>80.56</v>
       </c>
     </row>
     <row r="64">
@@ -7589,13 +7589,13 @@
         <v>36.62</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>47.77</v>
+        <v>47.53</v>
       </c>
       <c r="D64" s="5" t="n">
         <v>58.2</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>75.93000000000001</v>
+        <v>75.54000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -7608,13 +7608,13 @@
         <v>39.37</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>51.76</v>
+        <v>50.87</v>
       </c>
       <c r="D65" s="5" t="n">
         <v>62.64</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>82.36</v>
+        <v>80.94</v>
       </c>
     </row>
     <row r="66">
@@ -7627,13 +7627,13 @@
         <v>34.56</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>45.33</v>
+        <v>44.54</v>
       </c>
       <c r="D66" s="5" t="n">
         <v>55.05</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>72.2</v>
+        <v>70.95</v>
       </c>
     </row>
     <row r="67">
@@ -7646,13 +7646,13 @@
         <v>22.49</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>27.82</v>
+        <v>27.59</v>
       </c>
       <c r="D67" s="5" t="n">
         <v>35.86</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>44.36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68">
@@ -7665,13 +7665,13 @@
         <v>125.54</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>248.2</v>
+        <v>248.01</v>
       </c>
       <c r="D68" s="5" t="n">
         <v>200.11</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>395.64</v>
+        <v>395.33</v>
       </c>
     </row>
     <row r="69">
@@ -7684,13 +7684,13 @@
         <v>33.4</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>44.74</v>
+        <v>44.12</v>
       </c>
       <c r="D69" s="5" t="n">
         <v>53.22</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>71.29000000000001</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="70">
@@ -7703,13 +7703,13 @@
         <v>25.27</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>32.56</v>
+        <v>32.01</v>
       </c>
       <c r="D70" s="5" t="n">
         <v>40.25</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>51.86</v>
+        <v>50.99</v>
       </c>
     </row>
     <row r="71">
@@ -7722,13 +7722,13 @@
         <v>37.3</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>49.27</v>
+        <v>48.96</v>
       </c>
       <c r="D71" s="5" t="n">
         <v>59.32</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>78.34999999999999</v>
+        <v>77.86</v>
       </c>
     </row>
     <row r="72">
@@ -7741,13 +7741,13 @@
         <v>31.45</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>37.87</v>
+        <v>37.6</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>49.93</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>60.12</v>
+        <v>59.69</v>
       </c>
     </row>
     <row r="73">
@@ -7760,13 +7760,13 @@
         <v>30.07</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>37.13</v>
+        <v>37.07</v>
       </c>
       <c r="D73" s="5" t="n">
         <v>47.66</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>58.85</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="74">
@@ -7779,13 +7779,13 @@
         <v>26.84</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>32.55</v>
+        <v>32.46</v>
       </c>
       <c r="D74" s="5" t="n">
         <v>42.41</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>51.43</v>
+        <v>51.29</v>
       </c>
     </row>
     <row r="75">
@@ -7798,13 +7798,13 @@
         <v>22.44</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>28.02</v>
+        <v>27.81</v>
       </c>
       <c r="D75" s="5" t="n">
         <v>35.34</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>44.13</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="76">
@@ -7817,13 +7817,13 @@
         <v>22.94</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>27.43</v>
+        <v>27.42</v>
       </c>
       <c r="D76" s="5" t="n">
         <v>36.02</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>43.07</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="77">
@@ -7836,13 +7836,13 @@
         <v>25.56</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>31.55</v>
+        <v>30.83</v>
       </c>
       <c r="D77" s="5" t="n">
         <v>40.06</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>49.45</v>
+        <v>48.32</v>
       </c>
     </row>
     <row r="78">
@@ -7855,13 +7855,13 @@
         <v>32.43</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>44.98</v>
+        <v>44.77</v>
       </c>
       <c r="D78" s="5" t="n">
         <v>50.74</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>70.37</v>
+        <v>70.04000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -7874,13 +7874,13 @@
         <v>23.51</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>29.49</v>
+        <v>29.38</v>
       </c>
       <c r="D79" s="5" t="n">
         <v>36.72</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>46.06</v>
+        <v>45.88</v>
       </c>
     </row>
     <row r="80">
@@ -7893,13 +7893,13 @@
         <v>60.95</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>114.74</v>
+        <v>114.66</v>
       </c>
       <c r="D80" s="5" t="n">
         <v>94.89</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>178.64</v>
+        <v>178.52</v>
       </c>
     </row>
     <row r="81">
@@ -7912,13 +7912,13 @@
         <v>67.91</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>124.09</v>
+        <v>123.77</v>
       </c>
       <c r="D81" s="5" t="n">
         <v>105.4</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>192.6</v>
+        <v>192.1</v>
       </c>
     </row>
     <row r="82">
@@ -7931,13 +7931,13 @@
         <v>22.86</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>27.11</v>
+        <v>26.87</v>
       </c>
       <c r="D82" s="5" t="n">
         <v>35.37</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>41.95</v>
+        <v>41.58</v>
       </c>
     </row>
     <row r="83">
@@ -7950,13 +7950,13 @@
         <v>71.56</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>131.25</v>
+        <v>131.27</v>
       </c>
       <c r="D83" s="5" t="n">
         <v>110.5</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>202.68</v>
+        <v>202.71</v>
       </c>
     </row>
     <row r="84">
@@ -7969,13 +7969,13 @@
         <v>30.49</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>34.97</v>
+        <v>34.5</v>
       </c>
       <c r="D84" s="5" t="n">
         <v>46.99</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>53.89</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="85">
@@ -7988,13 +7988,13 @@
         <v>31.4</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>36.19</v>
+        <v>36.24</v>
       </c>
       <c r="D85" s="5" t="n">
         <v>48.29</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>55.66</v>
+        <v>55.74</v>
       </c>
     </row>
     <row r="86">
@@ -8007,13 +8007,13 @@
         <v>26.65</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>30.36</v>
+        <v>30.25</v>
       </c>
       <c r="D86" s="5" t="n">
         <v>40.89</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>46.58</v>
+        <v>46.41</v>
       </c>
     </row>
     <row r="87">
@@ -8026,13 +8026,13 @@
         <v>27.05</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>30.73</v>
+        <v>30.63</v>
       </c>
       <c r="D87" s="5" t="n">
         <v>41.4</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>47.04</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="88">
@@ -8045,13 +8045,13 @@
         <v>22.12</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>24.89</v>
+        <v>24.81</v>
       </c>
       <c r="D88" s="5" t="n">
         <v>33.78</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>38.01</v>
+        <v>37.89</v>
       </c>
     </row>
     <row r="89">
@@ -8064,13 +8064,13 @@
         <v>20.82</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>24.65</v>
+        <v>24.32</v>
       </c>
       <c r="D89" s="5" t="n">
         <v>31.75</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>37.59</v>
+        <v>37.09</v>
       </c>
     </row>
     <row r="90">
@@ -8083,13 +8083,13 @@
         <v>18.42</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>21.04</v>
+        <v>20.74</v>
       </c>
       <c r="D90" s="5" t="n">
         <v>28.06</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>32.05</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="91">
@@ -8102,13 +8102,13 @@
         <v>16.52</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>18.96</v>
+        <v>18.84</v>
       </c>
       <c r="D91" s="5" t="n">
         <v>25.13</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>28.84</v>
+        <v>28.66</v>
       </c>
     </row>
     <row r="92">
@@ -8121,13 +8121,13 @@
         <v>41.07</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>66.16</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D92" s="5" t="n">
         <v>62.15</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>100.12</v>
+        <v>99.73</v>
       </c>
     </row>
     <row r="93">
@@ -8140,13 +8140,13 @@
         <v>40.46</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>59.69</v>
+        <v>59.12</v>
       </c>
       <c r="D93" s="5" t="n">
         <v>60.92</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>89.87</v>
+        <v>89.01000000000001</v>
       </c>
     </row>
     <row r="94">
@@ -8159,13 +8159,13 @@
         <v>24.96</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>28.62</v>
+        <v>28.33</v>
       </c>
       <c r="D94" s="5" t="n">
         <v>37.39</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>42.87</v>
+        <v>42.44</v>
       </c>
     </row>
     <row r="95">
@@ -8197,13 +8197,13 @@
         <v>34.35</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>40.58</v>
+        <v>40.34</v>
       </c>
       <c r="D96" s="5" t="n">
         <v>51.14</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>60.42</v>
+        <v>60.06</v>
       </c>
     </row>
     <row r="97">
@@ -8216,13 +8216,13 @@
         <v>27.92</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>33.89</v>
+        <v>33.79</v>
       </c>
       <c r="D97" s="5" t="n">
         <v>41.44</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>50.3</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="98">
@@ -8235,13 +8235,13 @@
         <v>29.49</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>37.84</v>
+        <v>37.74</v>
       </c>
       <c r="D98" s="5" t="n">
         <v>43.68</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>56.05</v>
+        <v>55.91</v>
       </c>
     </row>
     <row r="99">
@@ -8254,13 +8254,13 @@
         <v>29.95</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>35.44</v>
+        <v>35.21</v>
       </c>
       <c r="D99" s="5" t="n">
         <v>44.28</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>52.39</v>
+        <v>52.05</v>
       </c>
     </row>
     <row r="100">
@@ -8273,13 +8273,13 @@
         <v>26.98</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>31.61</v>
+        <v>31.48</v>
       </c>
       <c r="D100" s="5" t="n">
         <v>39.81</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>46.64</v>
+        <v>46.45</v>
       </c>
     </row>
     <row r="101">
@@ -8292,13 +8292,13 @@
         <v>23.61</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>29</v>
+        <v>28.55</v>
       </c>
       <c r="D101" s="5" t="n">
         <v>34.84</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>42.79</v>
+        <v>42.13</v>
       </c>
     </row>
     <row r="102">
@@ -8311,13 +8311,13 @@
         <v>26.58</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>30.77</v>
+        <v>30.42</v>
       </c>
       <c r="D102" s="5" t="n">
         <v>39.22</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>45.4</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="103">
@@ -8330,13 +8330,13 @@
         <v>22.18</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>25.62</v>
+        <v>25.43</v>
       </c>
       <c r="D103" s="5" t="n">
         <v>32.73</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>37.8</v>
+        <v>37.52</v>
       </c>
     </row>
     <row r="104">
@@ -8349,13 +8349,13 @@
         <v>24.03</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>29.13</v>
+        <v>28.96</v>
       </c>
       <c r="D104" s="5" t="n">
         <v>35.45</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>42.97</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="105">
@@ -8368,13 +8368,13 @@
         <v>25.85</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>30.01</v>
+        <v>29.72</v>
       </c>
       <c r="D105" s="5" t="n">
         <v>38.13</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>44.26</v>
+        <v>43.83</v>
       </c>
     </row>
     <row r="106">
@@ -8387,13 +8387,13 @@
         <v>23.7</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>27.89</v>
+        <v>27.57</v>
       </c>
       <c r="D106" s="5" t="n">
         <v>34.95</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>41.13</v>
+        <v>40.66</v>
       </c>
     </row>
     <row r="107">
@@ -8406,13 +8406,13 @@
         <v>32.01</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>36.3</v>
+        <v>36.22</v>
       </c>
       <c r="D107" s="5" t="n">
         <v>47.12</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>53.44</v>
+        <v>53.32</v>
       </c>
     </row>
     <row r="108">
@@ -8444,13 +8444,13 @@
         <v>36.75</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>42.66</v>
+        <v>42.49</v>
       </c>
       <c r="D109" s="5" t="n">
         <v>53.91</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>62.58</v>
+        <v>62.33</v>
       </c>
     </row>
     <row r="110">
@@ -8463,13 +8463,13 @@
         <v>73.45999999999999</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>90.05</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="D110" s="5" t="n">
         <v>107.28</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>131.51</v>
+        <v>131.01</v>
       </c>
     </row>
     <row r="111">
@@ -8482,13 +8482,13 @@
         <v>55.76</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>58.79</v>
+        <v>58.42</v>
       </c>
       <c r="D111" s="5" t="n">
         <v>81.06</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>85.47</v>
+        <v>84.93000000000001</v>
       </c>
     </row>
     <row r="112">
@@ -8501,13 +8501,13 @@
         <v>53.48</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>60.96</v>
+        <v>60.79</v>
       </c>
       <c r="D112" s="5" t="n">
         <v>77.40000000000001</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>88.23</v>
+        <v>87.98</v>
       </c>
     </row>
     <row r="113">
@@ -8520,13 +8520,13 @@
         <v>51.27</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>55</v>
+        <v>54.54</v>
       </c>
       <c r="D113" s="5" t="n">
         <v>74.14</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>79.53</v>
+        <v>78.87</v>
       </c>
     </row>
     <row r="114">
@@ -8539,13 +8539,13 @@
         <v>77.18000000000001</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>108.73</v>
+        <v>108.42</v>
       </c>
       <c r="D114" s="5" t="n">
         <v>111.51</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>157.1</v>
+        <v>156.65</v>
       </c>
     </row>
     <row r="115">
@@ -8558,13 +8558,13 @@
         <v>52.18</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>58.92</v>
+        <v>58.79</v>
       </c>
       <c r="D115" s="5" t="n">
         <v>75.33</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>85.06</v>
+        <v>84.87</v>
       </c>
     </row>
     <row r="116">
@@ -8577,13 +8577,13 @@
         <v>54.27</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>65.31</v>
+        <v>65.27</v>
       </c>
       <c r="D116" s="5" t="n">
         <v>78.26000000000001</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>94.18000000000001</v>
+        <v>94.12</v>
       </c>
     </row>
     <row r="117">
@@ -8596,13 +8596,13 @@
         <v>53.59</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>59.78</v>
+        <v>59.25</v>
       </c>
       <c r="D117" s="5" t="n">
         <v>77.19</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>86.11</v>
+        <v>85.34</v>
       </c>
     </row>
     <row r="118">
@@ -8615,13 +8615,13 @@
         <v>52.31</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>60.03</v>
+        <v>59.68</v>
       </c>
       <c r="D118" s="5" t="n">
         <v>75.26000000000001</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>86.37</v>
+        <v>85.87</v>
       </c>
     </row>
     <row r="119">
@@ -8634,13 +8634,13 @@
         <v>50.02</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>53.46</v>
+        <v>53.14</v>
       </c>
       <c r="D119" s="5" t="n">
         <v>71.88</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>76.81999999999999</v>
+        <v>76.36</v>
       </c>
     </row>
     <row r="120">
@@ -8653,13 +8653,13 @@
         <v>54.85</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>61.01</v>
+        <v>60.42</v>
       </c>
       <c r="D120" s="5" t="n">
         <v>78.72</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>87.56</v>
+        <v>86.70999999999999</v>
       </c>
     </row>
     <row r="121">
@@ -8672,13 +8672,13 @@
         <v>60.9</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>70.51000000000001</v>
+        <v>70.08</v>
       </c>
       <c r="D121" s="5" t="n">
         <v>87.29000000000001</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>101.06</v>
+        <v>100.45</v>
       </c>
     </row>
     <row r="122">
@@ -8691,13 +8691,13 @@
         <v>58.35</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>62.4</v>
+        <v>61.74</v>
       </c>
       <c r="D122" s="5" t="n">
         <v>83.3</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>89.08</v>
+        <v>88.13</v>
       </c>
     </row>
     <row r="123">
@@ -8710,13 +8710,13 @@
         <v>54.12</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>57.79</v>
+        <v>57.53</v>
       </c>
       <c r="D123" s="5" t="n">
         <v>76.95</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>82.16</v>
+        <v>81.79000000000001</v>
       </c>
     </row>
     <row r="124">
@@ -8729,13 +8729,13 @@
         <v>49.25</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>52.11</v>
+        <v>51.96</v>
       </c>
       <c r="D124" s="5" t="n">
         <v>69.73999999999999</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>73.79000000000001</v>
+        <v>73.58</v>
       </c>
     </row>
     <row r="125">
@@ -8748,13 +8748,13 @@
         <v>49.47</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>51.91</v>
+        <v>51.51</v>
       </c>
       <c r="D125" s="5" t="n">
         <v>69.88</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>73.33</v>
+        <v>72.77</v>
       </c>
     </row>
     <row r="126">
@@ -8767,13 +8767,13 @@
         <v>46.76</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>49.47</v>
+        <v>49.21</v>
       </c>
       <c r="D126" s="5" t="n">
         <v>65.90000000000001</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>69.72</v>
+        <v>69.34999999999999</v>
       </c>
     </row>
     <row r="127">
@@ -8786,13 +8786,13 @@
         <v>50.33</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>57.51</v>
+        <v>57.33</v>
       </c>
       <c r="D127" s="5" t="n">
         <v>70.76000000000001</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>80.86</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="128">
@@ -8805,13 +8805,13 @@
         <v>72.43000000000001</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>105.62</v>
+        <v>105.36</v>
       </c>
       <c r="D128" s="5" t="n">
         <v>101.63</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>148.2</v>
+        <v>147.84</v>
       </c>
     </row>
     <row r="129">
@@ -8824,13 +8824,13 @@
         <v>49.25</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>51.64</v>
+        <v>51.23</v>
       </c>
       <c r="D129" s="5" t="n">
         <v>68.97</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>72.31999999999999</v>
+        <v>71.73999999999999</v>
       </c>
     </row>
     <row r="130">
@@ -8843,13 +8843,13 @@
         <v>45.96</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>50.99</v>
+        <v>50.43</v>
       </c>
       <c r="D130" s="5" t="n">
         <v>64.23999999999999</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>71.27</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="131">
@@ -8862,13 +8862,13 @@
         <v>43.79</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>46.48</v>
+        <v>46.35</v>
       </c>
       <c r="D131" s="5" t="n">
         <v>61.1</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>64.84999999999999</v>
+        <v>64.67</v>
       </c>
     </row>
     <row r="132">
@@ -8881,13 +8881,13 @@
         <v>48.2</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>53.42</v>
+        <v>53.06</v>
       </c>
       <c r="D132" s="5" t="n">
         <v>67.14</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>74.41</v>
+        <v>73.91</v>
       </c>
     </row>
     <row r="133">
@@ -8900,13 +8900,13 @@
         <v>49.17</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>53.9</v>
+        <v>53.86</v>
       </c>
       <c r="D133" s="5" t="n">
         <v>68.38</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>74.95999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="134">
@@ -8919,13 +8919,13 @@
         <v>38.59</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>43.69</v>
+        <v>43.59</v>
       </c>
       <c r="D134" s="5" t="n">
         <v>53.59</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>60.67</v>
+        <v>60.53</v>
       </c>
     </row>
     <row r="135">
@@ -8938,13 +8938,13 @@
         <v>34.51</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>40.67</v>
+        <v>40.37</v>
       </c>
       <c r="D135" s="5" t="n">
         <v>47.86</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>56.4</v>
+        <v>55.98</v>
       </c>
     </row>
     <row r="136">
@@ -8957,13 +8957,13 @@
         <v>36.26</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>42.07</v>
+        <v>41.59</v>
       </c>
       <c r="D136" s="5" t="n">
         <v>50.21</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>58.26</v>
+        <v>57.59</v>
       </c>
     </row>
     <row r="137">
@@ -8976,13 +8976,13 @@
         <v>26.59</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>30.63</v>
+        <v>30.36</v>
       </c>
       <c r="D137" s="5" t="n">
         <v>36.8</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>42.39</v>
+        <v>42.02</v>
       </c>
     </row>
     <row r="138">
@@ -8995,13 +8995,13 @@
         <v>28.56</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>34.46</v>
+        <v>34.02</v>
       </c>
       <c r="D138" s="5" t="n">
         <v>39.5</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>47.66</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="139">
@@ -9014,13 +9014,13 @@
         <v>26.54</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>31.31</v>
+        <v>31.02</v>
       </c>
       <c r="D139" s="5" t="n">
         <v>36.68</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>43.28</v>
+        <v>42.88</v>
       </c>
     </row>
     <row r="140">
@@ -9033,13 +9033,13 @@
         <v>26.1</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>33.61</v>
+        <v>33.35</v>
       </c>
       <c r="D140" s="5" t="n">
         <v>36.05</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>46.43</v>
+        <v>46.07</v>
       </c>
     </row>
     <row r="141">
@@ -9052,13 +9052,13 @@
         <v>28.03</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>35.21</v>
+        <v>34.67</v>
       </c>
       <c r="D141" s="5" t="n">
         <v>38.69</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>48.61</v>
+        <v>47.86</v>
       </c>
     </row>
     <row r="142">
@@ -9071,13 +9071,13 @@
         <v>25.81</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>31.79</v>
+        <v>30.8</v>
       </c>
       <c r="D142" s="5" t="n">
         <v>35.61</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>43.86</v>
+        <v>42.49</v>
       </c>
     </row>
     <row r="143">
@@ -9090,13 +9090,13 @@
         <v>28.91</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>35.26</v>
+        <v>34.91</v>
       </c>
       <c r="D143" s="5" t="n">
         <v>39.79</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>48.53</v>
+        <v>48.05</v>
       </c>
     </row>
     <row r="144">
@@ -9109,13 +9109,13 @@
         <v>29.85</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>38.41</v>
+        <v>38.04</v>
       </c>
       <c r="D144" s="5" t="n">
         <v>40.99</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>52.74</v>
+        <v>52.23</v>
       </c>
     </row>
     <row r="145">
@@ -9128,13 +9128,13 @@
         <v>34.41</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>41.52</v>
+        <v>40.94</v>
       </c>
       <c r="D145" s="5" t="n">
         <v>47.13</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>56.87</v>
+        <v>56.08</v>
       </c>
     </row>
     <row r="146">
@@ -9147,13 +9147,13 @@
         <v>34.75</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>42.82</v>
+        <v>42.4</v>
       </c>
       <c r="D146" s="5" t="n">
         <v>47.54</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>58.58</v>
+        <v>58</v>
       </c>
     </row>
     <row r="147">
@@ -9166,13 +9166,13 @@
         <v>35.04</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>42.1</v>
+        <v>41.42</v>
       </c>
       <c r="D147" s="5" t="n">
         <v>47.87</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>57.52</v>
+        <v>56.59</v>
       </c>
     </row>
     <row r="148">
@@ -9185,13 +9185,13 @@
         <v>44.55</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>50.84</v>
+        <v>50.53</v>
       </c>
       <c r="D148" s="5" t="n">
         <v>60.79</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>69.37</v>
+        <v>68.95</v>
       </c>
     </row>
     <row r="149">
@@ -9204,13 +9204,13 @@
         <v>35.63</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>45.47</v>
+        <v>44.46</v>
       </c>
       <c r="D149" s="5" t="n">
         <v>48.55</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>61.96</v>
+        <v>60.59</v>
       </c>
     </row>
     <row r="150">
@@ -9223,13 +9223,13 @@
         <v>34.92</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>45.23</v>
+        <v>44.68</v>
       </c>
       <c r="D150" s="5" t="n">
         <v>47.53</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>61.56</v>
+        <v>60.81</v>
       </c>
     </row>
     <row r="151">
@@ -9242,13 +9242,13 @@
         <v>48.01</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>62.67</v>
+        <v>61.92</v>
       </c>
       <c r="D151" s="5" t="n">
         <v>65.26000000000001</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>85.18000000000001</v>
+        <v>84.16</v>
       </c>
     </row>
     <row r="152">
@@ -9261,13 +9261,13 @@
         <v>46.95</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>72.90000000000001</v>
+        <v>72.53</v>
       </c>
       <c r="D152" s="5" t="n">
         <v>63.86</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>99.15000000000001</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="153">
@@ -9280,13 +9280,13 @@
         <v>35.42</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>44.52</v>
+        <v>43.88</v>
       </c>
       <c r="D153" s="5" t="n">
         <v>48.21</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>60.59</v>
+        <v>59.72</v>
       </c>
     </row>
     <row r="154">
@@ -9299,13 +9299,13 @@
         <v>45.89</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>59.65</v>
+        <v>58.3</v>
       </c>
       <c r="D154" s="5" t="n">
         <v>62.5</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>81.23999999999999</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="155">
@@ -9318,13 +9318,13 @@
         <v>45.88</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>61.49</v>
+        <v>59.14</v>
       </c>
       <c r="D155" s="5" t="n">
         <v>62.4</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>83.62</v>
+        <v>80.43000000000001</v>
       </c>
     </row>
     <row r="156">
@@ -9337,13 +9337,13 @@
         <v>54.24</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>76.45999999999999</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="D156" s="5" t="n">
         <v>73.66</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>103.83</v>
+        <v>99.91</v>
       </c>
     </row>
     <row r="157">
@@ -9356,13 +9356,13 @@
         <v>92.77</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>118.54</v>
+        <v>114.45</v>
       </c>
       <c r="D157" s="5" t="n">
         <v>125.8</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>160.74</v>
+        <v>155.19</v>
       </c>
     </row>
     <row r="158">
@@ -9375,13 +9375,13 @@
         <v>64.64</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>86.77</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="D158" s="5" t="n">
         <v>87.45</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>117.39</v>
+        <v>114.3</v>
       </c>
     </row>
     <row r="159">
@@ -9394,13 +9394,13 @@
         <v>43.24</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>55.76</v>
+        <v>53.5</v>
       </c>
       <c r="D159" s="5" t="n">
         <v>58.36</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>75.26000000000001</v>
+        <v>72.20999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -9413,13 +9413,13 @@
         <v>41.02</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>48.5</v>
+        <v>47.59</v>
       </c>
       <c r="D160" s="5" t="n">
         <v>55.24</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>65.31</v>
+        <v>64.08</v>
       </c>
     </row>
     <row r="161">
@@ -9432,13 +9432,13 @@
         <v>33.18</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>41.02</v>
+        <v>38.38</v>
       </c>
       <c r="D161" s="5" t="n">
         <v>44.6</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>55.14</v>
+        <v>51.59</v>
       </c>
     </row>
     <row r="162">
@@ -9451,13 +9451,13 @@
         <v>36.07</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>46.93</v>
+        <v>45.05</v>
       </c>
       <c r="D162" s="5" t="n">
         <v>48.4</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>62.97</v>
+        <v>60.45</v>
       </c>
     </row>
     <row r="163">
@@ -9470,13 +9470,13 @@
         <v>29.9</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>37.59</v>
+        <v>37.06</v>
       </c>
       <c r="D163" s="5" t="n">
         <v>40.05</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>50.35</v>
+        <v>49.64</v>
       </c>
     </row>
     <row r="164">
@@ -9489,13 +9489,13 @@
         <v>62.04</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>81.03</v>
+        <v>80.27</v>
       </c>
       <c r="D164" s="5" t="n">
         <v>82.98</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>108.37</v>
+        <v>107.36</v>
       </c>
     </row>
     <row r="165">
@@ -9508,13 +9508,13 @@
         <v>86.05</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>114.18</v>
+        <v>111.69</v>
       </c>
       <c r="D165" s="5" t="n">
         <v>114.91</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>152.48</v>
+        <v>149.15</v>
       </c>
     </row>
     <row r="166">
@@ -9527,13 +9527,13 @@
         <v>90.63</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>112.64</v>
+        <v>110.35</v>
       </c>
       <c r="D166" s="5" t="n">
         <v>120.84</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>150.19</v>
+        <v>147.14</v>
       </c>
     </row>
     <row r="167">
@@ -9546,13 +9546,13 @@
         <v>108.2</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>123.35</v>
+        <v>121.78</v>
       </c>
       <c r="D167" s="5" t="n">
         <v>144.18</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>164.36</v>
+        <v>162.27</v>
       </c>
     </row>
     <row r="168">
@@ -9565,13 +9565,13 @@
         <v>107.95</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>123.09</v>
+        <v>121.22</v>
       </c>
       <c r="D168" s="5" t="n">
         <v>143.75</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>163.91</v>
+        <v>161.42</v>
       </c>
     </row>
     <row r="169">
@@ -9584,13 +9584,13 @@
         <v>98.5</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>105</v>
+        <v>103.65</v>
       </c>
       <c r="D169" s="5" t="n">
         <v>131.08</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>139.73</v>
+        <v>137.93</v>
       </c>
     </row>
     <row r="170">
@@ -9603,13 +9603,13 @@
         <v>117.38</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>131.48</v>
+        <v>129.67</v>
       </c>
       <c r="D170" s="5" t="n">
         <v>155.89</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>174.61</v>
+        <v>172.21</v>
       </c>
     </row>
     <row r="171">
@@ -9622,13 +9622,13 @@
         <v>102.57</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>119.74</v>
+        <v>116.97</v>
       </c>
       <c r="D171" s="5" t="n">
         <v>135.94</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>158.7</v>
+        <v>155.03</v>
       </c>
     </row>
     <row r="172">
@@ -9641,13 +9641,13 @@
         <v>79.43000000000001</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>89.62</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D172" s="5" t="n">
         <v>105.06</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>118.54</v>
+        <v>117.85</v>
       </c>
     </row>
     <row r="173">
@@ -9660,13 +9660,13 @@
         <v>73.31</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>82.48</v>
+        <v>81.72</v>
       </c>
       <c r="D173" s="5" t="n">
         <v>96.75</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>108.85</v>
+        <v>107.85</v>
       </c>
     </row>
     <row r="174">
@@ -9679,13 +9679,13 @@
         <v>95.54000000000001</v>
       </c>
       <c r="C174" s="5" t="n">
-        <v>112.43</v>
+        <v>111.45</v>
       </c>
       <c r="D174" s="5" t="n">
         <v>125.81</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>148.05</v>
+        <v>146.76</v>
       </c>
     </row>
     <row r="175">
@@ -9698,13 +9698,13 @@
         <v>84.84999999999999</v>
       </c>
       <c r="C175" s="5" t="n">
-        <v>97.75</v>
+        <v>97.2</v>
       </c>
       <c r="D175" s="5" t="n">
         <v>111.48</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>128.43</v>
+        <v>127.71</v>
       </c>
     </row>
     <row r="176">
@@ -9717,13 +9717,13 @@
         <v>133.48</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>183</v>
+        <v>182.54</v>
       </c>
       <c r="D176" s="5" t="n">
         <v>175.12</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>240.09</v>
+        <v>239.48</v>
       </c>
     </row>
     <row r="177">
@@ -9736,13 +9736,13 @@
         <v>97.43000000000001</v>
       </c>
       <c r="C177" s="5" t="n">
-        <v>124.33</v>
+        <v>123.66</v>
       </c>
       <c r="D177" s="5" t="n">
         <v>127.64</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>162.88</v>
+        <v>162</v>
       </c>
     </row>
     <row r="178">
@@ -9755,13 +9755,13 @@
         <v>76.01000000000001</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>82.25</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="D178" s="5" t="n">
         <v>99.43000000000001</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>107.59</v>
+        <v>106.56</v>
       </c>
     </row>
     <row r="179">
@@ -9774,13 +9774,13 @@
         <v>74.04000000000001</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>87.09</v>
+        <v>86.12</v>
       </c>
       <c r="D179" s="5" t="n">
         <v>96.73999999999999</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>113.79</v>
+        <v>112.52</v>
       </c>
     </row>
     <row r="180">
@@ -9793,13 +9793,13 @@
         <v>79.79000000000001</v>
       </c>
       <c r="C180" s="5" t="n">
-        <v>95.98</v>
+        <v>93.45</v>
       </c>
       <c r="D180" s="5" t="n">
         <v>104.13</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>125.26</v>
+        <v>121.96</v>
       </c>
     </row>
     <row r="181">
@@ -9812,13 +9812,13 @@
         <v>93.72</v>
       </c>
       <c r="C181" s="5" t="n">
-        <v>112.11</v>
+        <v>109.8</v>
       </c>
       <c r="D181" s="5" t="n">
         <v>122.16</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>146.13</v>
+        <v>143.12</v>
       </c>
     </row>
     <row r="182">
@@ -9831,13 +9831,13 @@
         <v>70.09999999999999</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>88.33</v>
+        <v>86.86</v>
       </c>
       <c r="D182" s="5" t="n">
         <v>91.23999999999999</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>114.97</v>
+        <v>113.06</v>
       </c>
     </row>
     <row r="183">
@@ -9850,13 +9850,13 @@
         <v>79.17</v>
       </c>
       <c r="C183" s="5" t="n">
-        <v>102.2</v>
+        <v>100.32</v>
       </c>
       <c r="D183" s="5" t="n">
         <v>102.9</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>132.83</v>
+        <v>130.39</v>
       </c>
     </row>
     <row r="184">
@@ -9869,13 +9869,13 @@
         <v>92.84999999999999</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>108.02</v>
+        <v>106.94</v>
       </c>
       <c r="D184" s="5" t="n">
         <v>120.51</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>140.19</v>
+        <v>138.79</v>
       </c>
     </row>
     <row r="185">
@@ -9888,13 +9888,13 @@
         <v>99.83</v>
       </c>
       <c r="C185" s="5" t="n">
-        <v>109.7</v>
+        <v>108.4</v>
       </c>
       <c r="D185" s="5" t="n">
         <v>129.34</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>142.13</v>
+        <v>140.44</v>
       </c>
     </row>
     <row r="186">
@@ -9907,13 +9907,13 @@
         <v>97.84</v>
       </c>
       <c r="C186" s="5" t="n">
-        <v>105.48</v>
+        <v>104.23</v>
       </c>
       <c r="D186" s="5" t="n">
         <v>126.54</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>136.42</v>
+        <v>134.81</v>
       </c>
     </row>
     <row r="187">
@@ -9926,13 +9926,13 @@
         <v>91.79000000000001</v>
       </c>
       <c r="C187" s="5" t="n">
-        <v>113.92</v>
+        <v>113.57</v>
       </c>
       <c r="D187" s="5" t="n">
         <v>118.51</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>147.09</v>
+        <v>146.63</v>
       </c>
     </row>
     <row r="188">
@@ -9945,13 +9945,13 @@
         <v>250.33</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>423.33</v>
+        <v>421.41</v>
       </c>
       <c r="D188" s="5" t="n">
         <v>323.22</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>546.6</v>
+        <v>544.12</v>
       </c>
     </row>
     <row r="189">
@@ -9964,13 +9964,13 @@
         <v>111.16</v>
       </c>
       <c r="C189" s="5" t="n">
-        <v>120.86</v>
+        <v>119.46</v>
       </c>
       <c r="D189" s="5" t="n">
         <v>143.54</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>156.06</v>
+        <v>154.25</v>
       </c>
     </row>
     <row r="190">
@@ -9983,13 +9983,13 @@
         <v>131.11</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>177.81</v>
+        <v>176.04</v>
       </c>
       <c r="D190" s="5" t="n">
         <v>169.3</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>229.61</v>
+        <v>227.32</v>
       </c>
     </row>
     <row r="191">
@@ -10002,13 +10002,13 @@
         <v>98.44</v>
       </c>
       <c r="C191" s="5" t="n">
-        <v>106.79</v>
+        <v>105.41</v>
       </c>
       <c r="D191" s="5" t="n">
         <v>126.87</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>137.63</v>
+        <v>135.85</v>
       </c>
     </row>
     <row r="192">
@@ -10021,13 +10021,13 @@
         <v>91.90000000000001</v>
       </c>
       <c r="C192" s="5" t="n">
-        <v>104.25</v>
+        <v>103.35</v>
       </c>
       <c r="D192" s="5" t="n">
         <v>118.2</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>134.09</v>
+        <v>132.93</v>
       </c>
     </row>
     <row r="193">
@@ -10040,13 +10040,13 @@
         <v>101.81</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>122.01</v>
+        <v>120.77</v>
       </c>
       <c r="D193" s="5" t="n">
         <v>130.69</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>156.62</v>
+        <v>155.03</v>
       </c>
     </row>
     <row r="194">
@@ -10059,13 +10059,13 @@
         <v>85.92</v>
       </c>
       <c r="C194" s="5" t="n">
-        <v>105.02</v>
+        <v>104.22</v>
       </c>
       <c r="D194" s="5" t="n">
         <v>110.09</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>134.56</v>
+        <v>133.53</v>
       </c>
     </row>
     <row r="195">
@@ -10078,13 +10078,13 @@
         <v>104.95</v>
       </c>
       <c r="C195" s="5" t="n">
-        <v>130.29</v>
+        <v>128.34</v>
       </c>
       <c r="D195" s="5" t="n">
         <v>134.22</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>166.62</v>
+        <v>164.13</v>
       </c>
     </row>
     <row r="196">
@@ -10097,13 +10097,13 @@
         <v>104.76</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>121.93</v>
+        <v>119.12</v>
       </c>
       <c r="D196" s="5" t="n">
         <v>133.72</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>155.64</v>
+        <v>152.05</v>
       </c>
     </row>
     <row r="197">
@@ -10116,13 +10116,13 @@
         <v>100.7</v>
       </c>
       <c r="C197" s="5" t="n">
-        <v>113.03</v>
+        <v>110.98</v>
       </c>
       <c r="D197" s="5" t="n">
         <v>128.25</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>143.95</v>
+        <v>141.34</v>
       </c>
     </row>
     <row r="198">
@@ -10135,13 +10135,13 @@
         <v>67.98</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>69.79000000000001</v>
+        <v>68.72</v>
       </c>
       <c r="D198" s="5" t="n">
         <v>86.38</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>88.68000000000001</v>
+        <v>87.31999999999999</v>
       </c>
     </row>
     <row r="199">
@@ -10154,13 +10154,13 @@
         <v>61.39</v>
       </c>
       <c r="C199" s="5" t="n">
-        <v>77.45999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="D199" s="5" t="n">
         <v>77.83</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>98.2</v>
+        <v>97.92</v>
       </c>
     </row>
     <row r="200">
@@ -10173,13 +10173,13 @@
         <v>142.95</v>
       </c>
       <c r="C200" s="5" t="n">
-        <v>255.88</v>
+        <v>255.49</v>
       </c>
       <c r="D200" s="5" t="n">
         <v>181.01</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>324</v>
+        <v>323.5</v>
       </c>
     </row>
     <row r="201">
@@ -10192,13 +10192,13 @@
         <v>48.31</v>
       </c>
       <c r="C201" s="5" t="n">
-        <v>55.83</v>
+        <v>55.07</v>
       </c>
       <c r="D201" s="5" t="n">
         <v>61.1</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>70.61</v>
+        <v>69.64</v>
       </c>
     </row>
     <row r="202">
@@ -10211,13 +10211,13 @@
         <v>43.3</v>
       </c>
       <c r="C202" s="5" t="n">
-        <v>50.47</v>
+        <v>49.68</v>
       </c>
       <c r="D202" s="5" t="n">
         <v>54.69</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>63.75</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="203">
@@ -10230,13 +10230,13 @@
         <v>34.83</v>
       </c>
       <c r="C203" s="5" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="D203" s="5" t="n">
         <v>44.28</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>53.27</v>
+        <v>53.14</v>
       </c>
     </row>
     <row r="204">
@@ -10249,13 +10249,13 @@
         <v>38.29</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>47.04</v>
+        <v>46.68</v>
       </c>
       <c r="D204" s="5" t="n">
         <v>48.99</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>60.19</v>
+        <v>59.73</v>
       </c>
     </row>
     <row r="205">
@@ -10268,13 +10268,13 @@
         <v>48.66</v>
       </c>
       <c r="C205" s="5" t="n">
-        <v>62.91</v>
+        <v>62.5</v>
       </c>
       <c r="D205" s="5" t="n">
         <v>62.67</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>81.02</v>
+        <v>80.48999999999999</v>
       </c>
     </row>
     <row r="206">
@@ -10287,13 +10287,13 @@
         <v>63.6</v>
       </c>
       <c r="C206" s="5" t="n">
-        <v>75.01000000000001</v>
+        <v>74.52</v>
       </c>
       <c r="D206" s="5" t="n">
         <v>81.48999999999999</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>96.11</v>
+        <v>95.48</v>
       </c>
     </row>
     <row r="207">
@@ -10306,13 +10306,13 @@
         <v>53.7</v>
       </c>
       <c r="C207" s="5" t="n">
-        <v>66.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D207" s="5" t="n">
         <v>68.45</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>84.64</v>
+        <v>83.62</v>
       </c>
     </row>
     <row r="208">
@@ -10325,13 +10325,13 @@
         <v>34.65</v>
       </c>
       <c r="C208" s="5" t="n">
-        <v>39.08</v>
+        <v>38.68</v>
       </c>
       <c r="D208" s="5" t="n">
         <v>43.94</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>49.56</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="209">
@@ -10344,13 +10344,13 @@
         <v>44.79</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>55.4</v>
+        <v>53.68</v>
       </c>
       <c r="D209" s="5" t="n">
         <v>56.63</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>70.05</v>
+        <v>67.88</v>
       </c>
     </row>
     <row r="210">
@@ -10363,13 +10363,13 @@
         <v>44.07</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>49.88</v>
+        <v>49.58</v>
       </c>
       <c r="D210" s="5" t="n">
         <v>55.56</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>62.88</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="211">
@@ -10382,13 +10382,13 @@
         <v>23.79</v>
       </c>
       <c r="C211" s="5" t="n">
-        <v>23.5</v>
+        <v>23.43</v>
       </c>
       <c r="D211" s="5" t="n">
         <v>29.9</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>29.54</v>
+        <v>29.45</v>
       </c>
     </row>
     <row r="212">
@@ -10401,13 +10401,13 @@
         <v>22.82</v>
       </c>
       <c r="C212" s="5" t="n">
-        <v>20.68</v>
+        <v>20.66</v>
       </c>
       <c r="D212" s="5" t="n">
         <v>28.63</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>25.94</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="213">
@@ -10420,13 +10420,13 @@
         <v>21.85</v>
       </c>
       <c r="C213" s="5" t="n">
-        <v>24.89</v>
+        <v>24.62</v>
       </c>
       <c r="D213" s="5" t="n">
         <v>27.36</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>31.16</v>
+        <v>30.83</v>
       </c>
     </row>
     <row r="214">
@@ -10439,13 +10439,13 @@
         <v>30.36</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>32.84</v>
+        <v>31.29</v>
       </c>
       <c r="D214" s="5" t="n">
         <v>37.94</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>41.04</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="215">
@@ -10458,13 +10458,13 @@
         <v>49.47</v>
       </c>
       <c r="C215" s="5" t="n">
-        <v>62.46</v>
+        <v>60.46</v>
       </c>
       <c r="D215" s="5" t="n">
         <v>61.67</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>77.86</v>
+        <v>75.37</v>
       </c>
     </row>
     <row r="216">
@@ -10477,13 +10477,13 @@
         <v>72.84</v>
       </c>
       <c r="C216" s="5" t="n">
-        <v>114.98</v>
+        <v>113.74</v>
       </c>
       <c r="D216" s="5" t="n">
         <v>90.58</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>142.99</v>
+        <v>141.45</v>
       </c>
     </row>
     <row r="217">
@@ -10496,13 +10496,13 @@
         <v>87.92</v>
       </c>
       <c r="C217" s="5" t="n">
-        <v>107.95</v>
+        <v>107.34</v>
       </c>
       <c r="D217" s="5" t="n">
         <v>109.07</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>133.92</v>
+        <v>133.16</v>
       </c>
     </row>
     <row r="218">
@@ -10515,13 +10515,13 @@
         <v>91.72</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>126.87</v>
+        <v>127.01</v>
       </c>
       <c r="D218" s="5" t="n">
         <v>113.46</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>156.95</v>
+        <v>157.12</v>
       </c>
     </row>
     <row r="219">
@@ -10534,13 +10534,13 @@
         <v>47</v>
       </c>
       <c r="C219" s="5" t="n">
-        <v>55.18</v>
+        <v>54.92</v>
       </c>
       <c r="D219" s="5" t="n">
         <v>57.98</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>68.06999999999999</v>
+        <v>67.75</v>
       </c>
     </row>
     <row r="220">
@@ -10553,13 +10553,13 @@
         <v>27.72</v>
       </c>
       <c r="C220" s="5" t="n">
-        <v>33.73</v>
+        <v>33.28</v>
       </c>
       <c r="D220" s="5" t="n">
         <v>34.1</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>41.49</v>
+        <v>40.94</v>
       </c>
     </row>
     <row r="221">
@@ -10572,13 +10572,13 @@
         <v>18.46</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>15.09</v>
+        <v>15.04</v>
       </c>
       <c r="D221" s="5" t="n">
         <v>22.61</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>18.48</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="222">
@@ -10591,13 +10591,13 @@
         <v>35.02</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>40.78</v>
+        <v>40.75</v>
       </c>
       <c r="D222" s="5" t="n">
         <v>42.72</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>49.74</v>
+        <v>49.71</v>
       </c>
     </row>
     <row r="223">
@@ -10610,13 +10610,13 @@
         <v>32.23</v>
       </c>
       <c r="C223" s="5" t="n">
-        <v>30.8</v>
+        <v>30.93</v>
       </c>
       <c r="D223" s="5" t="n">
         <v>39.15</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>37.41</v>
+        <v>37.57</v>
       </c>
     </row>
     <row r="224">
@@ -10629,13 +10629,13 @@
         <v>60.82</v>
       </c>
       <c r="C224" s="5" t="n">
-        <v>75.01000000000001</v>
+        <v>75.05</v>
       </c>
       <c r="D224" s="5" t="n">
         <v>73.34999999999999</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>90.45999999999999</v>
+        <v>90.51000000000001</v>
       </c>
     </row>
     <row r="225">
@@ -10648,13 +10648,13 @@
         <v>54.17</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>48.54</v>
+        <v>48.46</v>
       </c>
       <c r="D225" s="5" t="n">
         <v>64.86</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>58.12</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="226">
@@ -10667,13 +10667,13 @@
         <v>54.78</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>56.47</v>
+        <v>56.21</v>
       </c>
       <c r="D226" s="5" t="n">
         <v>65.13</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>67.14</v>
+        <v>66.83</v>
       </c>
     </row>
     <row r="227">
@@ -10686,13 +10686,13 @@
         <v>141.51</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>168.15</v>
+        <v>167.79</v>
       </c>
       <c r="D227" s="5" t="n">
         <v>167.25</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>198.74</v>
+        <v>198.31</v>
       </c>
     </row>
     <row r="228">
@@ -10705,13 +10705,13 @@
         <v>233.64</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>264.24</v>
+        <v>264.05</v>
       </c>
       <c r="D228" s="5" t="n">
         <v>274.51</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>310.47</v>
+        <v>310.24</v>
       </c>
     </row>
     <row r="229">
@@ -10724,13 +10724,13 @@
         <v>296.49</v>
       </c>
       <c r="C229" s="5" t="n">
-        <v>375.96</v>
+        <v>375.27</v>
       </c>
       <c r="D229" s="5" t="n">
         <v>346.32</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>439.14</v>
+        <v>438.34</v>
       </c>
     </row>
     <row r="230">
@@ -10743,13 +10743,13 @@
         <v>340.34</v>
       </c>
       <c r="C230" s="5" t="n">
-        <v>432</v>
+        <v>431.21</v>
       </c>
       <c r="D230" s="5" t="n">
         <v>395.12</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>501.53</v>
+        <v>500.61</v>
       </c>
     </row>
     <row r="231">
@@ -10762,13 +10762,13 @@
         <v>121.01</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>137.33</v>
+        <v>136.75</v>
       </c>
       <c r="D231" s="5" t="n">
         <v>139.64</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>158.47</v>
+        <v>157.8</v>
       </c>
     </row>
     <row r="232">
@@ -10781,13 +10781,13 @@
         <v>111.77</v>
       </c>
       <c r="C232" s="5" t="n">
-        <v>130.9</v>
+        <v>130.63</v>
       </c>
       <c r="D232" s="5" t="n">
         <v>128.2</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>150.14</v>
+        <v>149.83</v>
       </c>
     </row>
     <row r="233">
@@ -10800,13 +10800,13 @@
         <v>98.90000000000001</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>97.36</v>
+        <v>96.98999999999999</v>
       </c>
       <c r="D233" s="5" t="n">
         <v>112.74</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>110.98</v>
+        <v>110.56</v>
       </c>
     </row>
     <row r="234">
@@ -10819,13 +10819,13 @@
         <v>58.63</v>
       </c>
       <c r="C234" s="5" t="n">
-        <v>58.3</v>
+        <v>58.52</v>
       </c>
       <c r="D234" s="5" t="n">
         <v>66.43000000000001</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>66.05</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="235">
@@ -10838,13 +10838,13 @@
         <v>31.28</v>
       </c>
       <c r="C235" s="5" t="n">
-        <v>11.57</v>
+        <v>11.86</v>
       </c>
       <c r="D235" s="5" t="n">
         <v>35.23</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>13.03</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="236">
@@ -10857,13 +10857,13 @@
         <v>48.09</v>
       </c>
       <c r="C236" s="5" t="n">
-        <v>32.05</v>
+        <v>32.16</v>
       </c>
       <c r="D236" s="5" t="n">
         <v>53.91</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>35.93</v>
+        <v>36.05</v>
       </c>
     </row>
     <row r="237">
@@ -10876,13 +10876,13 @@
         <v>58.01</v>
       </c>
       <c r="C237" s="5" t="n">
-        <v>55.29</v>
+        <v>55.28</v>
       </c>
       <c r="D237" s="5" t="n">
         <v>64.73999999999999</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>61.71</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="238">
@@ -10895,13 +10895,13 @@
         <v>62.02</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>54.59</v>
+        <v>54.34</v>
       </c>
       <c r="D238" s="5" t="n">
         <v>68.91</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>60.65</v>
+        <v>60.38</v>
       </c>
     </row>
     <row r="239">
@@ -10914,13 +10914,13 @@
         <v>83.62</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>86.78</v>
+        <v>86.66</v>
       </c>
       <c r="D239" s="5" t="n">
         <v>92.65000000000001</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>96.15000000000001</v>
+        <v>96.01000000000001</v>
       </c>
     </row>
     <row r="240">
@@ -10933,13 +10933,13 @@
         <v>127.15</v>
       </c>
       <c r="C240" s="5" t="n">
-        <v>145.97</v>
+        <v>145.34</v>
       </c>
       <c r="D240" s="5" t="n">
         <v>140.47</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>161.26</v>
+        <v>160.57</v>
       </c>
     </row>
     <row r="241">
@@ -10952,13 +10952,13 @@
         <v>54.53</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>85.79000000000001</v>
+        <v>85.58</v>
       </c>
       <c r="D241" s="5" t="n">
         <v>60.07</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>94.51000000000001</v>
+        <v>94.28</v>
       </c>
     </row>
     <row r="242">
@@ -10971,13 +10971,13 @@
         <v>55.21</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>76.38</v>
+        <v>75.97</v>
       </c>
       <c r="D242" s="5" t="n">
         <v>60.59</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>83.81999999999999</v>
+        <v>83.37</v>
       </c>
     </row>
     <row r="243">
@@ -10990,13 +10990,13 @@
         <v>64.66</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>80.04000000000001</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="D243" s="5" t="n">
         <v>70.69</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>87.5</v>
+        <v>86.95999999999999</v>
       </c>
     </row>
     <row r="244">
@@ -11009,13 +11009,13 @@
         <v>26.31</v>
       </c>
       <c r="C244" s="5" t="n">
-        <v>28.16</v>
+        <v>28.25</v>
       </c>
       <c r="D244" s="5" t="n">
         <v>28.65</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>30.67</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="245">
@@ -11028,13 +11028,13 @@
         <v>17.19</v>
       </c>
       <c r="C245" s="5" t="n">
-        <v>15.14</v>
+        <v>15.18</v>
       </c>
       <c r="D245" s="5" t="n">
         <v>18.68</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>16.45</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="246">
@@ -11047,13 +11047,13 @@
         <v>34.94</v>
       </c>
       <c r="C246" s="5" t="n">
-        <v>31.79</v>
+        <v>31.91</v>
       </c>
       <c r="D246" s="5" t="n">
         <v>37.89</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>34.48</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="247">
@@ -11066,13 +11066,13 @@
         <v>25.29</v>
       </c>
       <c r="C247" s="5" t="n">
-        <v>25.23</v>
+        <v>25.38</v>
       </c>
       <c r="D247" s="5" t="n">
         <v>27.37</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>27.31</v>
+        <v>27.47</v>
       </c>
     </row>
     <row r="248">
@@ -11085,13 +11085,13 @@
         <v>22.1</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>17.65</v>
+        <v>17.76</v>
       </c>
       <c r="D248" s="5" t="n">
         <v>23.84</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>19.04</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="249">
@@ -11104,13 +11104,13 @@
         <v>82.94</v>
       </c>
       <c r="C249" s="5" t="n">
-        <v>133.13</v>
+        <v>133.12</v>
       </c>
       <c r="D249" s="5" t="n">
         <v>89.20999999999999</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>143.2</v>
+        <v>143.19</v>
       </c>
     </row>
     <row r="250">
@@ -11123,13 +11123,13 @@
         <v>51.99</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>46.25</v>
+        <v>46.11</v>
       </c>
       <c r="D250" s="5" t="n">
         <v>55.75</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>49.59</v>
+        <v>49.44</v>
       </c>
     </row>
     <row r="251">
@@ -11142,13 +11142,13 @@
         <v>84.8</v>
       </c>
       <c r="C251" s="5" t="n">
-        <v>80.23</v>
+        <v>79.92</v>
       </c>
       <c r="D251" s="5" t="n">
         <v>90.62</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>85.73</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="252">
@@ -11161,13 +11161,13 @@
         <v>132.97</v>
       </c>
       <c r="C252" s="5" t="n">
-        <v>146.58</v>
+        <v>145.96</v>
       </c>
       <c r="D252" s="5" t="n">
         <v>141.6</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>156.09</v>
+        <v>155.43</v>
       </c>
     </row>
     <row r="253">
@@ -11180,13 +11180,13 @@
         <v>164.23</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>198.82</v>
+        <v>198.44</v>
       </c>
       <c r="D253" s="5" t="n">
         <v>174.28</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>210.99</v>
+        <v>210.58</v>
       </c>
     </row>
     <row r="254">
@@ -11199,13 +11199,13 @@
         <v>149.14</v>
       </c>
       <c r="C254" s="5" t="n">
-        <v>191.83</v>
+        <v>191.27</v>
       </c>
       <c r="D254" s="5" t="n">
         <v>158.15</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>203.42</v>
+        <v>202.83</v>
       </c>
     </row>
     <row r="255">
@@ -11218,13 +11218,13 @@
         <v>143.4</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>216.14</v>
+        <v>215.57</v>
       </c>
       <c r="D255" s="5" t="n">
         <v>151.95</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>229.03</v>
+        <v>228.43</v>
       </c>
     </row>
     <row r="256">
@@ -11256,13 +11256,13 @@
         <v>20.36</v>
       </c>
       <c r="C257" s="5" t="n">
-        <v>10.18</v>
+        <v>10.31</v>
       </c>
       <c r="D257" s="5" t="n">
         <v>21.54</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>10.77</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="258">
@@ -11275,13 +11275,13 @@
         <v>64.08</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>52.94</v>
+        <v>53.17</v>
       </c>
       <c r="D258" s="5" t="n">
         <v>67.76000000000001</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>55.98</v>
+        <v>56.23</v>
       </c>
     </row>
     <row r="259">
@@ -11294,13 +11294,13 @@
         <v>52.25</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>39.93</v>
+        <v>40.31</v>
       </c>
       <c r="D259" s="5" t="n">
         <v>55.22</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>42.2</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="260">
@@ -11313,13 +11313,13 @@
         <v>48.35</v>
       </c>
       <c r="C260" s="5" t="n">
-        <v>23.72</v>
+        <v>23.93</v>
       </c>
       <c r="D260" s="5" t="n">
         <v>50.94</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>24.99</v>
+        <v>25.21</v>
       </c>
     </row>
     <row r="261">
@@ -11332,13 +11332,13 @@
         <v>68.55</v>
       </c>
       <c r="C261" s="5" t="n">
-        <v>76.73</v>
+        <v>76.84</v>
       </c>
       <c r="D261" s="5" t="n">
         <v>72</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>80.59999999999999</v>
+        <v>80.70999999999999</v>
       </c>
     </row>
     <row r="262">
@@ -11351,13 +11351,13 @@
         <v>61.75</v>
       </c>
       <c r="C262" s="5" t="n">
-        <v>62.93</v>
+        <v>62.81</v>
       </c>
       <c r="D262" s="5" t="n">
         <v>64.66</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>65.90000000000001</v>
+        <v>65.77</v>
       </c>
     </row>
     <row r="263">
@@ -11370,13 +11370,13 @@
         <v>74.76000000000001</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>70.56</v>
+        <v>70.45</v>
       </c>
       <c r="D263" s="5" t="n">
         <v>78.09</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>73.70999999999999</v>
+        <v>73.59</v>
       </c>
     </row>
     <row r="264">
@@ -11389,13 +11389,13 @@
         <v>78.05</v>
       </c>
       <c r="C264" s="5" t="n">
-        <v>93.92</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="D264" s="5" t="n">
         <v>81.33</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>97.86</v>
+        <v>97.61</v>
       </c>
     </row>
     <row r="265">
@@ -11408,13 +11408,13 @@
         <v>264.6</v>
       </c>
       <c r="C265" s="5" t="n">
-        <v>463.18</v>
+        <v>462.78</v>
       </c>
       <c r="D265" s="5" t="n">
         <v>275.03</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>481.44</v>
+        <v>481.02</v>
       </c>
     </row>
     <row r="266">
@@ -11427,13 +11427,13 @@
         <v>82.13</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>107.96</v>
+        <v>107.55</v>
       </c>
       <c r="D266" s="5" t="n">
         <v>84.98999999999999</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>111.72</v>
+        <v>111.3</v>
       </c>
     </row>
     <row r="267">
@@ -11446,13 +11446,13 @@
         <v>93.19</v>
       </c>
       <c r="C267" s="5" t="n">
-        <v>107.79</v>
+        <v>107.41</v>
       </c>
       <c r="D267" s="5" t="n">
         <v>96.02</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>111.06</v>
+        <v>110.67</v>
       </c>
     </row>
     <row r="268">
@@ -11465,13 +11465,13 @@
         <v>55.27</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>61.8</v>
+        <v>61.94</v>
       </c>
       <c r="D268" s="5" t="n">
         <v>56.7</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>63.4</v>
+        <v>63.54</v>
       </c>
     </row>
     <row r="269">
@@ -11484,13 +11484,13 @@
         <v>51.37</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>45.13</v>
+        <v>45.17</v>
       </c>
       <c r="D269" s="5" t="n">
         <v>52.6</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>46.21</v>
+        <v>46.25</v>
       </c>
     </row>
     <row r="270">
@@ -11503,13 +11503,13 @@
         <v>31.92</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>13.79</v>
+        <v>14.11</v>
       </c>
       <c r="D270" s="5" t="n">
         <v>32.62</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>14.09</v>
+        <v>14.42</v>
       </c>
     </row>
     <row r="271">
@@ -11522,13 +11522,13 @@
         <v>27.51</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>16.99</v>
+        <v>17.32</v>
       </c>
       <c r="D271" s="5" t="n">
         <v>28.06</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>17.33</v>
+        <v>17.66</v>
       </c>
     </row>
     <row r="272">
@@ -11541,13 +11541,13 @@
         <v>38.55</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>43.74</v>
+        <v>43.95</v>
       </c>
       <c r="D272" s="5" t="n">
         <v>39.14</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>44.4</v>
+        <v>44.62</v>
       </c>
     </row>
     <row r="273">
@@ -11560,13 +11560,13 @@
         <v>45.06</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>40.2</v>
+        <v>40.32</v>
       </c>
       <c r="D273" s="5" t="n">
         <v>45.54</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>40.62</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="274">
@@ -11579,13 +11579,13 @@
         <v>44.74</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>44.69</v>
+        <v>44.57</v>
       </c>
       <c r="D274" s="5" t="n">
         <v>45.01</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>44.96</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="275">
@@ -11598,13 +11598,13 @@
         <v>35.68</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>37.67</v>
+        <v>37.64</v>
       </c>
       <c r="D275" s="5" t="n">
         <v>35.82</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>37.82</v>
+        <v>37.79</v>
       </c>
     </row>
     <row r="276">
@@ -11617,13 +11617,13 @@
         <v>64.77</v>
       </c>
       <c r="C276" s="5" t="n">
-        <v>73.73999999999999</v>
+        <v>73.55</v>
       </c>
       <c r="D276" s="5" t="n">
         <v>64.90000000000001</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>73.89</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="277">
@@ -11636,13 +11636,13 @@
         <v>66.81</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>78.04000000000001</v>
+        <v>77.88</v>
       </c>
       <c r="D277" s="5" t="n">
         <v>66.81</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>78.04000000000001</v>
+        <v>77.88</v>
       </c>
     </row>
     <row r="278">
@@ -11655,13 +11655,13 @@
         <v>70.36</v>
       </c>
       <c r="C278" s="5" t="n">
-        <v>90.75</v>
+        <v>90.62</v>
       </c>
       <c r="D278" s="5" t="n">
         <v>70.36</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>90.75</v>
+        <v>90.62</v>
       </c>
     </row>
     <row r="279">
@@ -11674,13 +11674,13 @@
         <v>60.4</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>68.86</v>
+        <v>68.78</v>
       </c>
       <c r="D279" s="5" t="n">
         <v>60.4</v>
       </c>
       <c r="E279" s="5" t="n">
-        <v>68.86</v>
+        <v>68.78</v>
       </c>
     </row>
     <row r="280">
@@ -11693,13 +11693,13 @@
         <v>36.83</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>36.93</v>
+        <v>37.02</v>
       </c>
       <c r="D280" s="5" t="n">
         <v>36.83</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>36.93</v>
+        <v>37.02</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/VIC_historical_prices.xlsx
+++ b/outputs/VIC_historical_prices.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -616,10 +616,55 @@
         <v>111.75</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>15-Year Average</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>66.79000000000001</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>79.47</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>82.81999999999999</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>98.65000000000001</v>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>20-Year Average</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>60.34</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>73.86</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>78.58</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>96.90000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Data through: Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Real prices are in Jun 2026 dollars (latest published CPI quarter). The latest 3 month(s) have no CPI yet, so real = nominal there (flagged in Monthly Data).</t>
         </is>
       </c>
     </row>
@@ -634,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F280"/>
+  <dimension ref="A1:G280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -643,6 +688,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -676,6 +722,11 @@
           <t>Carbon Tax</t>
         </is>
       </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>CPI Estimated</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -696,6 +747,7 @@
         <v>61.83</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
+      <c r="G2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -716,6 +768,7 @@
         <v>43.93</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -736,6 +789,7 @@
         <v>46.9</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -756,6 +810,7 @@
         <v>46.57</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -776,6 +831,7 @@
         <v>48.02</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -796,6 +852,7 @@
         <v>62.81</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -816,6 +873,7 @@
         <v>55.66</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -836,6 +894,7 @@
         <v>88.95999999999999</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -856,6 +915,7 @@
         <v>51.6</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -876,6 +936,7 @@
         <v>67.68000000000001</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -896,6 +957,7 @@
         <v>72.34999999999999</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -916,6 +978,7 @@
         <v>63.58</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -936,6 +999,7 @@
         <v>79.84</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -956,6 +1020,7 @@
         <v>49.73</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -976,6 +1041,7 @@
         <v>56.94</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -996,6 +1062,7 @@
         <v>127.91</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1016,6 +1083,7 @@
         <v>79.64</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1036,6 +1104,7 @@
         <v>59</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1056,6 +1125,7 @@
         <v>53.54</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1076,6 +1146,7 @@
         <v>48.78</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1096,6 +1167,7 @@
         <v>37.58</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1116,6 +1188,7 @@
         <v>67.54000000000001</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1136,6 +1209,7 @@
         <v>51.84</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1156,6 +1230,7 @@
         <v>48.58</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1176,6 +1251,7 @@
         <v>57.43</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1196,6 +1272,7 @@
         <v>71.15000000000001</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1216,6 +1293,7 @@
         <v>65.89</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1236,6 +1314,7 @@
         <v>50.15</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1256,6 +1335,7 @@
         <v>81.13</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1276,6 +1356,7 @@
         <v>86.34</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1296,6 +1377,7 @@
         <v>154.88</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1316,6 +1398,7 @@
         <v>183.92</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -1336,6 +1419,7 @@
         <v>50.61</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1356,6 +1440,7 @@
         <v>48.34</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -1376,6 +1461,7 @@
         <v>65.38</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -1396,6 +1482,7 @@
         <v>73.06999999999999</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -1416,6 +1503,7 @@
         <v>123.04</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -1436,6 +1524,7 @@
         <v>66.38</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -1456,6 +1545,7 @@
         <v>65.86</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -1476,6 +1566,7 @@
         <v>58.81</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -1496,6 +1587,7 @@
         <v>71.53</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -1516,6 +1608,7 @@
         <v>47.74</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
+      <c r="G43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -1536,6 +1629,7 @@
         <v>281.22</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
+      <c r="G44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -1556,6 +1650,7 @@
         <v>116.64</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -1576,6 +1671,7 @@
         <v>126.48</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
+      <c r="G46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -1596,6 +1692,7 @@
         <v>137.17</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -1616,6 +1713,7 @@
         <v>126.46</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
+      <c r="G48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -1636,6 +1734,7 @@
         <v>367.06</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -1656,6 +1755,7 @@
         <v>192.69</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
+      <c r="G50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -1676,6 +1776,7 @@
         <v>84.48</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -1696,6 +1797,7 @@
         <v>91.2</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
+      <c r="G52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -1716,6 +1818,7 @@
         <v>74.90000000000001</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
+      <c r="G53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -1736,6 +1839,7 @@
         <v>89.31</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
+      <c r="G54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -1756,6 +1860,7 @@
         <v>102.06</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -1776,6 +1881,7 @@
         <v>90.15000000000001</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -1796,6 +1902,7 @@
         <v>84.43000000000001</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
+      <c r="G57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -1816,6 +1923,7 @@
         <v>137.19</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
+      <c r="G58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -1836,6 +1944,7 @@
         <v>80.68000000000001</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
+      <c r="G59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -1856,6 +1965,7 @@
         <v>103.22</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -1876,6 +1986,7 @@
         <v>83.58</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
+      <c r="G61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -1896,6 +2007,7 @@
         <v>96.26000000000001</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
+      <c r="G62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -1916,6 +2028,7 @@
         <v>80.56</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -1936,6 +2049,7 @@
         <v>75.54000000000001</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -1956,6 +2070,7 @@
         <v>80.94</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
+      <c r="G65" s="7" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -1976,6 +2091,7 @@
         <v>70.95</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
+      <c r="G66" s="7" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -1996,6 +2112,7 @@
         <v>44</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
+      <c r="G67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -2016,6 +2133,7 @@
         <v>395.33</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
+      <c r="G68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -2036,6 +2154,7 @@
         <v>70.3</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
+      <c r="G69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -2056,6 +2175,7 @@
         <v>50.99</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
+      <c r="G70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -2076,6 +2196,7 @@
         <v>77.86</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
+      <c r="G71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -2096,6 +2217,7 @@
         <v>59.69</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
+      <c r="G72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -2116,6 +2238,7 @@
         <v>58.75</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
+      <c r="G73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -2136,6 +2259,7 @@
         <v>51.29</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
+      <c r="G74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -2156,6 +2280,7 @@
         <v>43.8</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
+      <c r="G75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -2176,6 +2301,7 @@
         <v>43.05</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
+      <c r="G76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -2196,6 +2322,7 @@
         <v>48.32</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
+      <c r="G77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -2216,6 +2343,7 @@
         <v>70.04000000000001</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -2236,6 +2364,7 @@
         <v>45.88</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
+      <c r="G79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -2256,6 +2385,7 @@
         <v>178.52</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
+      <c r="G80" s="7" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -2276,6 +2406,7 @@
         <v>192.1</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -2296,6 +2427,7 @@
         <v>41.58</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
+      <c r="G82" s="7" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -2316,6 +2448,7 @@
         <v>202.71</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
+      <c r="G83" s="7" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -2336,6 +2469,7 @@
         <v>53.17</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
+      <c r="G84" s="7" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -2356,6 +2490,7 @@
         <v>55.74</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
+      <c r="G85" s="7" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -2376,6 +2511,7 @@
         <v>46.41</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
+      <c r="G86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -2396,6 +2532,7 @@
         <v>46.88</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -2416,6 +2553,7 @@
         <v>37.89</v>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
+      <c r="G88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -2436,6 +2574,7 @@
         <v>37.09</v>
       </c>
       <c r="F89" s="7" t="inlineStr"/>
+      <c r="G89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -2456,6 +2595,7 @@
         <v>31.59</v>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
+      <c r="G90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -2476,6 +2616,7 @@
         <v>28.66</v>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
+      <c r="G91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -2496,6 +2637,7 @@
         <v>99.73</v>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
+      <c r="G92" s="7" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -2516,6 +2658,7 @@
         <v>89.01000000000001</v>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
+      <c r="G93" s="7" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -2536,6 +2679,7 @@
         <v>42.44</v>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -2556,6 +2700,7 @@
         <v>42.2</v>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
+      <c r="G95" s="7" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -2576,6 +2721,7 @@
         <v>60.06</v>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
+      <c r="G96" s="7" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -2596,6 +2742,7 @@
         <v>50.15</v>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
+      <c r="G97" s="7" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -2616,6 +2763,7 @@
         <v>55.91</v>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
+      <c r="G98" s="7" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -2636,6 +2784,7 @@
         <v>52.05</v>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
+      <c r="G99" s="7" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -2656,6 +2805,7 @@
         <v>46.45</v>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
+      <c r="G100" s="7" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -2676,6 +2826,7 @@
         <v>42.13</v>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
+      <c r="G101" s="7" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -2696,6 +2847,7 @@
         <v>44.88</v>
       </c>
       <c r="F102" s="7" t="inlineStr"/>
+      <c r="G102" s="7" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -2716,6 +2868,7 @@
         <v>37.52</v>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
+      <c r="G103" s="7" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -2736,6 +2889,7 @@
         <v>42.72</v>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
+      <c r="G104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -2756,6 +2910,7 @@
         <v>43.83</v>
       </c>
       <c r="F105" s="7" t="inlineStr"/>
+      <c r="G105" s="7" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -2776,6 +2931,7 @@
         <v>40.66</v>
       </c>
       <c r="F106" s="7" t="inlineStr"/>
+      <c r="G106" s="7" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -2796,6 +2952,7 @@
         <v>53.32</v>
       </c>
       <c r="F107" s="7" t="inlineStr"/>
+      <c r="G107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -2816,6 +2973,7 @@
         <v>44.22</v>
       </c>
       <c r="F108" s="7" t="inlineStr"/>
+      <c r="G108" s="7" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -2836,6 +2994,7 @@
         <v>62.33</v>
       </c>
       <c r="F109" s="7" t="inlineStr"/>
+      <c r="G109" s="7" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
@@ -2860,6 +3019,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G110" s="10" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
@@ -2884,6 +3044,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G111" s="10" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
@@ -2908,6 +3069,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G112" s="10" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
@@ -2932,6 +3094,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
@@ -2956,6 +3119,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G114" s="10" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
@@ -2980,6 +3144,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G115" s="10" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
@@ -3004,6 +3169,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G116" s="10" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
@@ -3028,6 +3194,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G117" s="10" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
@@ -3052,6 +3219,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G118" s="10" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
@@ -3076,6 +3244,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G119" s="10" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
@@ -3100,6 +3269,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G120" s="10" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
@@ -3124,6 +3294,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G121" s="10" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
@@ -3148,6 +3319,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G122" s="10" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
@@ -3172,6 +3344,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G123" s="10" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
@@ -3196,6 +3369,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G124" s="10" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
@@ -3220,6 +3394,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G125" s="10" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
@@ -3244,6 +3419,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G126" s="10" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
@@ -3268,6 +3444,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G127" s="10" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
@@ -3292,6 +3469,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G128" s="10" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
@@ -3316,6 +3494,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G129" s="10" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
@@ -3340,6 +3519,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G130" s="10" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
@@ -3364,6 +3544,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G131" s="10" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="8" t="inlineStr">
@@ -3388,6 +3569,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G132" s="10" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
@@ -3412,6 +3594,7 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G133" s="10" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -3432,6 +3615,7 @@
         <v>60.53</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
+      <c r="G134" s="7" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -3452,6 +3636,7 @@
         <v>55.98</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
+      <c r="G135" s="7" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -3472,6 +3657,7 @@
         <v>57.59</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
+      <c r="G136" s="7" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -3492,6 +3678,7 @@
         <v>42.02</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
+      <c r="G137" s="7" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -3512,6 +3699,7 @@
         <v>47.05</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
+      <c r="G138" s="7" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -3532,6 +3720,7 @@
         <v>42.88</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
+      <c r="G139" s="7" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -3552,6 +3741,7 @@
         <v>46.07</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
+      <c r="G140" s="7" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -3572,6 +3762,7 @@
         <v>47.86</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
+      <c r="G141" s="7" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -3592,6 +3783,7 @@
         <v>42.49</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
+      <c r="G142" s="7" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -3612,6 +3804,7 @@
         <v>48.05</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
+      <c r="G143" s="7" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -3632,6 +3825,7 @@
         <v>52.23</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
+      <c r="G144" s="7" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -3652,6 +3846,7 @@
         <v>56.08</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
+      <c r="G145" s="7" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -3672,6 +3867,7 @@
         <v>58</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
+      <c r="G146" s="7" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -3692,6 +3888,7 @@
         <v>56.59</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
+      <c r="G147" s="7" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -3712,6 +3909,7 @@
         <v>68.95</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
+      <c r="G148" s="7" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -3732,6 +3930,7 @@
         <v>60.59</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
+      <c r="G149" s="7" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -3752,6 +3951,7 @@
         <v>60.81</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
+      <c r="G150" s="7" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -3772,6 +3972,7 @@
         <v>84.16</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
+      <c r="G151" s="7" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -3792,6 +3993,7 @@
         <v>98.65000000000001</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
+      <c r="G152" s="7" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -3812,6 +4014,7 @@
         <v>59.72</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
+      <c r="G153" s="7" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -3832,6 +4035,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
+      <c r="G154" s="7" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -3852,6 +4056,7 @@
         <v>80.43000000000001</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
+      <c r="G155" s="7" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -3872,6 +4077,7 @@
         <v>99.91</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
+      <c r="G156" s="7" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -3892,6 +4098,7 @@
         <v>155.19</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
+      <c r="G157" s="7" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -3912,6 +4119,7 @@
         <v>114.3</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
+      <c r="G158" s="7" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -3932,6 +4140,7 @@
         <v>72.20999999999999</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
+      <c r="G159" s="7" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -3952,6 +4161,7 @@
         <v>64.08</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
+      <c r="G160" s="7" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -3972,6 +4182,7 @@
         <v>51.59</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
+      <c r="G161" s="7" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -3992,6 +4203,7 @@
         <v>60.45</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
+      <c r="G162" s="7" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -4012,6 +4224,7 @@
         <v>49.64</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
+      <c r="G163" s="7" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -4032,6 +4245,7 @@
         <v>107.36</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
+      <c r="G164" s="7" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -4052,6 +4266,7 @@
         <v>149.15</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
+      <c r="G165" s="7" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -4072,6 +4287,7 @@
         <v>147.14</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
+      <c r="G166" s="7" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -4092,6 +4308,7 @@
         <v>162.27</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
+      <c r="G167" s="7" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -4112,6 +4329,7 @@
         <v>161.42</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
+      <c r="G168" s="7" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -4132,6 +4350,7 @@
         <v>137.93</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
+      <c r="G169" s="7" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -4152,6 +4371,7 @@
         <v>172.21</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
+      <c r="G170" s="7" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -4172,6 +4392,7 @@
         <v>155.03</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
+      <c r="G171" s="7" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -4192,6 +4413,7 @@
         <v>117.85</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
+      <c r="G172" s="7" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -4212,6 +4434,7 @@
         <v>107.85</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
+      <c r="G173" s="7" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
@@ -4232,6 +4455,7 @@
         <v>146.76</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
+      <c r="G174" s="7" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -4252,6 +4476,7 @@
         <v>127.71</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
+      <c r="G175" s="7" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
@@ -4272,6 +4497,7 @@
         <v>239.48</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
+      <c r="G176" s="7" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -4292,6 +4518,7 @@
         <v>162</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
+      <c r="G177" s="7" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -4312,6 +4539,7 @@
         <v>106.56</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
+      <c r="G178" s="7" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -4332,6 +4560,7 @@
         <v>112.52</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
+      <c r="G179" s="7" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -4352,6 +4581,7 @@
         <v>121.96</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
+      <c r="G180" s="7" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -4372,6 +4602,7 @@
         <v>143.12</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
+      <c r="G181" s="7" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -4392,6 +4623,7 @@
         <v>113.06</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
+      <c r="G182" s="7" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -4412,6 +4644,7 @@
         <v>130.39</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
+      <c r="G183" s="7" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -4432,6 +4665,7 @@
         <v>138.79</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
+      <c r="G184" s="7" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -4452,6 +4686,7 @@
         <v>140.44</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
+      <c r="G185" s="7" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -4472,6 +4707,7 @@
         <v>134.81</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
+      <c r="G186" s="7" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -4492,6 +4728,7 @@
         <v>146.63</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
+      <c r="G187" s="7" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -4512,6 +4749,7 @@
         <v>544.12</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
+      <c r="G188" s="7" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -4532,6 +4770,7 @@
         <v>154.25</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
+      <c r="G189" s="7" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -4552,6 +4791,7 @@
         <v>227.32</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
+      <c r="G190" s="7" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -4572,6 +4812,7 @@
         <v>135.85</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
+      <c r="G191" s="7" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -4592,6 +4833,7 @@
         <v>132.93</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
+      <c r="G192" s="7" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -4612,6 +4854,7 @@
         <v>155.03</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
+      <c r="G193" s="7" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
@@ -4632,6 +4875,7 @@
         <v>133.53</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
+      <c r="G194" s="7" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -4652,6 +4896,7 @@
         <v>164.13</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
+      <c r="G195" s="7" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
@@ -4672,6 +4917,7 @@
         <v>152.05</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
+      <c r="G196" s="7" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -4692,6 +4938,7 @@
         <v>141.34</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
+      <c r="G197" s="7" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
@@ -4712,6 +4959,7 @@
         <v>87.31999999999999</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
+      <c r="G198" s="7" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -4732,6 +4980,7 @@
         <v>97.92</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
+      <c r="G199" s="7" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
@@ -4752,6 +5001,7 @@
         <v>323.5</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
+      <c r="G200" s="7" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -4772,6 +5022,7 @@
         <v>69.64</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
+      <c r="G201" s="7" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
@@ -4792,6 +5043,7 @@
         <v>62.75</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
+      <c r="G202" s="7" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -4812,6 +5064,7 @@
         <v>53.14</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
+      <c r="G203" s="7" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
@@ -4832,6 +5085,7 @@
         <v>59.73</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
+      <c r="G204" s="7" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -4852,6 +5106,7 @@
         <v>80.48999999999999</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
+      <c r="G205" s="7" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -4872,6 +5127,7 @@
         <v>95.48</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
+      <c r="G206" s="7" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -4892,6 +5148,7 @@
         <v>83.62</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
+      <c r="G207" s="7" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
@@ -4912,6 +5169,7 @@
         <v>49.06</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
+      <c r="G208" s="7" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -4932,6 +5190,7 @@
         <v>67.88</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
+      <c r="G209" s="7" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -4952,6 +5211,7 @@
         <v>62.5</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
+      <c r="G210" s="7" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
@@ -4972,6 +5232,7 @@
         <v>29.45</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
+      <c r="G211" s="7" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
@@ -4992,6 +5253,7 @@
         <v>25.92</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
+      <c r="G212" s="7" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
@@ -5012,6 +5274,7 @@
         <v>30.83</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
+      <c r="G213" s="7" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
@@ -5032,6 +5295,7 @@
         <v>39.1</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
+      <c r="G214" s="7" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -5052,6 +5316,7 @@
         <v>75.37</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
+      <c r="G215" s="7" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
@@ -5072,6 +5337,7 @@
         <v>141.45</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
+      <c r="G216" s="7" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
@@ -5092,6 +5358,7 @@
         <v>133.16</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
+      <c r="G217" s="7" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
@@ -5112,6 +5379,7 @@
         <v>157.12</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
+      <c r="G218" s="7" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
@@ -5132,6 +5400,7 @@
         <v>67.75</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
+      <c r="G219" s="7" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
@@ -5152,6 +5421,7 @@
         <v>40.94</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
+      <c r="G220" s="7" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
@@ -5172,6 +5442,7 @@
         <v>18.42</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
+      <c r="G221" s="7" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
@@ -5192,6 +5463,7 @@
         <v>49.71</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
+      <c r="G222" s="7" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
@@ -5212,6 +5484,7 @@
         <v>37.57</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
+      <c r="G223" s="7" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
@@ -5232,6 +5505,7 @@
         <v>90.51000000000001</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
+      <c r="G224" s="7" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
@@ -5252,6 +5526,7 @@
         <v>58.03</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
+      <c r="G225" s="7" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
@@ -5272,6 +5547,7 @@
         <v>66.83</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
+      <c r="G226" s="7" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
@@ -5292,6 +5568,7 @@
         <v>198.31</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
+      <c r="G227" s="7" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
@@ -5312,6 +5589,7 @@
         <v>310.24</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
+      <c r="G228" s="7" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
@@ -5332,6 +5610,7 @@
         <v>438.34</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
+      <c r="G229" s="7" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
@@ -5352,6 +5631,7 @@
         <v>500.61</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
+      <c r="G230" s="7" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
@@ -5372,6 +5652,7 @@
         <v>157.8</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
+      <c r="G231" s="7" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
@@ -5392,6 +5673,7 @@
         <v>149.83</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
+      <c r="G232" s="7" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
@@ -5412,6 +5694,7 @@
         <v>110.56</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
+      <c r="G233" s="7" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
@@ -5432,6 +5715,7 @@
         <v>66.3</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
+      <c r="G234" s="7" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
@@ -5452,6 +5736,7 @@
         <v>13.36</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
+      <c r="G235" s="7" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
@@ -5472,6 +5757,7 @@
         <v>36.05</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
+      <c r="G236" s="7" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
@@ -5492,6 +5778,7 @@
         <v>61.7</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
+      <c r="G237" s="7" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
@@ -5512,6 +5799,7 @@
         <v>60.38</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
+      <c r="G238" s="7" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
@@ -5532,6 +5820,7 @@
         <v>96.01000000000001</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
+      <c r="G239" s="7" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
@@ -5552,6 +5841,7 @@
         <v>160.57</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
+      <c r="G240" s="7" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
@@ -5572,6 +5862,7 @@
         <v>94.28</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
+      <c r="G241" s="7" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
@@ -5592,6 +5883,7 @@
         <v>83.37</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
+      <c r="G242" s="7" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
@@ -5612,6 +5904,7 @@
         <v>86.95999999999999</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
+      <c r="G243" s="7" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
@@ -5632,6 +5925,7 @@
         <v>30.77</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
+      <c r="G244" s="7" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
@@ -5652,6 +5946,7 @@
         <v>16.5</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
+      <c r="G245" s="7" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
@@ -5672,6 +5967,7 @@
         <v>34.61</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
+      <c r="G246" s="7" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
@@ -5692,6 +5988,7 @@
         <v>27.47</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
+      <c r="G247" s="7" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
@@ -5712,6 +6009,7 @@
         <v>19.16</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
+      <c r="G248" s="7" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
@@ -5732,6 +6030,7 @@
         <v>143.19</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
+      <c r="G249" s="7" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
@@ -5752,6 +6051,7 @@
         <v>49.44</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
+      <c r="G250" s="7" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
@@ -5772,6 +6072,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
+      <c r="G251" s="7" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
@@ -5792,6 +6093,7 @@
         <v>155.43</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
+      <c r="G252" s="7" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
@@ -5812,6 +6114,7 @@
         <v>210.58</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
+      <c r="G253" s="7" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
@@ -5832,6 +6135,7 @@
         <v>202.83</v>
       </c>
       <c r="F254" s="7" t="inlineStr"/>
+      <c r="G254" s="7" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
@@ -5852,6 +6156,7 @@
         <v>228.43</v>
       </c>
       <c r="F255" s="7" t="inlineStr"/>
+      <c r="G255" s="7" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
@@ -5872,6 +6177,7 @@
         <v>28.06</v>
       </c>
       <c r="F256" s="7" t="inlineStr"/>
+      <c r="G256" s="7" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
@@ -5892,6 +6198,7 @@
         <v>10.91</v>
       </c>
       <c r="F257" s="7" t="inlineStr"/>
+      <c r="G257" s="7" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
@@ -5912,6 +6219,7 @@
         <v>56.23</v>
       </c>
       <c r="F258" s="7" t="inlineStr"/>
+      <c r="G258" s="7" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
@@ -5932,6 +6240,7 @@
         <v>42.6</v>
       </c>
       <c r="F259" s="7" t="inlineStr"/>
+      <c r="G259" s="7" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
@@ -5952,6 +6261,7 @@
         <v>25.21</v>
       </c>
       <c r="F260" s="7" t="inlineStr"/>
+      <c r="G260" s="7" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
@@ -5972,6 +6282,7 @@
         <v>80.70999999999999</v>
       </c>
       <c r="F261" s="7" t="inlineStr"/>
+      <c r="G261" s="7" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
@@ -5992,6 +6303,7 @@
         <v>65.77</v>
       </c>
       <c r="F262" s="7" t="inlineStr"/>
+      <c r="G262" s="7" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
@@ -6012,6 +6324,7 @@
         <v>73.59</v>
       </c>
       <c r="F263" s="7" t="inlineStr"/>
+      <c r="G263" s="7" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
@@ -6032,6 +6345,7 @@
         <v>97.61</v>
       </c>
       <c r="F264" s="7" t="inlineStr"/>
+      <c r="G264" s="7" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
@@ -6052,6 +6366,7 @@
         <v>481.02</v>
       </c>
       <c r="F265" s="7" t="inlineStr"/>
+      <c r="G265" s="7" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
@@ -6072,6 +6387,7 @@
         <v>111.3</v>
       </c>
       <c r="F266" s="7" t="inlineStr"/>
+      <c r="G266" s="7" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
@@ -6092,6 +6408,7 @@
         <v>110.67</v>
       </c>
       <c r="F267" s="7" t="inlineStr"/>
+      <c r="G267" s="7" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
@@ -6112,6 +6429,7 @@
         <v>63.54</v>
       </c>
       <c r="F268" s="7" t="inlineStr"/>
+      <c r="G268" s="7" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
@@ -6132,6 +6450,7 @@
         <v>46.25</v>
       </c>
       <c r="F269" s="7" t="inlineStr"/>
+      <c r="G269" s="7" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
@@ -6152,6 +6471,7 @@
         <v>14.42</v>
       </c>
       <c r="F270" s="7" t="inlineStr"/>
+      <c r="G270" s="7" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
@@ -6172,6 +6492,7 @@
         <v>17.66</v>
       </c>
       <c r="F271" s="7" t="inlineStr"/>
+      <c r="G271" s="7" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
@@ -6192,6 +6513,7 @@
         <v>44.62</v>
       </c>
       <c r="F272" s="7" t="inlineStr"/>
+      <c r="G272" s="7" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
@@ -6212,6 +6534,7 @@
         <v>40.75</v>
       </c>
       <c r="F273" s="7" t="inlineStr"/>
+      <c r="G273" s="7" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
@@ -6232,6 +6555,7 @@
         <v>44.84</v>
       </c>
       <c r="F274" s="7" t="inlineStr"/>
+      <c r="G274" s="7" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
@@ -6252,6 +6576,7 @@
         <v>37.79</v>
       </c>
       <c r="F275" s="7" t="inlineStr"/>
+      <c r="G275" s="7" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
@@ -6272,6 +6597,7 @@
         <v>73.7</v>
       </c>
       <c r="F276" s="7" t="inlineStr"/>
+      <c r="G276" s="7" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
@@ -6292,6 +6618,7 @@
         <v>77.88</v>
       </c>
       <c r="F277" s="7" t="inlineStr"/>
+      <c r="G277" s="7" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
@@ -6312,6 +6639,11 @@
         <v>90.62</v>
       </c>
       <c r="F278" s="7" t="inlineStr"/>
+      <c r="G278" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
@@ -6332,6 +6664,11 @@
         <v>68.78</v>
       </c>
       <c r="F279" s="7" t="inlineStr"/>
+      <c r="G279" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
@@ -6352,6 +6689,11 @@
         <v>37.02</v>
       </c>
       <c r="F280" s="7" t="inlineStr"/>
+      <c r="G280" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/VIC_historical_prices.xlsx
+++ b/outputs/VIC_historical_prices.xlsx
@@ -534,10 +534,10 @@
         <v>49.24</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>48.17</v>
+        <v>48.69</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>49.53</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="6">
@@ -553,10 +553,10 @@
         <v>73.42</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>65.93000000000001</v>
+        <v>66.73</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>75.56</v>
+        <v>76.48</v>
       </c>
     </row>
     <row r="7">
@@ -572,10 +572,10 @@
         <v>80.26000000000001</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>71.39</v>
+        <v>72.28</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>83.73999999999999</v>
+        <v>84.79000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -591,10 +591,10 @@
         <v>91.2</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>99.84999999999999</v>
+        <v>101.13</v>
       </c>
     </row>
     <row r="9">
@@ -610,10 +610,10 @@
         <v>93.42</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>93.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>111.75</v>
+        <v>113.19</v>
       </c>
     </row>
     <row r="10">
@@ -629,10 +629,10 @@
         <v>79.47</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>82.81999999999999</v>
+        <v>83.89</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>98.65000000000001</v>
+        <v>99.92</v>
       </c>
     </row>
     <row r="11">
@@ -648,10 +648,10 @@
         <v>73.86</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>78.58</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>96.90000000000001</v>
+        <v>98.16</v>
       </c>
     </row>
     <row r="13">
@@ -664,7 +664,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Real prices are in Jun 2026 dollars (latest published CPI quarter). The latest 3 month(s) have no CPI yet, so real = nominal there (flagged in Monthly Data).</t>
+          <t>Real prices are in Sep 2026 dollars (latest published CPI quarter).</t>
         </is>
       </c>
     </row>
@@ -741,10 +741,10 @@
         <v>33.07</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>47.9</v>
+        <v>48.52</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>61.83</v>
+        <v>62.63</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
       <c r="G2" s="7" t="inlineStr"/>
@@ -762,10 +762,10 @@
         <v>23.54</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>37.6</v>
+        <v>38.09</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>43.93</v>
+        <v>44.5</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
       <c r="G3" s="7" t="inlineStr"/>
@@ -783,10 +783,10 @@
         <v>25.18</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>38.61</v>
+        <v>39.11</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>46.9</v>
+        <v>47.51</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
       <c r="G4" s="7" t="inlineStr"/>
@@ -804,10 +804,10 @@
         <v>25.05</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>38.56</v>
+        <v>39.06</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>46.57</v>
+        <v>47.18</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
       <c r="G5" s="7" t="inlineStr"/>
@@ -825,10 +825,10 @@
         <v>25.87</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>39.31</v>
+        <v>39.82</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>48.02</v>
+        <v>48.64</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
       <c r="G6" s="7" t="inlineStr"/>
@@ -846,10 +846,10 @@
         <v>33.9</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>46.26</v>
+        <v>46.87</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>62.81</v>
+        <v>63.63</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
       <c r="G7" s="7" t="inlineStr"/>
@@ -867,10 +867,10 @@
         <v>30.13</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>41.6</v>
+        <v>42.14</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>55.66</v>
+        <v>56.38</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr"/>
@@ -888,10 +888,10 @@
         <v>48.3</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>71.13</v>
+        <v>72.06</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>88.95999999999999</v>
+        <v>90.12</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
@@ -909,10 +909,10 @@
         <v>28.1</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>39.45</v>
+        <v>39.96</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>51.6</v>
+        <v>52.28</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
       <c r="G10" s="7" t="inlineStr"/>
@@ -930,10 +930,10 @@
         <v>36.91</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>54.02</v>
+        <v>54.72</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>67.68000000000001</v>
+        <v>68.56</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr"/>
@@ -951,10 +951,10 @@
         <v>39.52</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>57.29</v>
+        <v>58.03</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>72.34999999999999</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
       <c r="G12" s="7" t="inlineStr"/>
@@ -972,10 +972,10 @@
         <v>34.78</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>52.33</v>
+        <v>53.01</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>63.58</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
@@ -993,10 +993,10 @@
         <v>43.74</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>57.26</v>
+        <v>58.01</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>79.84</v>
+        <v>80.88</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
       <c r="G14" s="7" t="inlineStr"/>
@@ -1014,10 +1014,10 @@
         <v>27.28</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>41.11</v>
+        <v>41.64</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>49.73</v>
+        <v>50.38</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         <v>31.28</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>49.52</v>
+        <v>50.16</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>56.94</v>
+        <v>57.68</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
       <c r="G16" s="7" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         <v>70.44</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>81.48999999999999</v>
+        <v>82.55</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>127.91</v>
+        <v>129.57</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr"/>
@@ -1077,10 +1077,10 @@
         <v>43.97</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>64.59</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>79.64</v>
+        <v>80.67</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
       <c r="G18" s="7" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         <v>32.66</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>49.43</v>
+        <v>50.07</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>59</v>
+        <v>59.77</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr"/>
@@ -1119,10 +1119,10 @@
         <v>29.7</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>41.17</v>
+        <v>41.71</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>53.54</v>
+        <v>54.23</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
       <c r="G20" s="7" t="inlineStr"/>
@@ -1140,10 +1140,10 @@
         <v>27.12</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>39.26</v>
+        <v>39.77</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>48.78</v>
+        <v>49.41</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
       <c r="G21" s="7" t="inlineStr"/>
@@ -1161,10 +1161,10 @@
         <v>20.94</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>33.56</v>
+        <v>34</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>37.58</v>
+        <v>38.07</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
       <c r="G22" s="7" t="inlineStr"/>
@@ -1182,10 +1182,10 @@
         <v>37.71</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>54.86</v>
+        <v>55.57</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>67.54000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
       <c r="G23" s="7" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         <v>29</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>43.9</v>
+        <v>44.47</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>51.84</v>
+        <v>52.51</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
       <c r="G24" s="7" t="inlineStr"/>
@@ -1224,10 +1224,10 @@
         <v>27.23</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>41.99</v>
+        <v>42.54</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>48.58</v>
+        <v>49.21</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
       <c r="G25" s="7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         <v>32.3</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>47.14</v>
+        <v>47.75</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>57.43</v>
+        <v>58.18</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
       <c r="G26" s="7" t="inlineStr"/>
@@ -1266,10 +1266,10 @@
         <v>40.15</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>53.17</v>
+        <v>53.86</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>71.15000000000001</v>
+        <v>72.08</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
       <c r="G27" s="7" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
         <v>37.3</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>51.47</v>
+        <v>52.14</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>65.89</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
       <c r="G28" s="7" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         <v>28.44</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>39.92</v>
+        <v>40.44</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>50.15</v>
+        <v>50.8</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
       <c r="G29" s="7" t="inlineStr"/>
@@ -1329,10 +1329,10 @@
         <v>46.09</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>54.04</v>
+        <v>54.74</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>81.13</v>
+        <v>82.19</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
       <c r="G30" s="7" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         <v>49.13</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>60.17</v>
+        <v>60.95</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>86.34</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
       <c r="G31" s="7" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         <v>88.39</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>93.64</v>
+        <v>94.86</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>154.88</v>
+        <v>156.9</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
       <c r="G32" s="7" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         <v>105.26</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>97.84999999999999</v>
+        <v>99.12</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>183.92</v>
+        <v>186.31</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
       <c r="G33" s="7" t="inlineStr"/>
@@ -1413,10 +1413,10 @@
         <v>29.05</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>40.7</v>
+        <v>41.23</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>50.61</v>
+        <v>51.27</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
       <c r="G34" s="7" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         <v>27.89</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>39.15</v>
+        <v>39.66</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>48.34</v>
+        <v>48.97</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
       <c r="G35" s="7" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         <v>37.92</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>48.71</v>
+        <v>49.34</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>65.38</v>
+        <v>66.23</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
       <c r="G36" s="7" t="inlineStr"/>
@@ -1476,10 +1476,10 @@
         <v>42.6</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>59.36</v>
+        <v>60.13</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>73.06999999999999</v>
+        <v>74.02</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
       <c r="G37" s="7" t="inlineStr"/>
@@ -1497,10 +1497,10 @@
         <v>71.95</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>80.72</v>
+        <v>81.77</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>123.04</v>
+        <v>124.64</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
       <c r="G38" s="7" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         <v>38.93</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>54.92</v>
+        <v>55.63</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>66.38</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
       <c r="G39" s="7" t="inlineStr"/>
@@ -1539,10 +1539,10 @@
         <v>38.74</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>52.36</v>
+        <v>53.04</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>65.86</v>
+        <v>66.72</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
       <c r="G40" s="7" t="inlineStr"/>
@@ -1560,10 +1560,10 @@
         <v>34.58</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>47.04</v>
+        <v>47.65</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>58.81</v>
+        <v>59.58</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
       <c r="G41" s="7" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         <v>42.04</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>55.65</v>
+        <v>56.38</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>71.53</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
       <c r="G42" s="7" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         <v>28.05</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>37.92</v>
+        <v>38.41</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>47.74</v>
+        <v>48.36</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
       <c r="G43" s="7" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         <v>165.27</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>155.63</v>
+        <v>157.65</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>281.22</v>
+        <v>284.87</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
       <c r="G44" s="7" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         <v>68.56999999999999</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>80.7</v>
+        <v>81.75</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>116.64</v>
+        <v>118.16</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
       <c r="G45" s="7" t="inlineStr"/>
@@ -1665,10 +1665,10 @@
         <v>74.37</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>90.61</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>126.48</v>
+        <v>128.12</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
       <c r="G46" s="7" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         <v>80.98999999999999</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>114.76</v>
+        <v>116.26</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>137.17</v>
+        <v>138.95</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
       <c r="G47" s="7" t="inlineStr"/>
@@ -1707,10 +1707,10 @@
         <v>74.97</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>105.66</v>
+        <v>107.03</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>126.46</v>
+        <v>128.1</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
       <c r="G48" s="7" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         <v>218.49</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>240.71</v>
+        <v>243.83</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>367.06</v>
+        <v>371.83</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
       <c r="G49" s="7" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         <v>114.96</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>143.39</v>
+        <v>145.26</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>192.69</v>
+        <v>195.19</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
       <c r="G50" s="7" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         <v>50.52</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>69.78</v>
+        <v>70.69</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>84.48</v>
+        <v>85.58</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
       <c r="G51" s="7" t="inlineStr"/>
@@ -1791,10 +1791,10 @@
         <v>54.66</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>74.38</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>91.2</v>
+        <v>92.38</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
       <c r="G52" s="7" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         <v>45.03</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>59.06</v>
+        <v>59.83</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>74.90000000000001</v>
+        <v>75.87</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
       <c r="G53" s="7" t="inlineStr"/>
@@ -1833,10 +1833,10 @@
         <v>53.86</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>70.84999999999999</v>
+        <v>71.78</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>89.31</v>
+        <v>90.47</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
       <c r="G54" s="7" t="inlineStr"/>
@@ -1854,10 +1854,10 @@
         <v>61.74</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>74.04000000000001</v>
+        <v>75</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>102.06</v>
+        <v>103.39</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
       <c r="G55" s="7" t="inlineStr"/>
@@ -1875,10 +1875,10 @@
         <v>54.78</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>66.44</v>
+        <v>67.3</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>90.15000000000001</v>
+        <v>91.33</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
       <c r="G56" s="7" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         <v>51.53</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>60.43</v>
+        <v>61.21</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>84.43000000000001</v>
+        <v>85.53</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
       <c r="G57" s="7" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         <v>84.09999999999999</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>85.05</v>
+        <v>86.16</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>137.19</v>
+        <v>138.97</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
       <c r="G58" s="7" t="inlineStr"/>
@@ -1938,10 +1938,10 @@
         <v>49.7</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>64.70999999999999</v>
+        <v>65.55</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>80.68000000000001</v>
+        <v>81.73</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
       <c r="G59" s="7" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         <v>63.89</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>87.29000000000001</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>103.22</v>
+        <v>104.56</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
       <c r="G60" s="7" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         <v>51.98</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>67.59999999999999</v>
+        <v>68.47</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>83.58</v>
+        <v>84.66</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
       <c r="G61" s="7" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         <v>60.1</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>68.94</v>
+        <v>69.83</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>96.26000000000001</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
       <c r="G62" s="7" t="inlineStr"/>
@@ -2022,10 +2022,10 @@
         <v>50.49</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>65.27</v>
+        <v>66.12</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>80.56</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
       <c r="G63" s="7" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         <v>47.53</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>58.2</v>
+        <v>58.96</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>75.54000000000001</v>
+        <v>76.53</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
       <c r="G64" s="7" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         <v>50.87</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>62.64</v>
+        <v>63.46</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>80.94</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
       <c r="G65" s="7" t="inlineStr"/>
@@ -2085,10 +2085,10 @@
         <v>44.54</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>55.05</v>
+        <v>55.77</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>70.95</v>
+        <v>71.87</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
       <c r="G66" s="7" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         <v>27.59</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>35.86</v>
+        <v>36.33</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>44</v>
+        <v>44.57</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
       <c r="G67" s="7" t="inlineStr"/>
@@ -2127,10 +2127,10 @@
         <v>248.01</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>200.11</v>
+        <v>202.72</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>395.33</v>
+        <v>400.47</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
       <c r="G68" s="7" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         <v>44.12</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>53.22</v>
+        <v>53.91</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>70.3</v>
+        <v>71.22</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
       <c r="G69" s="7" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         <v>32.01</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>40.25</v>
+        <v>40.78</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>50.99</v>
+        <v>51.65</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
       <c r="G70" s="7" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         <v>48.96</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>59.32</v>
+        <v>60.09</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>77.86</v>
+        <v>78.87</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
       <c r="G71" s="7" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         <v>37.6</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>49.93</v>
+        <v>50.58</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>59.69</v>
+        <v>60.47</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
       <c r="G72" s="7" t="inlineStr"/>
@@ -2232,10 +2232,10 @@
         <v>37.07</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>47.66</v>
+        <v>48.28</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>58.75</v>
+        <v>59.52</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
       <c r="G73" s="7" t="inlineStr"/>
@@ -2253,10 +2253,10 @@
         <v>32.46</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>42.41</v>
+        <v>42.96</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>51.29</v>
+        <v>51.95</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
       <c r="G74" s="7" t="inlineStr"/>
@@ -2274,10 +2274,10 @@
         <v>27.81</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>35.34</v>
+        <v>35.8</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>43.8</v>
+        <v>44.37</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
       <c r="G75" s="7" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         <v>27.42</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>36.02</v>
+        <v>36.49</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>43.05</v>
+        <v>43.61</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
       <c r="G76" s="7" t="inlineStr"/>
@@ -2316,10 +2316,10 @@
         <v>30.83</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>40.06</v>
+        <v>40.58</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>48.32</v>
+        <v>48.95</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
       <c r="G77" s="7" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         <v>44.77</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>50.74</v>
+        <v>51.4</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>70.04000000000001</v>
+        <v>70.95</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
       <c r="G78" s="7" t="inlineStr"/>
@@ -2358,10 +2358,10 @@
         <v>29.38</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>36.72</v>
+        <v>37.19</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>45.88</v>
+        <v>46.48</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
       <c r="G79" s="7" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         <v>114.66</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>94.89</v>
+        <v>96.13</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>178.52</v>
+        <v>180.84</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
       <c r="G80" s="7" t="inlineStr"/>
@@ -2400,10 +2400,10 @@
         <v>123.77</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>105.4</v>
+        <v>106.77</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>192.1</v>
+        <v>194.6</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
       <c r="G81" s="7" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         <v>26.87</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>35.37</v>
+        <v>35.83</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>41.58</v>
+        <v>42.12</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
       <c r="G82" s="7" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         <v>131.27</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>110.5</v>
+        <v>111.94</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>202.71</v>
+        <v>205.35</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
       <c r="G83" s="7" t="inlineStr"/>
@@ -2463,10 +2463,10 @@
         <v>34.5</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>46.99</v>
+        <v>47.6</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>53.17</v>
+        <v>53.86</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
       <c r="G84" s="7" t="inlineStr"/>
@@ -2484,10 +2484,10 @@
         <v>36.24</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>48.29</v>
+        <v>48.92</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>55.74</v>
+        <v>56.46</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
       <c r="G85" s="7" t="inlineStr"/>
@@ -2505,10 +2505,10 @@
         <v>30.25</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>40.89</v>
+        <v>41.42</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>46.41</v>
+        <v>47.02</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
       <c r="G86" s="7" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         <v>30.63</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>41.4</v>
+        <v>41.94</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>46.88</v>
+        <v>47.49</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
       <c r="G87" s="7" t="inlineStr"/>
@@ -2547,10 +2547,10 @@
         <v>24.81</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>33.78</v>
+        <v>34.22</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>37.89</v>
+        <v>38.38</v>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
       <c r="G88" s="7" t="inlineStr"/>
@@ -2568,10 +2568,10 @@
         <v>24.32</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>31.75</v>
+        <v>32.16</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>37.09</v>
+        <v>37.57</v>
       </c>
       <c r="F89" s="7" t="inlineStr"/>
       <c r="G89" s="7" t="inlineStr"/>
@@ -2589,10 +2589,10 @@
         <v>20.74</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>28.06</v>
+        <v>28.42</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>31.59</v>
+        <v>32</v>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
       <c r="G90" s="7" t="inlineStr"/>
@@ -2610,10 +2610,10 @@
         <v>18.84</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>25.13</v>
+        <v>25.46</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>28.66</v>
+        <v>29.03</v>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
       <c r="G91" s="7" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         <v>65.90000000000001</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>62.15</v>
+        <v>62.96</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>99.73</v>
+        <v>101.02</v>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
       <c r="G92" s="7" t="inlineStr"/>
@@ -2652,10 +2652,10 @@
         <v>59.12</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>60.92</v>
+        <v>61.71</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>89.01000000000001</v>
+        <v>90.17</v>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
       <c r="G93" s="7" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         <v>28.33</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>37.39</v>
+        <v>37.87</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>42.44</v>
+        <v>42.99</v>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
       <c r="G94" s="7" t="inlineStr"/>
@@ -2694,10 +2694,10 @@
         <v>28.26</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>38.23</v>
+        <v>38.73</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>42.2</v>
+        <v>42.75</v>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
       <c r="G95" s="7" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         <v>40.34</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>51.14</v>
+        <v>51.8</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>60.06</v>
+        <v>60.84</v>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
       <c r="G96" s="7" t="inlineStr"/>
@@ -2736,10 +2736,10 @@
         <v>33.79</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>41.44</v>
+        <v>41.98</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>50.15</v>
+        <v>50.81</v>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
       <c r="G97" s="7" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         <v>37.74</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>43.68</v>
+        <v>44.25</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>55.91</v>
+        <v>56.63</v>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
       <c r="G98" s="7" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         <v>35.21</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>44.28</v>
+        <v>44.85</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>52.05</v>
+        <v>52.73</v>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
       <c r="G99" s="7" t="inlineStr"/>
@@ -2799,10 +2799,10 @@
         <v>31.48</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>39.81</v>
+        <v>40.33</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>46.45</v>
+        <v>47.05</v>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
       <c r="G100" s="7" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         <v>28.55</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>34.84</v>
+        <v>35.29</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>42.13</v>
+        <v>42.67</v>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
       <c r="G101" s="7" t="inlineStr"/>
@@ -2841,10 +2841,10 @@
         <v>30.42</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>39.22</v>
+        <v>39.73</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>44.88</v>
+        <v>45.47</v>
       </c>
       <c r="F102" s="7" t="inlineStr"/>
       <c r="G102" s="7" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         <v>25.43</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>32.73</v>
+        <v>33.15</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>37.52</v>
+        <v>38.01</v>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
       <c r="G103" s="7" t="inlineStr"/>
@@ -2883,10 +2883,10 @@
         <v>28.96</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>35.45</v>
+        <v>35.91</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>42.72</v>
+        <v>43.28</v>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
       <c r="G104" s="7" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         <v>29.72</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>38.13</v>
+        <v>38.62</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>43.83</v>
+        <v>44.4</v>
       </c>
       <c r="F105" s="7" t="inlineStr"/>
       <c r="G105" s="7" t="inlineStr"/>
@@ -2925,10 +2925,10 @@
         <v>27.57</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>34.95</v>
+        <v>35.4</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>40.66</v>
+        <v>41.18</v>
       </c>
       <c r="F106" s="7" t="inlineStr"/>
       <c r="G106" s="7" t="inlineStr"/>
@@ -2946,10 +2946,10 @@
         <v>36.22</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>47.12</v>
+        <v>47.73</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>53.32</v>
+        <v>54.01</v>
       </c>
       <c r="F107" s="7" t="inlineStr"/>
       <c r="G107" s="7" t="inlineStr"/>
@@ -2967,10 +2967,10 @@
         <v>30.09</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>39.06</v>
+        <v>39.57</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>44.22</v>
+        <v>44.79</v>
       </c>
       <c r="F108" s="7" t="inlineStr"/>
       <c r="G108" s="7" t="inlineStr"/>
@@ -2988,10 +2988,10 @@
         <v>42.49</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>53.91</v>
+        <v>54.61</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>62.33</v>
+        <v>63.14</v>
       </c>
       <c r="F109" s="7" t="inlineStr"/>
       <c r="G109" s="7" t="inlineStr"/>
@@ -3009,10 +3009,10 @@
         <v>89.70999999999999</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>107.28</v>
+        <v>108.67</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>131.01</v>
+        <v>132.71</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -3034,10 +3034,10 @@
         <v>58.42</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>81.06</v>
+        <v>82.12</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>84.93000000000001</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
         <v>60.79</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>77.40000000000001</v>
+        <v>78.41</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>87.98</v>
+        <v>89.13</v>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         <v>54.54</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>74.14</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>78.87</v>
+        <v>79.89</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
@@ -3109,10 +3109,10 @@
         <v>108.42</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>111.51</v>
+        <v>112.96</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>156.65</v>
+        <v>158.69</v>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
@@ -3134,10 +3134,10 @@
         <v>58.79</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>75.33</v>
+        <v>76.31</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>84.87</v>
+        <v>85.97</v>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
@@ -3159,10 +3159,10 @@
         <v>65.27</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>78.26000000000001</v>
+        <v>79.27</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>94.12</v>
+        <v>95.34</v>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
@@ -3184,10 +3184,10 @@
         <v>59.25</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>77.19</v>
+        <v>78.19</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>85.34</v>
+        <v>86.45</v>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
@@ -3209,10 +3209,10 @@
         <v>59.68</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>75.26000000000001</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="E118" s="9" t="n">
-        <v>85.87</v>
+        <v>86.98</v>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
@@ -3234,10 +3234,10 @@
         <v>53.14</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>71.88</v>
+        <v>72.81</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>76.36</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
@@ -3259,10 +3259,10 @@
         <v>60.42</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>78.72</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>86.70999999999999</v>
+        <v>87.84</v>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
@@ -3284,10 +3284,10 @@
         <v>70.08</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>87.29000000000001</v>
+        <v>88.42</v>
       </c>
       <c r="E121" s="9" t="n">
-        <v>100.45</v>
+        <v>101.75</v>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
@@ -3309,10 +3309,10 @@
         <v>61.74</v>
       </c>
       <c r="D122" s="9" t="n">
-        <v>83.3</v>
+        <v>84.38</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>88.13</v>
+        <v>89.28</v>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
@@ -3334,10 +3334,10 @@
         <v>57.53</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>76.95</v>
+        <v>77.95</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>81.79000000000001</v>
+        <v>82.86</v>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
@@ -3359,10 +3359,10 @@
         <v>51.96</v>
       </c>
       <c r="D124" s="9" t="n">
-        <v>69.73999999999999</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>73.58</v>
+        <v>74.53</v>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
@@ -3384,10 +3384,10 @@
         <v>51.51</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>69.88</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>72.77</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
@@ -3409,10 +3409,10 @@
         <v>49.21</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>65.90000000000001</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>69.34999999999999</v>
+        <v>70.25</v>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
@@ -3434,10 +3434,10 @@
         <v>57.33</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>70.76000000000001</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>80.59999999999999</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
@@ -3459,10 +3459,10 @@
         <v>105.36</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>101.63</v>
+        <v>102.95</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>147.84</v>
+        <v>149.76</v>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
@@ -3484,10 +3484,10 @@
         <v>51.23</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>68.97</v>
+        <v>69.87</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>71.73999999999999</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
         <v>50.43</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>64.23999999999999</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>70.48</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
@@ -3534,10 +3534,10 @@
         <v>46.35</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>61.1</v>
+        <v>61.9</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>64.67</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
@@ -3559,10 +3559,10 @@
         <v>53.06</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>67.14</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>73.91</v>
+        <v>74.87</v>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
         <v>53.86</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>68.38</v>
+        <v>69.27</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>74.90000000000001</v>
+        <v>75.87</v>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
@@ -3609,10 +3609,10 @@
         <v>43.59</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>53.59</v>
+        <v>54.29</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>60.53</v>
+        <v>61.32</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
       <c r="G134" s="7" t="inlineStr"/>
@@ -3630,10 +3630,10 @@
         <v>40.37</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>47.86</v>
+        <v>48.48</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>55.98</v>
+        <v>56.71</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
       <c r="G135" s="7" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         <v>41.59</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>50.21</v>
+        <v>50.87</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>57.59</v>
+        <v>58.34</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
       <c r="G136" s="7" t="inlineStr"/>
@@ -3672,10 +3672,10 @@
         <v>30.36</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>36.8</v>
+        <v>37.28</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>42.02</v>
+        <v>42.56</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
       <c r="G137" s="7" t="inlineStr"/>
@@ -3693,10 +3693,10 @@
         <v>34.02</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>39.5</v>
+        <v>40.01</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>47.05</v>
+        <v>47.66</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
       <c r="G138" s="7" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         <v>31.02</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>36.68</v>
+        <v>37.16</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>42.88</v>
+        <v>43.43</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
       <c r="G139" s="7" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         <v>33.35</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>36.05</v>
+        <v>36.52</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>46.07</v>
+        <v>46.67</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
       <c r="G140" s="7" t="inlineStr"/>
@@ -3756,10 +3756,10 @@
         <v>34.67</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>38.69</v>
+        <v>39.2</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>47.86</v>
+        <v>48.48</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
       <c r="G141" s="7" t="inlineStr"/>
@@ -3777,10 +3777,10 @@
         <v>30.8</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>35.61</v>
+        <v>36.07</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>42.49</v>
+        <v>43.04</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
       <c r="G142" s="7" t="inlineStr"/>
@@ -3798,10 +3798,10 @@
         <v>34.91</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>39.79</v>
+        <v>40.31</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>48.05</v>
+        <v>48.67</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
       <c r="G143" s="7" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         <v>38.04</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>40.99</v>
+        <v>41.52</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>52.23</v>
+        <v>52.91</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
       <c r="G144" s="7" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         <v>40.94</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>47.13</v>
+        <v>47.75</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>56.08</v>
+        <v>56.81</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
       <c r="G145" s="7" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         <v>42.4</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>47.54</v>
+        <v>48.16</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>58</v>
+        <v>58.76</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
       <c r="G146" s="7" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         <v>41.42</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>47.87</v>
+        <v>48.5</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>56.59</v>
+        <v>57.33</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
       <c r="G147" s="7" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
         <v>50.53</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>60.79</v>
+        <v>61.58</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>68.95</v>
+        <v>69.84</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
       <c r="G148" s="7" t="inlineStr"/>
@@ -3924,10 +3924,10 @@
         <v>44.46</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>48.55</v>
+        <v>49.19</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>60.59</v>
+        <v>61.38</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
       <c r="G149" s="7" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         <v>44.68</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>47.53</v>
+        <v>48.14</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>60.81</v>
+        <v>61.6</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
       <c r="G150" s="7" t="inlineStr"/>
@@ -3966,10 +3966,10 @@
         <v>61.92</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>65.26000000000001</v>
+        <v>66.11</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>84.16</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
       <c r="G151" s="7" t="inlineStr"/>
@@ -3987,10 +3987,10 @@
         <v>72.53</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>63.86</v>
+        <v>64.69</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>98.65000000000001</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
       <c r="G152" s="7" t="inlineStr"/>
@@ -4008,10 +4008,10 @@
         <v>43.88</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>48.21</v>
+        <v>48.84</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>59.72</v>
+        <v>60.5</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
       <c r="G153" s="7" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         <v>58.3</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>62.5</v>
+        <v>63.31</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>79.40000000000001</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
       <c r="G154" s="7" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         <v>59.14</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>62.4</v>
+        <v>63.21</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>80.43000000000001</v>
+        <v>81.47</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
       <c r="G155" s="7" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         <v>73.56999999999999</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>73.66</v>
+        <v>74.61</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>99.91</v>
+        <v>101.21</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
       <c r="G156" s="7" t="inlineStr"/>
@@ -4092,10 +4092,10 @@
         <v>114.45</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>125.8</v>
+        <v>127.43</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>155.19</v>
+        <v>157.21</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
       <c r="G157" s="7" t="inlineStr"/>
@@ -4113,10 +4113,10 @@
         <v>84.48999999999999</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>87.45</v>
+        <v>88.58</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>114.3</v>
+        <v>115.79</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
       <c r="G158" s="7" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         <v>53.5</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>58.36</v>
+        <v>59.12</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>72.20999999999999</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
       <c r="G159" s="7" t="inlineStr"/>
@@ -4155,10 +4155,10 @@
         <v>47.59</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>55.24</v>
+        <v>55.95</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>64.08</v>
+        <v>64.91</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
       <c r="G160" s="7" t="inlineStr"/>
@@ -4176,10 +4176,10 @@
         <v>38.38</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>44.6</v>
+        <v>45.18</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>51.59</v>
+        <v>52.26</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
       <c r="G161" s="7" t="inlineStr"/>
@@ -4197,10 +4197,10 @@
         <v>45.05</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>48.4</v>
+        <v>49.03</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>60.45</v>
+        <v>61.24</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
       <c r="G162" s="7" t="inlineStr"/>
@@ -4218,10 +4218,10 @@
         <v>37.06</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>40.05</v>
+        <v>40.57</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>49.64</v>
+        <v>50.29</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
       <c r="G163" s="7" t="inlineStr"/>
@@ -4239,10 +4239,10 @@
         <v>80.27</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>82.98</v>
+        <v>84.05</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>107.36</v>
+        <v>108.75</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
       <c r="G164" s="7" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         <v>111.69</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>114.91</v>
+        <v>116.41</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>149.15</v>
+        <v>151.09</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
       <c r="G165" s="7" t="inlineStr"/>
@@ -4281,10 +4281,10 @@
         <v>110.35</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>120.84</v>
+        <v>122.41</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>147.14</v>
+        <v>149.05</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
       <c r="G166" s="7" t="inlineStr"/>
@@ -4302,10 +4302,10 @@
         <v>121.78</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>144.18</v>
+        <v>146.05</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>162.27</v>
+        <v>164.38</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
       <c r="G167" s="7" t="inlineStr"/>
@@ -4323,10 +4323,10 @@
         <v>121.22</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>143.75</v>
+        <v>145.62</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>161.42</v>
+        <v>163.52</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
       <c r="G168" s="7" t="inlineStr"/>
@@ -4344,10 +4344,10 @@
         <v>103.65</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>131.08</v>
+        <v>132.79</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>137.93</v>
+        <v>139.73</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
       <c r="G169" s="7" t="inlineStr"/>
@@ -4365,10 +4365,10 @@
         <v>129.67</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>155.89</v>
+        <v>157.92</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>172.21</v>
+        <v>174.45</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
       <c r="G170" s="7" t="inlineStr"/>
@@ -4386,10 +4386,10 @@
         <v>116.97</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>135.94</v>
+        <v>137.71</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>155.03</v>
+        <v>157.04</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
       <c r="G171" s="7" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>105.06</v>
+        <v>106.43</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>117.85</v>
+        <v>119.38</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
       <c r="G172" s="7" t="inlineStr"/>
@@ -4428,10 +4428,10 @@
         <v>81.72</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>96.75</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>107.85</v>
+        <v>109.25</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
       <c r="G173" s="7" t="inlineStr"/>
@@ -4449,10 +4449,10 @@
         <v>111.45</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>125.81</v>
+        <v>127.44</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>146.76</v>
+        <v>148.66</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
       <c r="G174" s="7" t="inlineStr"/>
@@ -4470,10 +4470,10 @@
         <v>97.2</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>111.48</v>
+        <v>112.93</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>127.71</v>
+        <v>129.37</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
       <c r="G175" s="7" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         <v>182.54</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>175.12</v>
+        <v>177.4</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>239.48</v>
+        <v>242.6</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
       <c r="G176" s="7" t="inlineStr"/>
@@ -4512,10 +4512,10 @@
         <v>123.66</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>127.64</v>
+        <v>129.3</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>162</v>
+        <v>164.11</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
       <c r="G177" s="7" t="inlineStr"/>
@@ -4533,10 +4533,10 @@
         <v>81.45999999999999</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>99.43000000000001</v>
+        <v>100.72</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>106.56</v>
+        <v>107.95</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
       <c r="G178" s="7" t="inlineStr"/>
@@ -4554,10 +4554,10 @@
         <v>86.12</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>96.73999999999999</v>
+        <v>98</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>112.52</v>
+        <v>113.99</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
       <c r="G179" s="7" t="inlineStr"/>
@@ -4575,10 +4575,10 @@
         <v>93.45</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>104.13</v>
+        <v>105.48</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>121.96</v>
+        <v>123.54</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
       <c r="G180" s="7" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         <v>109.8</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>122.16</v>
+        <v>123.75</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>143.12</v>
+        <v>144.98</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
       <c r="G181" s="7" t="inlineStr"/>
@@ -4617,10 +4617,10 @@
         <v>86.86</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>91.23999999999999</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>113.06</v>
+        <v>114.53</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
       <c r="G182" s="7" t="inlineStr"/>
@@ -4638,10 +4638,10 @@
         <v>100.32</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>102.9</v>
+        <v>104.24</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>130.39</v>
+        <v>132.08</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
       <c r="G183" s="7" t="inlineStr"/>
@@ -4659,10 +4659,10 @@
         <v>106.94</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>120.51</v>
+        <v>122.07</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>138.79</v>
+        <v>140.6</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
       <c r="G184" s="7" t="inlineStr"/>
@@ -4680,10 +4680,10 @@
         <v>108.4</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>129.34</v>
+        <v>131.02</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>140.44</v>
+        <v>142.27</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
       <c r="G185" s="7" t="inlineStr"/>
@@ -4701,10 +4701,10 @@
         <v>104.23</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>126.54</v>
+        <v>128.19</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>134.81</v>
+        <v>136.56</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
       <c r="G186" s="7" t="inlineStr"/>
@@ -4722,10 +4722,10 @@
         <v>113.57</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>118.51</v>
+        <v>120.05</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>146.63</v>
+        <v>148.54</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
       <c r="G187" s="7" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         <v>421.41</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>323.22</v>
+        <v>327.43</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>544.12</v>
+        <v>551.2</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
       <c r="G188" s="7" t="inlineStr"/>
@@ -4764,10 +4764,10 @@
         <v>119.46</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>143.54</v>
+        <v>145.4</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>154.25</v>
+        <v>156.26</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
       <c r="G189" s="7" t="inlineStr"/>
@@ -4785,10 +4785,10 @@
         <v>176.04</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>169.3</v>
+        <v>171.5</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>227.32</v>
+        <v>230.28</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
       <c r="G190" s="7" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         <v>105.41</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>126.87</v>
+        <v>128.51</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>135.85</v>
+        <v>137.61</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
       <c r="G191" s="7" t="inlineStr"/>
@@ -4827,10 +4827,10 @@
         <v>103.35</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>118.2</v>
+        <v>119.74</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>132.93</v>
+        <v>134.66</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
       <c r="G192" s="7" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         <v>120.77</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>130.69</v>
+        <v>132.39</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>155.03</v>
+        <v>157.05</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
       <c r="G193" s="7" t="inlineStr"/>
@@ -4869,10 +4869,10 @@
         <v>104.22</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>110.09</v>
+        <v>111.52</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>133.53</v>
+        <v>135.27</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
       <c r="G194" s="7" t="inlineStr"/>
@@ -4890,10 +4890,10 @@
         <v>128.34</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>134.22</v>
+        <v>135.96</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>164.13</v>
+        <v>166.26</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
       <c r="G195" s="7" t="inlineStr"/>
@@ -4911,10 +4911,10 @@
         <v>119.12</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>133.72</v>
+        <v>135.46</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>152.05</v>
+        <v>154.03</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
       <c r="G196" s="7" t="inlineStr"/>
@@ -4932,10 +4932,10 @@
         <v>110.98</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>128.25</v>
+        <v>129.92</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>141.34</v>
+        <v>143.18</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
       <c r="G197" s="7" t="inlineStr"/>
@@ -4953,10 +4953,10 @@
         <v>68.72</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>86.38</v>
+        <v>87.5</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>87.31999999999999</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
       <c r="G198" s="7" t="inlineStr"/>
@@ -4974,10 +4974,10 @@
         <v>77.23999999999999</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>77.83</v>
+        <v>78.84</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>97.92</v>
+        <v>99.2</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
       <c r="G199" s="7" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         <v>255.49</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>181.01</v>
+        <v>183.36</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>323.5</v>
+        <v>327.71</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
       <c r="G200" s="7" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         <v>55.07</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>61.1</v>
+        <v>61.89</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>69.64</v>
+        <v>70.55</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
       <c r="G201" s="7" t="inlineStr"/>
@@ -5037,10 +5037,10 @@
         <v>49.68</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>54.69</v>
+        <v>55.4</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>62.75</v>
+        <v>63.57</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
       <c r="G202" s="7" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         <v>41.8</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>44.28</v>
+        <v>44.85</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>53.14</v>
+        <v>53.83</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
       <c r="G203" s="7" t="inlineStr"/>
@@ -5079,10 +5079,10 @@
         <v>46.68</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>48.99</v>
+        <v>49.63</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>59.73</v>
+        <v>60.5</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
       <c r="G204" s="7" t="inlineStr"/>
@@ -5100,10 +5100,10 @@
         <v>62.5</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>62.67</v>
+        <v>63.48</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>80.48999999999999</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
       <c r="G205" s="7" t="inlineStr"/>
@@ -5121,10 +5121,10 @@
         <v>74.52</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>81.48999999999999</v>
+        <v>82.55</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>95.48</v>
+        <v>96.72</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
       <c r="G206" s="7" t="inlineStr"/>
@@ -5142,10 +5142,10 @@
         <v>65.59999999999999</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>68.45</v>
+        <v>69.34</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>83.62</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
       <c r="G207" s="7" t="inlineStr"/>
@@ -5163,10 +5163,10 @@
         <v>38.68</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>43.94</v>
+        <v>44.52</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>49.06</v>
+        <v>49.69</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
       <c r="G208" s="7" t="inlineStr"/>
@@ -5184,10 +5184,10 @@
         <v>53.68</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>56.63</v>
+        <v>57.37</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>67.88</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
       <c r="G209" s="7" t="inlineStr"/>
@@ -5205,10 +5205,10 @@
         <v>49.58</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>55.56</v>
+        <v>56.28</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>62.5</v>
+        <v>63.32</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
       <c r="G210" s="7" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
         <v>23.43</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>29.9</v>
+        <v>30.29</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>29.45</v>
+        <v>29.83</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
       <c r="G211" s="7" t="inlineStr"/>
@@ -5247,10 +5247,10 @@
         <v>20.66</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>28.63</v>
+        <v>29</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>25.92</v>
+        <v>26.25</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
       <c r="G212" s="7" t="inlineStr"/>
@@ -5268,10 +5268,10 @@
         <v>24.62</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>27.36</v>
+        <v>27.71</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>30.83</v>
+        <v>31.23</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
       <c r="G213" s="7" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         <v>31.29</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>37.94</v>
+        <v>38.43</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>39.1</v>
+        <v>39.61</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
       <c r="G214" s="7" t="inlineStr"/>
@@ -5310,10 +5310,10 @@
         <v>60.46</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>61.67</v>
+        <v>62.47</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>75.37</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
       <c r="G215" s="7" t="inlineStr"/>
@@ -5331,10 +5331,10 @@
         <v>113.74</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>90.58</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>141.45</v>
+        <v>143.28</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
       <c r="G216" s="7" t="inlineStr"/>
@@ -5352,10 +5352,10 @@
         <v>107.34</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>109.07</v>
+        <v>110.49</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>133.16</v>
+        <v>134.89</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
       <c r="G217" s="7" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         <v>127.01</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>113.46</v>
+        <v>114.94</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>157.12</v>
+        <v>159.16</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
       <c r="G218" s="7" t="inlineStr"/>
@@ -5394,10 +5394,10 @@
         <v>54.92</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>57.98</v>
+        <v>58.73</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>67.75</v>
+        <v>68.63</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
       <c r="G219" s="7" t="inlineStr"/>
@@ -5415,10 +5415,10 @@
         <v>33.28</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>34.1</v>
+        <v>34.54</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>40.94</v>
+        <v>41.47</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
       <c r="G220" s="7" t="inlineStr"/>
@@ -5436,10 +5436,10 @@
         <v>15.04</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>22.61</v>
+        <v>22.91</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>18.42</v>
+        <v>18.66</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
       <c r="G221" s="7" t="inlineStr"/>
@@ -5457,10 +5457,10 @@
         <v>40.75</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>42.72</v>
+        <v>43.27</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>49.71</v>
+        <v>50.35</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
       <c r="G222" s="7" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         <v>30.93</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>39.15</v>
+        <v>39.66</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>37.57</v>
+        <v>38.06</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
       <c r="G223" s="7" t="inlineStr"/>
@@ -5499,10 +5499,10 @@
         <v>75.05</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>73.34999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>90.51000000000001</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
       <c r="G224" s="7" t="inlineStr"/>
@@ -5520,10 +5520,10 @@
         <v>48.46</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>64.86</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>58.03</v>
+        <v>58.78</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
       <c r="G225" s="7" t="inlineStr"/>
@@ -5541,10 +5541,10 @@
         <v>56.21</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>65.13</v>
+        <v>65.98</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>66.83</v>
+        <v>67.7</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
       <c r="G226" s="7" t="inlineStr"/>
@@ -5562,10 +5562,10 @@
         <v>167.79</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>167.25</v>
+        <v>169.43</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>198.31</v>
+        <v>200.89</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
       <c r="G227" s="7" t="inlineStr"/>
@@ -5583,10 +5583,10 @@
         <v>264.05</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>274.51</v>
+        <v>278.08</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>310.24</v>
+        <v>314.28</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
       <c r="G228" s="7" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         <v>375.27</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>346.32</v>
+        <v>350.82</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>438.34</v>
+        <v>444.03</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
       <c r="G229" s="7" t="inlineStr"/>
@@ -5625,10 +5625,10 @@
         <v>431.21</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>395.12</v>
+        <v>400.25</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>500.61</v>
+        <v>507.12</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
       <c r="G230" s="7" t="inlineStr"/>
@@ -5646,10 +5646,10 @@
         <v>136.75</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>139.64</v>
+        <v>141.45</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>157.8</v>
+        <v>159.85</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
       <c r="G231" s="7" t="inlineStr"/>
@@ -5667,10 +5667,10 @@
         <v>130.63</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>128.2</v>
+        <v>129.86</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>149.83</v>
+        <v>151.78</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
       <c r="G232" s="7" t="inlineStr"/>
@@ -5688,10 +5688,10 @@
         <v>96.98999999999999</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>112.74</v>
+        <v>114.21</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>110.56</v>
+        <v>112</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
       <c r="G233" s="7" t="inlineStr"/>
@@ -5709,10 +5709,10 @@
         <v>58.52</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>66.43000000000001</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>66.3</v>
+        <v>67.17</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
       <c r="G234" s="7" t="inlineStr"/>
@@ -5730,10 +5730,10 @@
         <v>11.86</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>35.23</v>
+        <v>35.68</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>13.36</v>
+        <v>13.53</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
       <c r="G235" s="7" t="inlineStr"/>
@@ -5751,10 +5751,10 @@
         <v>32.16</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>53.91</v>
+        <v>54.61</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>36.05</v>
+        <v>36.52</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
       <c r="G236" s="7" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         <v>55.28</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>64.73999999999999</v>
+        <v>65.58</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>61.7</v>
+        <v>62.5</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
       <c r="G237" s="7" t="inlineStr"/>
@@ -5793,10 +5793,10 @@
         <v>54.34</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>68.91</v>
+        <v>69.81</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>60.38</v>
+        <v>61.16</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
       <c r="G238" s="7" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         <v>86.66</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>92.65000000000001</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>96.01000000000001</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
       <c r="G239" s="7" t="inlineStr"/>
@@ -5835,10 +5835,10 @@
         <v>145.34</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>140.47</v>
+        <v>142.3</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>160.57</v>
+        <v>162.66</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
       <c r="G240" s="7" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         <v>85.58</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>60.07</v>
+        <v>60.85</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>94.28</v>
+        <v>95.5</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
       <c r="G241" s="7" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         <v>75.97</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>60.59</v>
+        <v>61.38</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>83.37</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
       <c r="G242" s="7" t="inlineStr"/>
@@ -5898,10 +5898,10 @@
         <v>79.54000000000001</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>70.69</v>
+        <v>71.61</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>86.95999999999999</v>
+        <v>88.09</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
       <c r="G243" s="7" t="inlineStr"/>
@@ -5919,10 +5919,10 @@
         <v>28.25</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>28.65</v>
+        <v>29.03</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>30.77</v>
+        <v>31.17</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
       <c r="G244" s="7" t="inlineStr"/>
@@ -5940,10 +5940,10 @@
         <v>15.18</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>18.68</v>
+        <v>18.93</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>16.5</v>
+        <v>16.71</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
       <c r="G245" s="7" t="inlineStr"/>
@@ -5961,10 +5961,10 @@
         <v>31.91</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>37.89</v>
+        <v>38.39</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>34.61</v>
+        <v>35.06</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
       <c r="G246" s="7" t="inlineStr"/>
@@ -5982,10 +5982,10 @@
         <v>25.38</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>27.37</v>
+        <v>27.73</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>27.47</v>
+        <v>27.83</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
       <c r="G247" s="7" t="inlineStr"/>
@@ -6003,10 +6003,10 @@
         <v>17.76</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>23.84</v>
+        <v>24.15</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>19.16</v>
+        <v>19.41</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
       <c r="G248" s="7" t="inlineStr"/>
@@ -6024,10 +6024,10 @@
         <v>133.12</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>89.20999999999999</v>
+        <v>90.37</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>143.19</v>
+        <v>145.05</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
       <c r="G249" s="7" t="inlineStr"/>
@@ -6045,10 +6045,10 @@
         <v>46.11</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>55.75</v>
+        <v>56.47</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>49.44</v>
+        <v>50.09</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
       <c r="G250" s="7" t="inlineStr"/>
@@ -6066,10 +6066,10 @@
         <v>79.92</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>90.62</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>85.40000000000001</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
       <c r="G251" s="7" t="inlineStr"/>
@@ -6087,10 +6087,10 @@
         <v>145.96</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>141.6</v>
+        <v>143.44</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>155.43</v>
+        <v>157.45</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
       <c r="G252" s="7" t="inlineStr"/>
@@ -6108,10 +6108,10 @@
         <v>198.44</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>174.28</v>
+        <v>176.55</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>210.58</v>
+        <v>213.32</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
       <c r="G253" s="7" t="inlineStr"/>
@@ -6129,10 +6129,10 @@
         <v>191.27</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>158.15</v>
+        <v>160.21</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>202.83</v>
+        <v>205.46</v>
       </c>
       <c r="F254" s="7" t="inlineStr"/>
       <c r="G254" s="7" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
         <v>215.57</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>151.95</v>
+        <v>153.93</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>228.43</v>
+        <v>231.4</v>
       </c>
       <c r="F255" s="7" t="inlineStr"/>
       <c r="G255" s="7" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         <v>26.5</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>18.41</v>
+        <v>18.65</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>28.06</v>
+        <v>28.43</v>
       </c>
       <c r="F256" s="7" t="inlineStr"/>
       <c r="G256" s="7" t="inlineStr"/>
@@ -6192,10 +6192,10 @@
         <v>10.31</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>21.54</v>
+        <v>21.82</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>10.91</v>
+        <v>11.05</v>
       </c>
       <c r="F257" s="7" t="inlineStr"/>
       <c r="G257" s="7" t="inlineStr"/>
@@ -6213,10 +6213,10 @@
         <v>53.17</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>67.76000000000001</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>56.23</v>
+        <v>56.96</v>
       </c>
       <c r="F258" s="7" t="inlineStr"/>
       <c r="G258" s="7" t="inlineStr"/>
@@ -6234,10 +6234,10 @@
         <v>40.31</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>55.22</v>
+        <v>55.94</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>42.6</v>
+        <v>43.15</v>
       </c>
       <c r="F259" s="7" t="inlineStr"/>
       <c r="G259" s="7" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         <v>23.93</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>50.94</v>
+        <v>51.6</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>25.21</v>
+        <v>25.54</v>
       </c>
       <c r="F260" s="7" t="inlineStr"/>
       <c r="G260" s="7" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
         <v>76.84</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>72</v>
+        <v>72.94</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>80.70999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="F261" s="7" t="inlineStr"/>
       <c r="G261" s="7" t="inlineStr"/>
@@ -6297,10 +6297,10 @@
         <v>62.81</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>64.66</v>
+        <v>65.5</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>65.77</v>
+        <v>66.63</v>
       </c>
       <c r="F262" s="7" t="inlineStr"/>
       <c r="G262" s="7" t="inlineStr"/>
@@ -6318,10 +6318,10 @@
         <v>70.45</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>78.09</v>
+        <v>79.11</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>73.59</v>
+        <v>74.55</v>
       </c>
       <c r="F263" s="7" t="inlineStr"/>
       <c r="G263" s="7" t="inlineStr"/>
@@ -6339,10 +6339,10 @@
         <v>93.68000000000001</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>81.33</v>
+        <v>82.38</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>97.61</v>
+        <v>98.88</v>
       </c>
       <c r="F264" s="7" t="inlineStr"/>
       <c r="G264" s="7" t="inlineStr"/>
@@ -6360,10 +6360,10 @@
         <v>462.78</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>275.03</v>
+        <v>278.61</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>481.02</v>
+        <v>487.28</v>
       </c>
       <c r="F265" s="7" t="inlineStr"/>
       <c r="G265" s="7" t="inlineStr"/>
@@ -6381,10 +6381,10 @@
         <v>107.55</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>84.98999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>111.3</v>
+        <v>112.75</v>
       </c>
       <c r="F266" s="7" t="inlineStr"/>
       <c r="G266" s="7" t="inlineStr"/>
@@ -6402,10 +6402,10 @@
         <v>107.41</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>96.02</v>
+        <v>97.27</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>110.67</v>
+        <v>112.11</v>
       </c>
       <c r="F267" s="7" t="inlineStr"/>
       <c r="G267" s="7" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
         <v>61.94</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>56.7</v>
+        <v>57.44</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>63.54</v>
+        <v>64.37</v>
       </c>
       <c r="F268" s="7" t="inlineStr"/>
       <c r="G268" s="7" t="inlineStr"/>
@@ -6444,10 +6444,10 @@
         <v>45.17</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>52.6</v>
+        <v>53.28</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>46.25</v>
+        <v>46.85</v>
       </c>
       <c r="F269" s="7" t="inlineStr"/>
       <c r="G269" s="7" t="inlineStr"/>
@@ -6465,10 +6465,10 @@
         <v>14.11</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>32.62</v>
+        <v>33.04</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>14.42</v>
+        <v>14.61</v>
       </c>
       <c r="F270" s="7" t="inlineStr"/>
       <c r="G270" s="7" t="inlineStr"/>
@@ -6486,10 +6486,10 @@
         <v>17.32</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>28.06</v>
+        <v>28.42</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>17.66</v>
+        <v>17.89</v>
       </c>
       <c r="F271" s="7" t="inlineStr"/>
       <c r="G271" s="7" t="inlineStr"/>
@@ -6507,10 +6507,10 @@
         <v>43.95</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>39.14</v>
+        <v>39.64</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>44.62</v>
+        <v>45.2</v>
       </c>
       <c r="F272" s="7" t="inlineStr"/>
       <c r="G272" s="7" t="inlineStr"/>
@@ -6528,10 +6528,10 @@
         <v>40.32</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>45.54</v>
+        <v>46.13</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>40.75</v>
+        <v>41.28</v>
       </c>
       <c r="F273" s="7" t="inlineStr"/>
       <c r="G273" s="7" t="inlineStr"/>
@@ -6549,10 +6549,10 @@
         <v>44.57</v>
       </c>
       <c r="D274" s="5" t="n">
-        <v>45.01</v>
+        <v>45.59</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>44.84</v>
+        <v>45.42</v>
       </c>
       <c r="F274" s="7" t="inlineStr"/>
       <c r="G274" s="7" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         <v>37.64</v>
       </c>
       <c r="D275" s="5" t="n">
-        <v>35.82</v>
+        <v>36.29</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>37.79</v>
+        <v>38.28</v>
       </c>
       <c r="F275" s="7" t="inlineStr"/>
       <c r="G275" s="7" t="inlineStr"/>
@@ -6591,10 +6591,10 @@
         <v>73.55</v>
       </c>
       <c r="D276" s="5" t="n">
-        <v>64.90000000000001</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>73.7</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="F276" s="7" t="inlineStr"/>
       <c r="G276" s="7" t="inlineStr"/>
@@ -6612,10 +6612,10 @@
         <v>77.88</v>
       </c>
       <c r="D277" s="5" t="n">
-        <v>66.81</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>77.88</v>
+        <v>78.89</v>
       </c>
       <c r="F277" s="7" t="inlineStr"/>
       <c r="G277" s="7" t="inlineStr"/>
@@ -6633,17 +6633,13 @@
         <v>90.62</v>
       </c>
       <c r="D278" s="5" t="n">
-        <v>70.36</v>
+        <v>70.97</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>90.62</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F278" s="7" t="inlineStr"/>
-      <c r="G278" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G278" s="7" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
@@ -6658,17 +6654,13 @@
         <v>68.78</v>
       </c>
       <c r="D279" s="5" t="n">
-        <v>60.4</v>
+        <v>60.66</v>
       </c>
       <c r="E279" s="5" t="n">
-        <v>68.78</v>
+        <v>69.08</v>
       </c>
       <c r="F279" s="7" t="inlineStr"/>
-      <c r="G279" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G279" s="7" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
@@ -6689,11 +6681,7 @@
         <v>37.02</v>
       </c>
       <c r="F280" s="7" t="inlineStr"/>
-      <c r="G280" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="G280" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6756,10 +6744,10 @@
         <v>33.07</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>47.9</v>
+        <v>48.52</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>61.83</v>
+        <v>62.63</v>
       </c>
     </row>
     <row r="3">
@@ -6775,10 +6763,10 @@
         <v>23.54</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>37.6</v>
+        <v>38.09</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>43.93</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="4">
@@ -6794,10 +6782,10 @@
         <v>25.18</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>38.61</v>
+        <v>39.11</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>46.9</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="5">
@@ -6813,10 +6801,10 @@
         <v>25.05</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>38.56</v>
+        <v>39.06</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>46.57</v>
+        <v>47.18</v>
       </c>
     </row>
     <row r="6">
@@ -6832,10 +6820,10 @@
         <v>25.87</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>39.31</v>
+        <v>39.82</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>48.02</v>
+        <v>48.64</v>
       </c>
     </row>
     <row r="7">
@@ -6851,10 +6839,10 @@
         <v>33.9</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>46.26</v>
+        <v>46.87</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>62.81</v>
+        <v>63.63</v>
       </c>
     </row>
     <row r="8">
@@ -6870,10 +6858,10 @@
         <v>30.13</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>41.6</v>
+        <v>42.14</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>55.66</v>
+        <v>56.38</v>
       </c>
     </row>
     <row r="9">
@@ -6889,10 +6877,10 @@
         <v>48.3</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>71.13</v>
+        <v>72.06</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>88.95999999999999</v>
+        <v>90.12</v>
       </c>
     </row>
     <row r="10">
@@ -6908,10 +6896,10 @@
         <v>28.1</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>39.45</v>
+        <v>39.96</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>51.6</v>
+        <v>52.28</v>
       </c>
     </row>
     <row r="11">
@@ -6927,10 +6915,10 @@
         <v>36.91</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>54.02</v>
+        <v>54.72</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>67.68000000000001</v>
+        <v>68.56</v>
       </c>
     </row>
     <row r="12">
@@ -6946,10 +6934,10 @@
         <v>39.52</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>57.29</v>
+        <v>58.03</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>72.34999999999999</v>
+        <v>73.29000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -6965,10 +6953,10 @@
         <v>34.78</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>52.33</v>
+        <v>53.01</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>63.58</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -6984,10 +6972,10 @@
         <v>43.74</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>57.26</v>
+        <v>58.01</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>79.84</v>
+        <v>80.88</v>
       </c>
     </row>
     <row r="15">
@@ -7003,10 +6991,10 @@
         <v>27.28</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>41.11</v>
+        <v>41.64</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>49.73</v>
+        <v>50.38</v>
       </c>
     </row>
     <row r="16">
@@ -7022,10 +7010,10 @@
         <v>31.28</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>49.52</v>
+        <v>50.16</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>56.94</v>
+        <v>57.68</v>
       </c>
     </row>
     <row r="17">
@@ -7041,10 +7029,10 @@
         <v>70.44</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>81.48999999999999</v>
+        <v>82.55</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>127.91</v>
+        <v>129.57</v>
       </c>
     </row>
     <row r="18">
@@ -7060,10 +7048,10 @@
         <v>43.97</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>64.59</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>79.64</v>
+        <v>80.67</v>
       </c>
     </row>
     <row r="19">
@@ -7079,10 +7067,10 @@
         <v>32.66</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>49.43</v>
+        <v>50.07</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>59</v>
+        <v>59.77</v>
       </c>
     </row>
     <row r="20">
@@ -7098,10 +7086,10 @@
         <v>29.7</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>41.17</v>
+        <v>41.71</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>53.54</v>
+        <v>54.23</v>
       </c>
     </row>
     <row r="21">
@@ -7117,10 +7105,10 @@
         <v>27.12</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>39.26</v>
+        <v>39.77</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>48.78</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="22">
@@ -7136,10 +7124,10 @@
         <v>20.94</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>33.56</v>
+        <v>34</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>37.58</v>
+        <v>38.07</v>
       </c>
     </row>
     <row r="23">
@@ -7155,10 +7143,10 @@
         <v>37.71</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>54.86</v>
+        <v>55.57</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>67.54000000000001</v>
+        <v>68.42</v>
       </c>
     </row>
     <row r="24">
@@ -7174,10 +7162,10 @@
         <v>29</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>43.9</v>
+        <v>44.47</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>51.84</v>
+        <v>52.51</v>
       </c>
     </row>
     <row r="25">
@@ -7193,10 +7181,10 @@
         <v>27.23</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>41.99</v>
+        <v>42.54</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>48.58</v>
+        <v>49.21</v>
       </c>
     </row>
     <row r="26">
@@ -7212,10 +7200,10 @@
         <v>32.3</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>47.14</v>
+        <v>47.75</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>57.43</v>
+        <v>58.18</v>
       </c>
     </row>
     <row r="27">
@@ -7231,10 +7219,10 @@
         <v>40.15</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>53.17</v>
+        <v>53.86</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>71.15000000000001</v>
+        <v>72.08</v>
       </c>
     </row>
     <row r="28">
@@ -7250,10 +7238,10 @@
         <v>37.3</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>51.47</v>
+        <v>52.14</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>65.89</v>
+        <v>66.73999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -7269,10 +7257,10 @@
         <v>28.44</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>39.92</v>
+        <v>40.44</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>50.15</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="30">
@@ -7288,10 +7276,10 @@
         <v>46.09</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>54.04</v>
+        <v>54.74</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>81.13</v>
+        <v>82.19</v>
       </c>
     </row>
     <row r="31">
@@ -7307,10 +7295,10 @@
         <v>49.13</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>60.17</v>
+        <v>60.95</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>86.34</v>
+        <v>87.45999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -7326,10 +7314,10 @@
         <v>88.39</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>93.64</v>
+        <v>94.86</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>154.88</v>
+        <v>156.9</v>
       </c>
     </row>
     <row r="33">
@@ -7345,10 +7333,10 @@
         <v>105.26</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>97.84999999999999</v>
+        <v>99.12</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>183.92</v>
+        <v>186.31</v>
       </c>
     </row>
     <row r="34">
@@ -7364,10 +7352,10 @@
         <v>29.05</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>40.7</v>
+        <v>41.23</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>50.61</v>
+        <v>51.27</v>
       </c>
     </row>
     <row r="35">
@@ -7383,10 +7371,10 @@
         <v>27.89</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>39.15</v>
+        <v>39.66</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>48.34</v>
+        <v>48.97</v>
       </c>
     </row>
     <row r="36">
@@ -7402,10 +7390,10 @@
         <v>37.92</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>48.71</v>
+        <v>49.34</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>65.38</v>
+        <v>66.23</v>
       </c>
     </row>
     <row r="37">
@@ -7421,10 +7409,10 @@
         <v>42.6</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>59.36</v>
+        <v>60.13</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>73.06999999999999</v>
+        <v>74.02</v>
       </c>
     </row>
     <row r="38">
@@ -7440,10 +7428,10 @@
         <v>71.95</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>80.72</v>
+        <v>81.77</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>123.04</v>
+        <v>124.64</v>
       </c>
     </row>
     <row r="39">
@@ -7459,10 +7447,10 @@
         <v>38.93</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>54.92</v>
+        <v>55.63</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>66.38</v>
+        <v>67.23999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -7478,10 +7466,10 @@
         <v>38.74</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>52.36</v>
+        <v>53.04</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>65.86</v>
+        <v>66.72</v>
       </c>
     </row>
     <row r="41">
@@ -7497,10 +7485,10 @@
         <v>34.58</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>47.04</v>
+        <v>47.65</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>58.81</v>
+        <v>59.58</v>
       </c>
     </row>
     <row r="42">
@@ -7516,10 +7504,10 @@
         <v>42.04</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>55.65</v>
+        <v>56.38</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>71.53</v>
+        <v>72.45999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -7535,10 +7523,10 @@
         <v>28.05</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>37.92</v>
+        <v>38.41</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>47.74</v>
+        <v>48.36</v>
       </c>
     </row>
     <row r="44">
@@ -7554,10 +7542,10 @@
         <v>165.27</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>155.63</v>
+        <v>157.65</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>281.22</v>
+        <v>284.87</v>
       </c>
     </row>
     <row r="45">
@@ -7573,10 +7561,10 @@
         <v>68.56999999999999</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>80.7</v>
+        <v>81.75</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>116.64</v>
+        <v>118.16</v>
       </c>
     </row>
     <row r="46">
@@ -7592,10 +7580,10 @@
         <v>74.37</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>90.61</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>126.48</v>
+        <v>128.12</v>
       </c>
     </row>
     <row r="47">
@@ -7611,10 +7599,10 @@
         <v>80.98999999999999</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>114.76</v>
+        <v>116.26</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>137.17</v>
+        <v>138.95</v>
       </c>
     </row>
     <row r="48">
@@ -7630,10 +7618,10 @@
         <v>74.97</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>105.66</v>
+        <v>107.03</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>126.46</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="49">
@@ -7649,10 +7637,10 @@
         <v>218.49</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>240.71</v>
+        <v>243.83</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>367.06</v>
+        <v>371.83</v>
       </c>
     </row>
     <row r="50">
@@ -7668,10 +7656,10 @@
         <v>114.96</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>143.39</v>
+        <v>145.26</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>192.69</v>
+        <v>195.19</v>
       </c>
     </row>
     <row r="51">
@@ -7687,10 +7675,10 @@
         <v>50.52</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>69.78</v>
+        <v>70.69</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>84.48</v>
+        <v>85.58</v>
       </c>
     </row>
     <row r="52">
@@ -7706,10 +7694,10 @@
         <v>54.66</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>74.38</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>91.2</v>
+        <v>92.38</v>
       </c>
     </row>
     <row r="53">
@@ -7725,10 +7713,10 @@
         <v>45.03</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>59.06</v>
+        <v>59.83</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>74.90000000000001</v>
+        <v>75.87</v>
       </c>
     </row>
     <row r="54">
@@ -7744,10 +7732,10 @@
         <v>53.86</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>70.84999999999999</v>
+        <v>71.78</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>89.31</v>
+        <v>90.47</v>
       </c>
     </row>
     <row r="55">
@@ -7763,10 +7751,10 @@
         <v>61.74</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>74.04000000000001</v>
+        <v>75</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>102.06</v>
+        <v>103.39</v>
       </c>
     </row>
     <row r="56">
@@ -7782,10 +7770,10 @@
         <v>54.78</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>66.44</v>
+        <v>67.3</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>90.15000000000001</v>
+        <v>91.33</v>
       </c>
     </row>
     <row r="57">
@@ -7801,10 +7789,10 @@
         <v>51.53</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>60.43</v>
+        <v>61.21</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>84.43000000000001</v>
+        <v>85.53</v>
       </c>
     </row>
     <row r="58">
@@ -7820,10 +7808,10 @@
         <v>84.09999999999999</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>85.05</v>
+        <v>86.16</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>137.19</v>
+        <v>138.97</v>
       </c>
     </row>
     <row r="59">
@@ -7839,10 +7827,10 @@
         <v>49.7</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>64.70999999999999</v>
+        <v>65.55</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>80.68000000000001</v>
+        <v>81.73</v>
       </c>
     </row>
     <row r="60">
@@ -7858,10 +7846,10 @@
         <v>63.89</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>87.29000000000001</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>103.22</v>
+        <v>104.56</v>
       </c>
     </row>
     <row r="61">
@@ -7877,10 +7865,10 @@
         <v>51.98</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>67.59999999999999</v>
+        <v>68.47</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>83.58</v>
+        <v>84.66</v>
       </c>
     </row>
     <row r="62">
@@ -7896,10 +7884,10 @@
         <v>60.1</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>68.94</v>
+        <v>69.83</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>96.26000000000001</v>
+        <v>97.51000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -7915,10 +7903,10 @@
         <v>50.49</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>65.27</v>
+        <v>66.12</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>80.56</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -7934,10 +7922,10 @@
         <v>47.53</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>58.2</v>
+        <v>58.96</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>75.54000000000001</v>
+        <v>76.53</v>
       </c>
     </row>
     <row r="65">
@@ -7953,10 +7941,10 @@
         <v>50.87</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>62.64</v>
+        <v>63.46</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>80.94</v>
+        <v>81.98999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -7972,10 +7960,10 @@
         <v>44.54</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>55.05</v>
+        <v>55.77</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>70.95</v>
+        <v>71.87</v>
       </c>
     </row>
     <row r="67">
@@ -7991,10 +7979,10 @@
         <v>27.59</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>35.86</v>
+        <v>36.33</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>44</v>
+        <v>44.57</v>
       </c>
     </row>
     <row r="68">
@@ -8010,10 +7998,10 @@
         <v>248.01</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>200.11</v>
+        <v>202.72</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>395.33</v>
+        <v>400.47</v>
       </c>
     </row>
     <row r="69">
@@ -8029,10 +8017,10 @@
         <v>44.12</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>53.22</v>
+        <v>53.91</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>70.3</v>
+        <v>71.22</v>
       </c>
     </row>
     <row r="70">
@@ -8048,10 +8036,10 @@
         <v>32.01</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>40.25</v>
+        <v>40.78</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>50.99</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="71">
@@ -8067,10 +8055,10 @@
         <v>48.96</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>59.32</v>
+        <v>60.09</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>77.86</v>
+        <v>78.87</v>
       </c>
     </row>
     <row r="72">
@@ -8086,10 +8074,10 @@
         <v>37.6</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>49.93</v>
+        <v>50.58</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>59.69</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="73">
@@ -8105,10 +8093,10 @@
         <v>37.07</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>47.66</v>
+        <v>48.28</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>58.75</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="74">
@@ -8124,10 +8112,10 @@
         <v>32.46</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>42.41</v>
+        <v>42.96</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>51.29</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="75">
@@ -8143,10 +8131,10 @@
         <v>27.81</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>35.34</v>
+        <v>35.8</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>43.8</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="76">
@@ -8162,10 +8150,10 @@
         <v>27.42</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>36.02</v>
+        <v>36.49</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>43.05</v>
+        <v>43.61</v>
       </c>
     </row>
     <row r="77">
@@ -8181,10 +8169,10 @@
         <v>30.83</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>40.06</v>
+        <v>40.58</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>48.32</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="78">
@@ -8200,10 +8188,10 @@
         <v>44.77</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>50.74</v>
+        <v>51.4</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>70.04000000000001</v>
+        <v>70.95</v>
       </c>
     </row>
     <row r="79">
@@ -8219,10 +8207,10 @@
         <v>29.38</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>36.72</v>
+        <v>37.19</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>45.88</v>
+        <v>46.48</v>
       </c>
     </row>
     <row r="80">
@@ -8238,10 +8226,10 @@
         <v>114.66</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>94.89</v>
+        <v>96.13</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>178.52</v>
+        <v>180.84</v>
       </c>
     </row>
     <row r="81">
@@ -8257,10 +8245,10 @@
         <v>123.77</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>105.4</v>
+        <v>106.77</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>192.1</v>
+        <v>194.6</v>
       </c>
     </row>
     <row r="82">
@@ -8276,10 +8264,10 @@
         <v>26.87</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>35.37</v>
+        <v>35.83</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>41.58</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="83">
@@ -8295,10 +8283,10 @@
         <v>131.27</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>110.5</v>
+        <v>111.94</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>202.71</v>
+        <v>205.35</v>
       </c>
     </row>
     <row r="84">
@@ -8314,10 +8302,10 @@
         <v>34.5</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>46.99</v>
+        <v>47.6</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>53.17</v>
+        <v>53.86</v>
       </c>
     </row>
     <row r="85">
@@ -8333,10 +8321,10 @@
         <v>36.24</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>48.29</v>
+        <v>48.92</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>55.74</v>
+        <v>56.46</v>
       </c>
     </row>
     <row r="86">
@@ -8352,10 +8340,10 @@
         <v>30.25</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>40.89</v>
+        <v>41.42</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>46.41</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="87">
@@ -8371,10 +8359,10 @@
         <v>30.63</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>41.4</v>
+        <v>41.94</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>46.88</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="88">
@@ -8390,10 +8378,10 @@
         <v>24.81</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>33.78</v>
+        <v>34.22</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>37.89</v>
+        <v>38.38</v>
       </c>
     </row>
     <row r="89">
@@ -8409,10 +8397,10 @@
         <v>24.32</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>31.75</v>
+        <v>32.16</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>37.09</v>
+        <v>37.57</v>
       </c>
     </row>
     <row r="90">
@@ -8428,10 +8416,10 @@
         <v>20.74</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>28.06</v>
+        <v>28.42</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>31.59</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91">
@@ -8447,10 +8435,10 @@
         <v>18.84</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>25.13</v>
+        <v>25.46</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>28.66</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="92">
@@ -8466,10 +8454,10 @@
         <v>65.90000000000001</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>62.15</v>
+        <v>62.96</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>99.73</v>
+        <v>101.02</v>
       </c>
     </row>
     <row r="93">
@@ -8485,10 +8473,10 @@
         <v>59.12</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>60.92</v>
+        <v>61.71</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>89.01000000000001</v>
+        <v>90.17</v>
       </c>
     </row>
     <row r="94">
@@ -8504,10 +8492,10 @@
         <v>28.33</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>37.39</v>
+        <v>37.87</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>42.44</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="95">
@@ -8523,10 +8511,10 @@
         <v>28.26</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>38.23</v>
+        <v>38.73</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>42.2</v>
+        <v>42.75</v>
       </c>
     </row>
     <row r="96">
@@ -8542,10 +8530,10 @@
         <v>40.34</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>51.14</v>
+        <v>51.8</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>60.06</v>
+        <v>60.84</v>
       </c>
     </row>
     <row r="97">
@@ -8561,10 +8549,10 @@
         <v>33.79</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>41.44</v>
+        <v>41.98</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>50.15</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="98">
@@ -8580,10 +8568,10 @@
         <v>37.74</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>43.68</v>
+        <v>44.25</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>55.91</v>
+        <v>56.63</v>
       </c>
     </row>
     <row r="99">
@@ -8599,10 +8587,10 @@
         <v>35.21</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>44.28</v>
+        <v>44.85</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>52.05</v>
+        <v>52.73</v>
       </c>
     </row>
     <row r="100">
@@ -8618,10 +8606,10 @@
         <v>31.48</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>39.81</v>
+        <v>40.33</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>46.45</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="101">
@@ -8637,10 +8625,10 @@
         <v>28.55</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>34.84</v>
+        <v>35.29</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>42.13</v>
+        <v>42.67</v>
       </c>
     </row>
     <row r="102">
@@ -8656,10 +8644,10 @@
         <v>30.42</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>39.22</v>
+        <v>39.73</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>44.88</v>
+        <v>45.47</v>
       </c>
     </row>
     <row r="103">
@@ -8675,10 +8663,10 @@
         <v>25.43</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>32.73</v>
+        <v>33.15</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>37.52</v>
+        <v>38.01</v>
       </c>
     </row>
     <row r="104">
@@ -8694,10 +8682,10 @@
         <v>28.96</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>35.45</v>
+        <v>35.91</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>42.72</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="105">
@@ -8713,10 +8701,10 @@
         <v>29.72</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>38.13</v>
+        <v>38.62</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>43.83</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="106">
@@ -8732,10 +8720,10 @@
         <v>27.57</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>34.95</v>
+        <v>35.4</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>40.66</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="107">
@@ -8751,10 +8739,10 @@
         <v>36.22</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>47.12</v>
+        <v>47.73</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>53.32</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="108">
@@ -8770,10 +8758,10 @@
         <v>30.09</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>39.06</v>
+        <v>39.57</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>44.22</v>
+        <v>44.79</v>
       </c>
     </row>
     <row r="109">
@@ -8789,10 +8777,10 @@
         <v>42.49</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>53.91</v>
+        <v>54.61</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>62.33</v>
+        <v>63.14</v>
       </c>
     </row>
     <row r="110">
@@ -8808,10 +8796,10 @@
         <v>89.70999999999999</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>107.28</v>
+        <v>108.67</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>131.01</v>
+        <v>132.71</v>
       </c>
     </row>
     <row r="111">
@@ -8827,10 +8815,10 @@
         <v>58.42</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>81.06</v>
+        <v>82.12</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>84.93000000000001</v>
+        <v>86.04000000000001</v>
       </c>
     </row>
     <row r="112">
@@ -8846,10 +8834,10 @@
         <v>60.79</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>78.41</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>87.98</v>
+        <v>89.13</v>
       </c>
     </row>
     <row r="113">
@@ -8865,10 +8853,10 @@
         <v>54.54</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>74.14</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>78.87</v>
+        <v>79.89</v>
       </c>
     </row>
     <row r="114">
@@ -8884,10 +8872,10 @@
         <v>108.42</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>111.51</v>
+        <v>112.96</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>156.65</v>
+        <v>158.69</v>
       </c>
     </row>
     <row r="115">
@@ -8903,10 +8891,10 @@
         <v>58.79</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>75.33</v>
+        <v>76.31</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>84.87</v>
+        <v>85.97</v>
       </c>
     </row>
     <row r="116">
@@ -8922,10 +8910,10 @@
         <v>65.27</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>78.26000000000001</v>
+        <v>79.27</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>94.12</v>
+        <v>95.34</v>
       </c>
     </row>
     <row r="117">
@@ -8941,10 +8929,10 @@
         <v>59.25</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>77.19</v>
+        <v>78.19</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>85.34</v>
+        <v>86.45</v>
       </c>
     </row>
     <row r="118">
@@ -8960,10 +8948,10 @@
         <v>59.68</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>75.26000000000001</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>85.87</v>
+        <v>86.98</v>
       </c>
     </row>
     <row r="119">
@@ -8979,10 +8967,10 @@
         <v>53.14</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>71.88</v>
+        <v>72.81</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>76.36</v>
+        <v>77.34999999999999</v>
       </c>
     </row>
     <row r="120">
@@ -8998,10 +8986,10 @@
         <v>60.42</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>78.72</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>86.70999999999999</v>
+        <v>87.84</v>
       </c>
     </row>
     <row r="121">
@@ -9017,10 +9005,10 @@
         <v>70.08</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>87.29000000000001</v>
+        <v>88.42</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>100.45</v>
+        <v>101.75</v>
       </c>
     </row>
     <row r="122">
@@ -9036,10 +9024,10 @@
         <v>61.74</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>83.3</v>
+        <v>84.38</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>88.13</v>
+        <v>89.28</v>
       </c>
     </row>
     <row r="123">
@@ -9055,10 +9043,10 @@
         <v>57.53</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>76.95</v>
+        <v>77.95</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>81.79000000000001</v>
+        <v>82.86</v>
       </c>
     </row>
     <row r="124">
@@ -9074,10 +9062,10 @@
         <v>51.96</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>69.73999999999999</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>73.58</v>
+        <v>74.53</v>
       </c>
     </row>
     <row r="125">
@@ -9093,10 +9081,10 @@
         <v>51.51</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>69.88</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>72.77</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="126">
@@ -9112,10 +9100,10 @@
         <v>49.21</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>65.90000000000001</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>69.34999999999999</v>
+        <v>70.25</v>
       </c>
     </row>
     <row r="127">
@@ -9131,10 +9119,10 @@
         <v>57.33</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>70.76000000000001</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>80.59999999999999</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="128">
@@ -9150,10 +9138,10 @@
         <v>105.36</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>101.63</v>
+        <v>102.95</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>147.84</v>
+        <v>149.76</v>
       </c>
     </row>
     <row r="129">
@@ -9169,10 +9157,10 @@
         <v>51.23</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>68.97</v>
+        <v>69.87</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>71.73999999999999</v>
+        <v>72.68000000000001</v>
       </c>
     </row>
     <row r="130">
@@ -9188,10 +9176,10 @@
         <v>50.43</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>64.23999999999999</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>70.48</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -9207,10 +9195,10 @@
         <v>46.35</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>61.1</v>
+        <v>61.9</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>64.67</v>
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="132">
@@ -9226,10 +9214,10 @@
         <v>53.06</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>67.14</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>73.91</v>
+        <v>74.87</v>
       </c>
     </row>
     <row r="133">
@@ -9245,10 +9233,10 @@
         <v>53.86</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>68.38</v>
+        <v>69.27</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>74.90000000000001</v>
+        <v>75.87</v>
       </c>
     </row>
     <row r="134">
@@ -9264,10 +9252,10 @@
         <v>43.59</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>53.59</v>
+        <v>54.29</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>60.53</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="135">
@@ -9283,10 +9271,10 @@
         <v>40.37</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>47.86</v>
+        <v>48.48</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>55.98</v>
+        <v>56.71</v>
       </c>
     </row>
     <row r="136">
@@ -9302,10 +9290,10 @@
         <v>41.59</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>50.21</v>
+        <v>50.87</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>57.59</v>
+        <v>58.34</v>
       </c>
     </row>
     <row r="137">
@@ -9321,10 +9309,10 @@
         <v>30.36</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>36.8</v>
+        <v>37.28</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>42.02</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="138">
@@ -9340,10 +9328,10 @@
         <v>34.02</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>39.5</v>
+        <v>40.01</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>47.05</v>
+        <v>47.66</v>
       </c>
     </row>
     <row r="139">
@@ -9359,10 +9347,10 @@
         <v>31.02</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>36.68</v>
+        <v>37.16</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>42.88</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="140">
@@ -9378,10 +9366,10 @@
         <v>33.35</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>36.05</v>
+        <v>36.52</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>46.07</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="141">
@@ -9397,10 +9385,10 @@
         <v>34.67</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>38.69</v>
+        <v>39.2</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>47.86</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="142">
@@ -9416,10 +9404,10 @@
         <v>30.8</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>35.61</v>
+        <v>36.07</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>42.49</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="143">
@@ -9435,10 +9423,10 @@
         <v>34.91</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>39.79</v>
+        <v>40.31</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>48.05</v>
+        <v>48.67</v>
       </c>
     </row>
     <row r="144">
@@ -9454,10 +9442,10 @@
         <v>38.04</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>40.99</v>
+        <v>41.52</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>52.23</v>
+        <v>52.91</v>
       </c>
     </row>
     <row r="145">
@@ -9473,10 +9461,10 @@
         <v>40.94</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>47.13</v>
+        <v>47.75</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>56.08</v>
+        <v>56.81</v>
       </c>
     </row>
     <row r="146">
@@ -9492,10 +9480,10 @@
         <v>42.4</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>47.54</v>
+        <v>48.16</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>58</v>
+        <v>58.76</v>
       </c>
     </row>
     <row r="147">
@@ -9511,10 +9499,10 @@
         <v>41.42</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>47.87</v>
+        <v>48.5</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>56.59</v>
+        <v>57.33</v>
       </c>
     </row>
     <row r="148">
@@ -9530,10 +9518,10 @@
         <v>50.53</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>60.79</v>
+        <v>61.58</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>68.95</v>
+        <v>69.84</v>
       </c>
     </row>
     <row r="149">
@@ -9549,10 +9537,10 @@
         <v>44.46</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>48.55</v>
+        <v>49.19</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>60.59</v>
+        <v>61.38</v>
       </c>
     </row>
     <row r="150">
@@ -9568,10 +9556,10 @@
         <v>44.68</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>47.53</v>
+        <v>48.14</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>60.81</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="151">
@@ -9587,10 +9575,10 @@
         <v>61.92</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>65.26000000000001</v>
+        <v>66.11</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>84.16</v>
+        <v>85.26000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -9606,10 +9594,10 @@
         <v>72.53</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>63.86</v>
+        <v>64.69</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>98.65000000000001</v>
+        <v>99.93000000000001</v>
       </c>
     </row>
     <row r="153">
@@ -9625,10 +9613,10 @@
         <v>43.88</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>48.21</v>
+        <v>48.84</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>59.72</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="154">
@@ -9644,10 +9632,10 @@
         <v>58.3</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>62.5</v>
+        <v>63.31</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>79.40000000000001</v>
+        <v>80.43000000000001</v>
       </c>
     </row>
     <row r="155">
@@ -9663,10 +9651,10 @@
         <v>59.14</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>62.4</v>
+        <v>63.21</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>80.43000000000001</v>
+        <v>81.47</v>
       </c>
     </row>
     <row r="156">
@@ -9682,10 +9670,10 @@
         <v>73.56999999999999</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>73.66</v>
+        <v>74.61</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>99.91</v>
+        <v>101.21</v>
       </c>
     </row>
     <row r="157">
@@ -9701,10 +9689,10 @@
         <v>114.45</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>125.8</v>
+        <v>127.43</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>155.19</v>
+        <v>157.21</v>
       </c>
     </row>
     <row r="158">
@@ -9720,10 +9708,10 @@
         <v>84.48999999999999</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>87.45</v>
+        <v>88.58</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>114.3</v>
+        <v>115.79</v>
       </c>
     </row>
     <row r="159">
@@ -9739,10 +9727,10 @@
         <v>53.5</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>58.36</v>
+        <v>59.12</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>72.20999999999999</v>
+        <v>73.15000000000001</v>
       </c>
     </row>
     <row r="160">
@@ -9758,10 +9746,10 @@
         <v>47.59</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>55.24</v>
+        <v>55.95</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>64.08</v>
+        <v>64.91</v>
       </c>
     </row>
     <row r="161">
@@ -9777,10 +9765,10 @@
         <v>38.38</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>44.6</v>
+        <v>45.18</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>51.59</v>
+        <v>52.26</v>
       </c>
     </row>
     <row r="162">
@@ -9796,10 +9784,10 @@
         <v>45.05</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>48.4</v>
+        <v>49.03</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>60.45</v>
+        <v>61.24</v>
       </c>
     </row>
     <row r="163">
@@ -9815,10 +9803,10 @@
         <v>37.06</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>40.05</v>
+        <v>40.57</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>49.64</v>
+        <v>50.29</v>
       </c>
     </row>
     <row r="164">
@@ -9834,10 +9822,10 @@
         <v>80.27</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>82.98</v>
+        <v>84.05</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>107.36</v>
+        <v>108.75</v>
       </c>
     </row>
     <row r="165">
@@ -9853,10 +9841,10 @@
         <v>111.69</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>114.91</v>
+        <v>116.41</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>149.15</v>
+        <v>151.09</v>
       </c>
     </row>
     <row r="166">
@@ -9872,10 +9860,10 @@
         <v>110.35</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>120.84</v>
+        <v>122.41</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>147.14</v>
+        <v>149.05</v>
       </c>
     </row>
     <row r="167">
@@ -9891,10 +9879,10 @@
         <v>121.78</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>144.18</v>
+        <v>146.05</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>162.27</v>
+        <v>164.38</v>
       </c>
     </row>
     <row r="168">
@@ -9910,10 +9898,10 @@
         <v>121.22</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>143.75</v>
+        <v>145.62</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>161.42</v>
+        <v>163.52</v>
       </c>
     </row>
     <row r="169">
@@ -9929,10 +9917,10 @@
         <v>103.65</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>131.08</v>
+        <v>132.79</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>137.93</v>
+        <v>139.73</v>
       </c>
     </row>
     <row r="170">
@@ -9948,10 +9936,10 @@
         <v>129.67</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>155.89</v>
+        <v>157.92</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>172.21</v>
+        <v>174.45</v>
       </c>
     </row>
     <row r="171">
@@ -9967,10 +9955,10 @@
         <v>116.97</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>135.94</v>
+        <v>137.71</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>155.03</v>
+        <v>157.04</v>
       </c>
     </row>
     <row r="172">
@@ -9986,10 +9974,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>105.06</v>
+        <v>106.43</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>117.85</v>
+        <v>119.38</v>
       </c>
     </row>
     <row r="173">
@@ -10005,10 +9993,10 @@
         <v>81.72</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>96.75</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>107.85</v>
+        <v>109.25</v>
       </c>
     </row>
     <row r="174">
@@ -10024,10 +10012,10 @@
         <v>111.45</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>125.81</v>
+        <v>127.44</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>146.76</v>
+        <v>148.66</v>
       </c>
     </row>
     <row r="175">
@@ -10043,10 +10031,10 @@
         <v>97.2</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>111.48</v>
+        <v>112.93</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>127.71</v>
+        <v>129.37</v>
       </c>
     </row>
     <row r="176">
@@ -10062,10 +10050,10 @@
         <v>182.54</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>175.12</v>
+        <v>177.4</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>239.48</v>
+        <v>242.6</v>
       </c>
     </row>
     <row r="177">
@@ -10081,10 +10069,10 @@
         <v>123.66</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>127.64</v>
+        <v>129.3</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>162</v>
+        <v>164.11</v>
       </c>
     </row>
     <row r="178">
@@ -10100,10 +10088,10 @@
         <v>81.45999999999999</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>99.43000000000001</v>
+        <v>100.72</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>106.56</v>
+        <v>107.95</v>
       </c>
     </row>
     <row r="179">
@@ -10119,10 +10107,10 @@
         <v>86.12</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>96.73999999999999</v>
+        <v>98</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>112.52</v>
+        <v>113.99</v>
       </c>
     </row>
     <row r="180">
@@ -10138,10 +10126,10 @@
         <v>93.45</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>104.13</v>
+        <v>105.48</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>121.96</v>
+        <v>123.54</v>
       </c>
     </row>
     <row r="181">
@@ -10157,10 +10145,10 @@
         <v>109.8</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>122.16</v>
+        <v>123.75</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>143.12</v>
+        <v>144.98</v>
       </c>
     </row>
     <row r="182">
@@ -10176,10 +10164,10 @@
         <v>86.86</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>91.23999999999999</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>113.06</v>
+        <v>114.53</v>
       </c>
     </row>
     <row r="183">
@@ -10195,10 +10183,10 @@
         <v>100.32</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>102.9</v>
+        <v>104.24</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>130.39</v>
+        <v>132.08</v>
       </c>
     </row>
     <row r="184">
@@ -10214,10 +10202,10 @@
         <v>106.94</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>120.51</v>
+        <v>122.07</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>138.79</v>
+        <v>140.6</v>
       </c>
     </row>
     <row r="185">
@@ -10233,10 +10221,10 @@
         <v>108.4</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>129.34</v>
+        <v>131.02</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>140.44</v>
+        <v>142.27</v>
       </c>
     </row>
     <row r="186">
@@ -10252,10 +10240,10 @@
         <v>104.23</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>126.54</v>
+        <v>128.19</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>134.81</v>
+        <v>136.56</v>
       </c>
     </row>
     <row r="187">
@@ -10271,10 +10259,10 @@
         <v>113.57</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>118.51</v>
+        <v>120.05</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>146.63</v>
+        <v>148.54</v>
       </c>
     </row>
     <row r="188">
@@ -10290,10 +10278,10 @@
         <v>421.41</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>323.22</v>
+        <v>327.43</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>544.12</v>
+        <v>551.2</v>
       </c>
     </row>
     <row r="189">
@@ -10309,10 +10297,10 @@
         <v>119.46</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>143.54</v>
+        <v>145.4</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>154.25</v>
+        <v>156.26</v>
       </c>
     </row>
     <row r="190">
@@ -10328,10 +10316,10 @@
         <v>176.04</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>169.3</v>
+        <v>171.5</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>227.32</v>
+        <v>230.28</v>
       </c>
     </row>
     <row r="191">
@@ -10347,10 +10335,10 @@
         <v>105.41</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>126.87</v>
+        <v>128.51</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>135.85</v>
+        <v>137.61</v>
       </c>
     </row>
     <row r="192">
@@ -10366,10 +10354,10 @@
         <v>103.35</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>118.2</v>
+        <v>119.74</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>132.93</v>
+        <v>134.66</v>
       </c>
     </row>
     <row r="193">
@@ -10385,10 +10373,10 @@
         <v>120.77</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>130.69</v>
+        <v>132.39</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>155.03</v>
+        <v>157.05</v>
       </c>
     </row>
     <row r="194">
@@ -10404,10 +10392,10 @@
         <v>104.22</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>110.09</v>
+        <v>111.52</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>133.53</v>
+        <v>135.27</v>
       </c>
     </row>
     <row r="195">
@@ -10423,10 +10411,10 @@
         <v>128.34</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>134.22</v>
+        <v>135.96</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>164.13</v>
+        <v>166.26</v>
       </c>
     </row>
     <row r="196">
@@ -10442,10 +10430,10 @@
         <v>119.12</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>133.72</v>
+        <v>135.46</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>152.05</v>
+        <v>154.03</v>
       </c>
     </row>
     <row r="197">
@@ -10461,10 +10449,10 @@
         <v>110.98</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>128.25</v>
+        <v>129.92</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>141.34</v>
+        <v>143.18</v>
       </c>
     </row>
     <row r="198">
@@ -10480,10 +10468,10 @@
         <v>68.72</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>86.38</v>
+        <v>87.5</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>87.31999999999999</v>
+        <v>88.45999999999999</v>
       </c>
     </row>
     <row r="199">
@@ -10499,10 +10487,10 @@
         <v>77.23999999999999</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>77.83</v>
+        <v>78.84</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>97.92</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="200">
@@ -10518,10 +10506,10 @@
         <v>255.49</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>181.01</v>
+        <v>183.36</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>323.5</v>
+        <v>327.71</v>
       </c>
     </row>
     <row r="201">
@@ -10537,10 +10525,10 @@
         <v>55.07</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>61.1</v>
+        <v>61.89</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>69.64</v>
+        <v>70.55</v>
       </c>
     </row>
     <row r="202">
@@ -10556,10 +10544,10 @@
         <v>49.68</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>54.69</v>
+        <v>55.4</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>62.75</v>
+        <v>63.57</v>
       </c>
     </row>
     <row r="203">
@@ -10575,10 +10563,10 @@
         <v>41.8</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>44.28</v>
+        <v>44.85</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>53.14</v>
+        <v>53.83</v>
       </c>
     </row>
     <row r="204">
@@ -10594,10 +10582,10 @@
         <v>46.68</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>48.99</v>
+        <v>49.63</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>59.73</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="205">
@@ -10613,10 +10601,10 @@
         <v>62.5</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>62.67</v>
+        <v>63.48</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>80.48999999999999</v>
+        <v>81.54000000000001</v>
       </c>
     </row>
     <row r="206">
@@ -10632,10 +10620,10 @@
         <v>74.52</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>81.48999999999999</v>
+        <v>82.55</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>95.48</v>
+        <v>96.72</v>
       </c>
     </row>
     <row r="207">
@@ -10651,10 +10639,10 @@
         <v>65.59999999999999</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>68.45</v>
+        <v>69.34</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>83.62</v>
+        <v>84.70999999999999</v>
       </c>
     </row>
     <row r="208">
@@ -10670,10 +10658,10 @@
         <v>38.68</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>43.94</v>
+        <v>44.52</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>49.06</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="209">
@@ -10689,10 +10677,10 @@
         <v>53.68</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>56.63</v>
+        <v>57.37</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>67.88</v>
+        <v>68.76000000000001</v>
       </c>
     </row>
     <row r="210">
@@ -10708,10 +10696,10 @@
         <v>49.58</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>55.56</v>
+        <v>56.28</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>62.5</v>
+        <v>63.32</v>
       </c>
     </row>
     <row r="211">
@@ -10727,10 +10715,10 @@
         <v>23.43</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>29.9</v>
+        <v>30.29</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>29.45</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="212">
@@ -10746,10 +10734,10 @@
         <v>20.66</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>28.63</v>
+        <v>29</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>25.92</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="213">
@@ -10765,10 +10753,10 @@
         <v>24.62</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>27.36</v>
+        <v>27.71</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>30.83</v>
+        <v>31.23</v>
       </c>
     </row>
     <row r="214">
@@ -10784,10 +10772,10 @@
         <v>31.29</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>37.94</v>
+        <v>38.43</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>39.1</v>
+        <v>39.61</v>
       </c>
     </row>
     <row r="215">
@@ -10803,10 +10791,10 @@
         <v>60.46</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>61.67</v>
+        <v>62.47</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>75.37</v>
+        <v>76.34999999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10822,10 +10810,10 @@
         <v>113.74</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>90.58</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>141.45</v>
+        <v>143.28</v>
       </c>
     </row>
     <row r="217">
@@ -10841,10 +10829,10 @@
         <v>107.34</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>109.07</v>
+        <v>110.49</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>133.16</v>
+        <v>134.89</v>
       </c>
     </row>
     <row r="218">
@@ -10860,10 +10848,10 @@
         <v>127.01</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>113.46</v>
+        <v>114.94</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>157.12</v>
+        <v>159.16</v>
       </c>
     </row>
     <row r="219">
@@ -10879,10 +10867,10 @@
         <v>54.92</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>57.98</v>
+        <v>58.73</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>67.75</v>
+        <v>68.63</v>
       </c>
     </row>
     <row r="220">
@@ -10898,10 +10886,10 @@
         <v>33.28</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>34.1</v>
+        <v>34.54</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>40.94</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="221">
@@ -10917,10 +10905,10 @@
         <v>15.04</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>22.61</v>
+        <v>22.91</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>18.42</v>
+        <v>18.66</v>
       </c>
     </row>
     <row r="222">
@@ -10936,10 +10924,10 @@
         <v>40.75</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>42.72</v>
+        <v>43.27</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>49.71</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="223">
@@ -10955,10 +10943,10 @@
         <v>30.93</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>39.15</v>
+        <v>39.66</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>37.57</v>
+        <v>38.06</v>
       </c>
     </row>
     <row r="224">
@@ -10974,10 +10962,10 @@
         <v>75.05</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>73.34999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>90.51000000000001</v>
+        <v>91.68000000000001</v>
       </c>
     </row>
     <row r="225">
@@ -10993,10 +10981,10 @@
         <v>48.46</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>64.86</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>58.03</v>
+        <v>58.78</v>
       </c>
     </row>
     <row r="226">
@@ -11012,10 +11000,10 @@
         <v>56.21</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>65.13</v>
+        <v>65.98</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>66.83</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="227">
@@ -11031,10 +11019,10 @@
         <v>167.79</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>167.25</v>
+        <v>169.43</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>198.31</v>
+        <v>200.89</v>
       </c>
     </row>
     <row r="228">
@@ -11050,10 +11038,10 @@
         <v>264.05</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>274.51</v>
+        <v>278.08</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>310.24</v>
+        <v>314.28</v>
       </c>
     </row>
     <row r="229">
@@ -11069,10 +11057,10 @@
         <v>375.27</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>346.32</v>
+        <v>350.82</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>438.34</v>
+        <v>444.03</v>
       </c>
     </row>
     <row r="230">
@@ -11088,10 +11076,10 @@
         <v>431.21</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>395.12</v>
+        <v>400.25</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>500.61</v>
+        <v>507.12</v>
       </c>
     </row>
     <row r="231">
@@ -11107,10 +11095,10 @@
         <v>136.75</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>139.64</v>
+        <v>141.45</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>157.8</v>
+        <v>159.85</v>
       </c>
     </row>
     <row r="232">
@@ -11126,10 +11114,10 @@
         <v>130.63</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>128.2</v>
+        <v>129.86</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>149.83</v>
+        <v>151.78</v>
       </c>
     </row>
     <row r="233">
@@ -11145,10 +11133,10 @@
         <v>96.98999999999999</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>112.74</v>
+        <v>114.21</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>110.56</v>
+        <v>112</v>
       </c>
     </row>
     <row r="234">
@@ -11164,10 +11152,10 @@
         <v>58.52</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>66.43000000000001</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>66.3</v>
+        <v>67.17</v>
       </c>
     </row>
     <row r="235">
@@ -11183,10 +11171,10 @@
         <v>11.86</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>35.23</v>
+        <v>35.68</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>13.36</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="236">
@@ -11202,10 +11190,10 @@
         <v>32.16</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>53.91</v>
+        <v>54.61</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>36.05</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="237">
@@ -11221,10 +11209,10 @@
         <v>55.28</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>64.73999999999999</v>
+        <v>65.58</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>61.7</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="238">
@@ -11240,10 +11228,10 @@
         <v>54.34</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>68.91</v>
+        <v>69.81</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>60.38</v>
+        <v>61.16</v>
       </c>
     </row>
     <row r="239">
@@ -11259,10 +11247,10 @@
         <v>86.66</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>92.65000000000001</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>96.01000000000001</v>
+        <v>97.26000000000001</v>
       </c>
     </row>
     <row r="240">
@@ -11278,10 +11266,10 @@
         <v>145.34</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>140.47</v>
+        <v>142.3</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>160.57</v>
+        <v>162.66</v>
       </c>
     </row>
     <row r="241">
@@ -11297,10 +11285,10 @@
         <v>85.58</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>60.07</v>
+        <v>60.85</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>94.28</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="242">
@@ -11316,10 +11304,10 @@
         <v>75.97</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>60.59</v>
+        <v>61.38</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>83.37</v>
+        <v>84.45999999999999</v>
       </c>
     </row>
     <row r="243">
@@ -11335,10 +11323,10 @@
         <v>79.54000000000001</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>70.69</v>
+        <v>71.61</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>86.95999999999999</v>
+        <v>88.09</v>
       </c>
     </row>
     <row r="244">
@@ -11354,10 +11342,10 @@
         <v>28.25</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>28.65</v>
+        <v>29.03</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>30.77</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="245">
@@ -11373,10 +11361,10 @@
         <v>15.18</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>18.68</v>
+        <v>18.93</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>16.5</v>
+        <v>16.71</v>
       </c>
     </row>
     <row r="246">
@@ -11392,10 +11380,10 @@
         <v>31.91</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>37.89</v>
+        <v>38.39</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>34.61</v>
+        <v>35.06</v>
       </c>
     </row>
     <row r="247">
@@ -11411,10 +11399,10 @@
         <v>25.38</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>27.37</v>
+        <v>27.73</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>27.47</v>
+        <v>27.83</v>
       </c>
     </row>
     <row r="248">
@@ -11430,10 +11418,10 @@
         <v>17.76</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>23.84</v>
+        <v>24.15</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>19.16</v>
+        <v>19.41</v>
       </c>
     </row>
     <row r="249">
@@ -11449,10 +11437,10 @@
         <v>133.12</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>89.20999999999999</v>
+        <v>90.37</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>143.19</v>
+        <v>145.05</v>
       </c>
     </row>
     <row r="250">
@@ -11468,10 +11456,10 @@
         <v>46.11</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>55.75</v>
+        <v>56.47</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>49.44</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="251">
@@ -11487,10 +11475,10 @@
         <v>79.92</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>90.62</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>85.40000000000001</v>
+        <v>86.51000000000001</v>
       </c>
     </row>
     <row r="252">
@@ -11506,10 +11494,10 @@
         <v>145.96</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>141.6</v>
+        <v>143.44</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>155.43</v>
+        <v>157.45</v>
       </c>
     </row>
     <row r="253">
@@ -11525,10 +11513,10 @@
         <v>198.44</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>174.28</v>
+        <v>176.55</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>210.58</v>
+        <v>213.32</v>
       </c>
     </row>
     <row r="254">
@@ -11544,10 +11532,10 @@
         <v>191.27</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>158.15</v>
+        <v>160.21</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>202.83</v>
+        <v>205.46</v>
       </c>
     </row>
     <row r="255">
@@ -11563,10 +11551,10 @@
         <v>215.57</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>151.95</v>
+        <v>153.93</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>228.43</v>
+        <v>231.4</v>
       </c>
     </row>
     <row r="256">
@@ -11582,10 +11570,10 @@
         <v>26.5</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>18.41</v>
+        <v>18.65</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>28.06</v>
+        <v>28.43</v>
       </c>
     </row>
     <row r="257">
@@ -11601,10 +11589,10 @@
         <v>10.31</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>21.54</v>
+        <v>21.82</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>10.91</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="258">
@@ -11620,10 +11608,10 @@
         <v>53.17</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>67.76000000000001</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>56.23</v>
+        <v>56.96</v>
       </c>
     </row>
     <row r="259">
@@ -11639,10 +11627,10 @@
         <v>40.31</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>55.22</v>
+        <v>55.94</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>42.6</v>
+        <v>43.15</v>
       </c>
     </row>
     <row r="260">
@@ -11658,10 +11646,10 @@
         <v>23.93</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>50.94</v>
+        <v>51.6</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>25.21</v>
+        <v>25.54</v>
       </c>
     </row>
     <row r="261">
@@ -11677,10 +11665,10 @@
         <v>76.84</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>72</v>
+        <v>72.94</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>80.70999999999999</v>
+        <v>81.76000000000001</v>
       </c>
     </row>
     <row r="262">
@@ -11696,10 +11684,10 @@
         <v>62.81</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>64.66</v>
+        <v>65.5</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>65.77</v>
+        <v>66.63</v>
       </c>
     </row>
     <row r="263">
@@ -11715,10 +11703,10 @@
         <v>70.45</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>78.09</v>
+        <v>79.11</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>73.59</v>
+        <v>74.55</v>
       </c>
     </row>
     <row r="264">
@@ -11734,10 +11722,10 @@
         <v>93.68000000000001</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>81.33</v>
+        <v>82.38</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>97.61</v>
+        <v>98.88</v>
       </c>
     </row>
     <row r="265">
@@ -11753,10 +11741,10 @@
         <v>462.78</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>275.03</v>
+        <v>278.61</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>481.02</v>
+        <v>487.28</v>
       </c>
     </row>
     <row r="266">
@@ -11772,10 +11760,10 @@
         <v>107.55</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>84.98999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>111.3</v>
+        <v>112.75</v>
       </c>
     </row>
     <row r="267">
@@ -11791,10 +11779,10 @@
         <v>107.41</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>96.02</v>
+        <v>97.27</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>110.67</v>
+        <v>112.11</v>
       </c>
     </row>
     <row r="268">
@@ -11810,10 +11798,10 @@
         <v>61.94</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>56.7</v>
+        <v>57.44</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>63.54</v>
+        <v>64.37</v>
       </c>
     </row>
     <row r="269">
@@ -11829,10 +11817,10 @@
         <v>45.17</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>52.6</v>
+        <v>53.28</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>46.25</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="270">
@@ -11848,10 +11836,10 @@
         <v>14.11</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>32.62</v>
+        <v>33.04</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>14.42</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="271">
@@ -11867,10 +11855,10 @@
         <v>17.32</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>28.06</v>
+        <v>28.42</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>17.66</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="272">
@@ -11886,10 +11874,10 @@
         <v>43.95</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>39.14</v>
+        <v>39.64</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>44.62</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="273">
@@ -11905,10 +11893,10 @@
         <v>40.32</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>45.54</v>
+        <v>46.13</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>40.75</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="274">
@@ -11924,10 +11912,10 @@
         <v>44.57</v>
       </c>
       <c r="D274" s="5" t="n">
-        <v>45.01</v>
+        <v>45.59</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>44.84</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="275">
@@ -11943,10 +11931,10 @@
         <v>37.64</v>
       </c>
       <c r="D275" s="5" t="n">
-        <v>35.82</v>
+        <v>36.29</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>37.79</v>
+        <v>38.28</v>
       </c>
     </row>
     <row r="276">
@@ -11962,10 +11950,10 @@
         <v>73.55</v>
       </c>
       <c r="D276" s="5" t="n">
-        <v>64.90000000000001</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>73.7</v>
+        <v>74.65000000000001</v>
       </c>
     </row>
     <row r="277">
@@ -11981,10 +11969,10 @@
         <v>77.88</v>
       </c>
       <c r="D277" s="5" t="n">
-        <v>66.81</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>77.88</v>
+        <v>78.89</v>
       </c>
     </row>
     <row r="278">
@@ -12000,10 +11988,10 @@
         <v>90.62</v>
       </c>
       <c r="D278" s="5" t="n">
-        <v>70.36</v>
+        <v>70.97</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>90.62</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="279">
@@ -12019,10 +12007,10 @@
         <v>68.78</v>
       </c>
       <c r="D279" s="5" t="n">
-        <v>60.4</v>
+        <v>60.66</v>
       </c>
       <c r="E279" s="5" t="n">
-        <v>68.78</v>
+        <v>69.08</v>
       </c>
     </row>
     <row r="280">
